--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -515,12 +515,12 @@
   <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20.4" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="28.45" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>

--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +37,11 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A6A6A6"/>
+      <sz val="8"/>
     </font>
     <font>
       <b val="1"/>
@@ -86,13 +91,45 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <left style="dashed">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="dashed">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -115,38 +152,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -528,997 +572,1015 @@
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34" customHeight="1">
+    <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>NÓMINA SIMPLIFICADA</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="E1" s="2" t="n"/>
+      <c r="F1" s="2" t="n"/>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Cálculo estimado por periodo (referencia administrativa, no sustituye cálculo fiscal)</t>
         </is>
       </c>
+      <c r="J2" s="6" t="n"/>
+      <c r="K2" s="7" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n"/>
-      <c r="C4" s="4" t="n"/>
-      <c r="D4" s="4" t="n"/>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
       </c>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Días del periodo</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="9" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>% retención IMSS (est.)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="10" t="n">
         <v>0.0275</v>
       </c>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
+      <c r="H5" s="9" t="n"/>
+      <c r="I5" s="9" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Empleado</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Sueldo diario</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="11" t="inlineStr">
         <is>
           <t>Días trab.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="11" t="inlineStr">
         <is>
           <t>Horas extra</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="G7" s="11" t="inlineStr">
         <is>
           <t>Pago horas extra</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="11" t="inlineStr">
         <is>
           <t>Bonos / otros</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
+      <c r="I7" s="11" t="inlineStr">
         <is>
           <t>Retención IMSS</t>
         </is>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="11" t="inlineStr">
         <is>
           <t>ISR retenido</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
+      <c r="K7" s="11" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-      <c r="F8" s="9">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="13" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="14">
         <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="G8" s="9">
+      <c r="G8" s="14">
         <f>IF(C8="","",E8*(C8/8)*2)</f>
         <v/>
       </c>
-      <c r="H8" s="8" t="n"/>
-      <c r="I8" s="9">
+      <c r="H8" s="13" t="n"/>
+      <c r="I8" s="14">
         <f>IF(C8="","",ROUND((F8+G8)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="9">
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="14">
         <f>IF(C8="","",F8+G8+H8-I8-J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="4" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="9">
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="13" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="14">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="14">
         <f>IF(C9="","",E9*(C9/8)*2)</f>
         <v/>
       </c>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="9">
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="14">
         <f>IF(C9="","",ROUND((F9+G9)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="9">
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="14">
         <f>IF(C9="","",F9+G9+H9-I9-J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="4" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="9">
+      <c r="B10" s="9" t="n"/>
+      <c r="C10" s="13" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="14">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="14">
         <f>IF(C10="","",E10*(C10/8)*2)</f>
         <v/>
       </c>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="9">
+      <c r="H10" s="13" t="n"/>
+      <c r="I10" s="14">
         <f>IF(C10="","",ROUND((F10+G10)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="9">
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="14">
         <f>IF(C10="","",F10+G10+H10-I10-J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="4" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="9">
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="13" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="14">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="14">
         <f>IF(C11="","",E11*(C11/8)*2)</f>
         <v/>
       </c>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="9">
+      <c r="H11" s="13" t="n"/>
+      <c r="I11" s="14">
         <f>IF(C11="","",ROUND((F11+G11)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="9">
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="14">
         <f>IF(C11="","",F11+G11+H11-I11-J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="9">
+      <c r="B12" s="9" t="n"/>
+      <c r="C12" s="13" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="14">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="G12" s="9">
+      <c r="G12" s="14">
         <f>IF(C12="","",E12*(C12/8)*2)</f>
         <v/>
       </c>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="9">
+      <c r="H12" s="13" t="n"/>
+      <c r="I12" s="14">
         <f>IF(C12="","",ROUND((F12+G12)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="9">
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="14">
         <f>IF(C12="","",F12+G12+H12-I12-J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="9">
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="13" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="14">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="14">
         <f>IF(C13="","",E13*(C13/8)*2)</f>
         <v/>
       </c>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="9">
+      <c r="H13" s="13" t="n"/>
+      <c r="I13" s="14">
         <f>IF(C13="","",ROUND((F13+G13)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="9">
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="14">
         <f>IF(C13="","",F13+G13+H13-I13-J13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="9">
+      <c r="B14" s="9" t="n"/>
+      <c r="C14" s="13" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="14">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="14">
         <f>IF(C14="","",E14*(C14/8)*2)</f>
         <v/>
       </c>
-      <c r="H14" s="8" t="n"/>
-      <c r="I14" s="9">
+      <c r="H14" s="13" t="n"/>
+      <c r="I14" s="14">
         <f>IF(C14="","",ROUND((F14+G14)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="n"/>
-      <c r="K14" s="9">
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="14">
         <f>IF(C14="","",F14+G14+H14-I14-J14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="9">
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="13" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="14">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="14">
         <f>IF(C15="","",E15*(C15/8)*2)</f>
         <v/>
       </c>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="9">
+      <c r="H15" s="13" t="n"/>
+      <c r="I15" s="14">
         <f>IF(C15="","",ROUND((F15+G15)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="9">
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="14">
         <f>IF(C15="","",F15+G15+H15-I15-J15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="9">
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="14">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="14">
         <f>IF(C16="","",E16*(C16/8)*2)</f>
         <v/>
       </c>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="9">
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="14">
         <f>IF(C16="","",ROUND((F16+G16)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="9">
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="14">
         <f>IF(C16="","",F16+G16+H16-I16-J16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="4" t="n"/>
-      <c r="F17" s="9">
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="13" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="14">
         <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="14">
         <f>IF(C17="","",E17*(C17/8)*2)</f>
         <v/>
       </c>
-      <c r="H17" s="8" t="n"/>
-      <c r="I17" s="9">
+      <c r="H17" s="13" t="n"/>
+      <c r="I17" s="14">
         <f>IF(C17="","",ROUND((F17+G17)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="n"/>
-      <c r="K17" s="9">
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="14">
         <f>IF(C17="","",F17+G17+H17-I17-J17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="4" t="n"/>
-      <c r="F18" s="9">
+      <c r="B18" s="9" t="n"/>
+      <c r="C18" s="13" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="14">
         <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="14">
         <f>IF(C18="","",E18*(C18/8)*2)</f>
         <v/>
       </c>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="9">
+      <c r="H18" s="13" t="n"/>
+      <c r="I18" s="14">
         <f>IF(C18="","",ROUND((F18+G18)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="9">
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="14">
         <f>IF(C18="","",F18+G18+H18-I18-J18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="4" t="n"/>
-      <c r="F19" s="9">
+      <c r="B19" s="9" t="n"/>
+      <c r="C19" s="13" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="14">
         <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
-      <c r="G19" s="9">
+      <c r="G19" s="14">
         <f>IF(C19="","",E19*(C19/8)*2)</f>
         <v/>
       </c>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="9">
+      <c r="H19" s="13" t="n"/>
+      <c r="I19" s="14">
         <f>IF(C19="","",ROUND((F19+G19)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="9">
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="14">
         <f>IF(C19="","",F19+G19+H19-I19-J19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="4" t="n"/>
-      <c r="F20" s="9">
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="13" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="14">
         <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="14">
         <f>IF(C20="","",E20*(C20/8)*2)</f>
         <v/>
       </c>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="9">
+      <c r="H20" s="13" t="n"/>
+      <c r="I20" s="14">
         <f>IF(C20="","",ROUND((F20+G20)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="n"/>
-      <c r="K20" s="9">
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="14">
         <f>IF(C20="","",F20+G20+H20-I20-J20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="9">
+      <c r="B21" s="9" t="n"/>
+      <c r="C21" s="13" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="14">
         <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
-      <c r="G21" s="9">
+      <c r="G21" s="14">
         <f>IF(C21="","",E21*(C21/8)*2)</f>
         <v/>
       </c>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="9">
+      <c r="H21" s="13" t="n"/>
+      <c r="I21" s="14">
         <f>IF(C21="","",ROUND((F21+G21)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J21" s="8" t="n"/>
-      <c r="K21" s="9">
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="14">
         <f>IF(C21="","",F21+G21+H21-I21-J21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="9">
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="13" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="14">
         <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
-      <c r="G22" s="9">
+      <c r="G22" s="14">
         <f>IF(C22="","",E22*(C22/8)*2)</f>
         <v/>
       </c>
-      <c r="H22" s="8" t="n"/>
-      <c r="I22" s="9">
+      <c r="H22" s="13" t="n"/>
+      <c r="I22" s="14">
         <f>IF(C22="","",ROUND((F22+G22)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="n"/>
-      <c r="K22" s="9">
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="14">
         <f>IF(C22="","",F22+G22+H22-I22-J22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="9">
+      <c r="B23" s="9" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="14">
         <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="14">
         <f>IF(C23="","",E23*(C23/8)*2)</f>
         <v/>
       </c>
-      <c r="H23" s="8" t="n"/>
-      <c r="I23" s="9">
+      <c r="H23" s="13" t="n"/>
+      <c r="I23" s="14">
         <f>IF(C23="","",ROUND((F23+G23)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J23" s="8" t="n"/>
-      <c r="K23" s="9">
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="14">
         <f>IF(C23="","",F23+G23+H23-I23-J23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="9">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="13" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="14">
         <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="14">
         <f>IF(C24="","",E24*(C24/8)*2)</f>
         <v/>
       </c>
-      <c r="H24" s="8" t="n"/>
-      <c r="I24" s="9">
+      <c r="H24" s="13" t="n"/>
+      <c r="I24" s="14">
         <f>IF(C24="","",ROUND((F24+G24)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J24" s="8" t="n"/>
-      <c r="K24" s="9">
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="14">
         <f>IF(C24="","",F24+G24+H24-I24-J24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="7" t="n">
+      <c r="A25" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="9">
+      <c r="B25" s="9" t="n"/>
+      <c r="C25" s="13" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="14">
         <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
-      <c r="G25" s="9">
+      <c r="G25" s="14">
         <f>IF(C25="","",E25*(C25/8)*2)</f>
         <v/>
       </c>
-      <c r="H25" s="8" t="n"/>
-      <c r="I25" s="9">
+      <c r="H25" s="13" t="n"/>
+      <c r="I25" s="14">
         <f>IF(C25="","",ROUND((F25+G25)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J25" s="8" t="n"/>
-      <c r="K25" s="9">
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="14">
         <f>IF(C25="","",F25+G25+H25-I25-J25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="7" t="n">
+      <c r="A26" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="4" t="n"/>
-      <c r="F26" s="9">
+      <c r="B26" s="9" t="n"/>
+      <c r="C26" s="13" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="14">
         <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="14">
         <f>IF(C26="","",E26*(C26/8)*2)</f>
         <v/>
       </c>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="9">
+      <c r="H26" s="13" t="n"/>
+      <c r="I26" s="14">
         <f>IF(C26="","",ROUND((F26+G26)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J26" s="8" t="n"/>
-      <c r="K26" s="9">
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="14">
         <f>IF(C26="","",F26+G26+H26-I26-J26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="n">
+      <c r="A27" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="9">
+      <c r="B27" s="9" t="n"/>
+      <c r="C27" s="13" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="14">
         <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="14">
         <f>IF(C27="","",E27*(C27/8)*2)</f>
         <v/>
       </c>
-      <c r="H27" s="8" t="n"/>
-      <c r="I27" s="9">
+      <c r="H27" s="13" t="n"/>
+      <c r="I27" s="14">
         <f>IF(C27="","",ROUND((F27+G27)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J27" s="8" t="n"/>
-      <c r="K27" s="9">
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="14">
         <f>IF(C27="","",F27+G27+H27-I27-J27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="n">
+      <c r="A28" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="9">
+      <c r="B28" s="9" t="n"/>
+      <c r="C28" s="13" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="14">
         <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="14">
         <f>IF(C28="","",E28*(C28/8)*2)</f>
         <v/>
       </c>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="9">
+      <c r="H28" s="13" t="n"/>
+      <c r="I28" s="14">
         <f>IF(C28="","",ROUND((F28+G28)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J28" s="8" t="n"/>
-      <c r="K28" s="9">
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="14">
         <f>IF(C28="","",F28+G28+H28-I28-J28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="n">
+      <c r="A29" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="9">
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="13" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="14">
         <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="14">
         <f>IF(C29="","",E29*(C29/8)*2)</f>
         <v/>
       </c>
-      <c r="H29" s="8" t="n"/>
-      <c r="I29" s="9">
+      <c r="H29" s="13" t="n"/>
+      <c r="I29" s="14">
         <f>IF(C29="","",ROUND((F29+G29)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J29" s="8" t="n"/>
-      <c r="K29" s="9">
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="14">
         <f>IF(C29="","",F29+G29+H29-I29-J29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="n">
+      <c r="A30" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="4" t="n"/>
-      <c r="F30" s="9">
+      <c r="B30" s="9" t="n"/>
+      <c r="C30" s="13" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="14">
         <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="14">
         <f>IF(C30="","",E30*(C30/8)*2)</f>
         <v/>
       </c>
-      <c r="H30" s="8" t="n"/>
-      <c r="I30" s="9">
+      <c r="H30" s="13" t="n"/>
+      <c r="I30" s="14">
         <f>IF(C30="","",ROUND((F30+G30)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J30" s="8" t="n"/>
-      <c r="K30" s="9">
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="14">
         <f>IF(C30="","",F30+G30+H30-I30-J30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="n">
+      <c r="A31" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="4" t="n"/>
-      <c r="F31" s="9">
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="13" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="14">
         <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="14">
         <f>IF(C31="","",E31*(C31/8)*2)</f>
         <v/>
       </c>
-      <c r="H31" s="8" t="n"/>
-      <c r="I31" s="9">
+      <c r="H31" s="13" t="n"/>
+      <c r="I31" s="14">
         <f>IF(C31="","",ROUND((F31+G31)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J31" s="8" t="n"/>
-      <c r="K31" s="9">
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="14">
         <f>IF(C31="","",F31+G31+H31-I31-J31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="n">
+      <c r="A32" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="9">
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="13" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="14">
         <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="14">
         <f>IF(C32="","",E32*(C32/8)*2)</f>
         <v/>
       </c>
-      <c r="H32" s="8" t="n"/>
-      <c r="I32" s="9">
+      <c r="H32" s="13" t="n"/>
+      <c r="I32" s="14">
         <f>IF(C32="","",ROUND((F32+G32)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J32" s="8" t="n"/>
-      <c r="K32" s="9">
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="14">
         <f>IF(C32="","",F32+G32+H32-I32-J32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="n">
+      <c r="A33" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="9">
+      <c r="B33" s="9" t="n"/>
+      <c r="C33" s="13" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="14">
         <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="14">
         <f>IF(C33="","",E33*(C33/8)*2)</f>
         <v/>
       </c>
-      <c r="H33" s="8" t="n"/>
-      <c r="I33" s="9">
+      <c r="H33" s="13" t="n"/>
+      <c r="I33" s="14">
         <f>IF(C33="","",ROUND((F33+G33)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J33" s="8" t="n"/>
-      <c r="K33" s="9">
+      <c r="J33" s="13" t="n"/>
+      <c r="K33" s="14">
         <f>IF(C33="","",F33+G33+H33-I33-J33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="n">
+      <c r="A34" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="4" t="n"/>
-      <c r="F34" s="9">
+      <c r="B34" s="9" t="n"/>
+      <c r="C34" s="13" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="14">
         <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="14">
         <f>IF(C34="","",E34*(C34/8)*2)</f>
         <v/>
       </c>
-      <c r="H34" s="8" t="n"/>
-      <c r="I34" s="9">
+      <c r="H34" s="13" t="n"/>
+      <c r="I34" s="14">
         <f>IF(C34="","",ROUND((F34+G34)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J34" s="8" t="n"/>
-      <c r="K34" s="9">
+      <c r="J34" s="13" t="n"/>
+      <c r="K34" s="14">
         <f>IF(C34="","",F34+G34+H34-I34-J34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="n">
+      <c r="A35" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="9">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="13" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="14">
         <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="14">
         <f>IF(C35="","",E35*(C35/8)*2)</f>
         <v/>
       </c>
-      <c r="H35" s="8" t="n"/>
-      <c r="I35" s="9">
+      <c r="H35" s="13" t="n"/>
+      <c r="I35" s="14">
         <f>IF(C35="","",ROUND((F35+G35)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J35" s="8" t="n"/>
-      <c r="K35" s="9">
+      <c r="J35" s="13" t="n"/>
+      <c r="K35" s="14">
         <f>IF(C35="","",F35+G35+H35-I35-J35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="n">
+      <c r="A36" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="4" t="n"/>
-      <c r="F36" s="9">
+      <c r="B36" s="9" t="n"/>
+      <c r="C36" s="13" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="14">
         <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="14">
         <f>IF(C36="","",E36*(C36/8)*2)</f>
         <v/>
       </c>
-      <c r="H36" s="8" t="n"/>
-      <c r="I36" s="9">
+      <c r="H36" s="13" t="n"/>
+      <c r="I36" s="14">
         <f>IF(C36="","",ROUND((F36+G36)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J36" s="8" t="n"/>
-      <c r="K36" s="9">
+      <c r="J36" s="13" t="n"/>
+      <c r="K36" s="14">
         <f>IF(C36="","",F36+G36+H36-I36-J36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="n">
+      <c r="A37" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="8" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="4" t="n"/>
-      <c r="F37" s="9">
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="13" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="14">
         <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="14">
         <f>IF(C37="","",E37*(C37/8)*2)</f>
         <v/>
       </c>
-      <c r="H37" s="8" t="n"/>
-      <c r="I37" s="9">
+      <c r="H37" s="13" t="n"/>
+      <c r="I37" s="14">
         <f>IF(C37="","",ROUND((F37+G37)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J37" s="8" t="n"/>
-      <c r="K37" s="9">
+      <c r="J37" s="13" t="n"/>
+      <c r="K37" s="14">
         <f>IF(C37="","",F37+G37+H37-I37-J37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="10" t="inlineStr">
+      <c r="E38" s="15" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="16">
         <f>SUM(F8:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="11">
+      <c r="G38" s="16">
         <f>SUM(G8:G37)</f>
         <v/>
       </c>
-      <c r="H38" s="11">
+      <c r="H38" s="16">
         <f>SUM(H8:H37)</f>
         <v/>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="16">
         <f>SUM(I8:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="11">
+      <c r="J38" s="16">
         <f>SUM(J8:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="11">
+      <c r="K38" s="16">
         <f>SUM(K8:K37)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
+      <c r="A41" s="17" t="n"/>
+      <c r="B41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="G41" s="17" t="n"/>
+      <c r="H41" s="17" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="13" t="inlineStr">
+      <c r="A42" s="18" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="D42" s="13" t="inlineStr">
+      <c r="D42" s="18" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
-      <c r="G42" s="13" t="inlineStr">
+      <c r="G42" s="18" t="inlineStr">
         <is>
           <t>Autorizó</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="B5:D5"/>
+    <mergeCell ref="A2:I2"/>
     <mergeCell ref="D42:E42"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="A41:B41"/>
     <mergeCell ref="G42:H42"/>
     <mergeCell ref="B4:D4"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:I1"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="G4:I4"/>
+    <mergeCell ref="J1:K2"/>
     <mergeCell ref="D41:E41"/>
-    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1532,7 +1594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1540,71 +1602,81 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="19" t="inlineStr">
         <is>
           <t>Nómina simplificada</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t>Guía de uso</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="18" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
         </is>

--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,35 +32,82 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="18"/>
+      <sz val="20"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
-      <color rgb="00595959"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001B6B73"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
-      <sz val="16"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001F4E78"/>
+      <color rgb="000B2A4A"/>
     </font>
     <font>
-      <i val="1"/>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="26"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="002B2B2B"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008A97A3"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="6">
@@ -72,31 +119,45 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="000B2A4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E6ECF1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF9E5"/>
+        <fgColor rgb="00FFFCF0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
+        <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00C9A227"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -133,64 +194,83 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="00C9D3DB"/>
       </bottom>
     </border>
     <border>
       <bottom style="thin"/>
     </border>
+    <border>
+      <top style="thick">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -553,6 +633,200 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="5" customWidth="1" min="2" max="2"/>
+    <col width="88" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+      <c r="D3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="1" t="n"/>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Nómina simplificada</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n"/>
+      <c r="D4" s="1" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Formato administrativo editable · México</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n"/>
+      <c r="D5" s="1" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="1" t="n"/>
+      <c r="C6" s="1" t="n"/>
+      <c r="D6" s="1" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="1" t="n"/>
+      <c r="C7" s="1" t="n"/>
+      <c r="D7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="6" customHeight="1">
+      <c r="A8" s="5" t="n"/>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>CÓMO USARLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="21" customHeight="1">
+      <c r="B11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="B12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C12" s="8" t="inlineStr">
+        <is>
+          <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="B13" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="B15" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="B16" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>LEYENDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="9" t="inlineStr"/>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Celda de captura: escribe aquí.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="11" t="inlineStr"/>
+      <c r="C20" s="10" t="inlineStr">
+        <is>
+          <t>Cálculo automático: no la modifiques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="12" t="inlineStr"/>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>Encabezados y títulos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="13" t="n"/>
+      <c r="C23" s="13" t="n"/>
+      <c r="D23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="000B2A4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -572,39 +846,47 @@
     <col width="16" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>NÓMINA SIMPLIFICADA</t>
         </is>
       </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="2" t="n"/>
-      <c r="D1" s="2" t="n"/>
-      <c r="E1" s="2" t="n"/>
-      <c r="F1" s="2" t="n"/>
-      <c r="G1" s="2" t="n"/>
-      <c r="H1" s="2" t="n"/>
-      <c r="I1" s="2" t="n"/>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="16" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="K1" s="4" t="n"/>
-    </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="K1" s="17" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="18" t="inlineStr">
         <is>
           <t>Cálculo estimado por periodo (referencia administrativa, no sustituye cálculo fiscal)</t>
         </is>
       </c>
-      <c r="J2" s="6" t="n"/>
-      <c r="K2" s="7" t="n"/>
+      <c r="B2" s="19" t="n"/>
+      <c r="C2" s="19" t="n"/>
+      <c r="D2" s="19" t="n"/>
+      <c r="E2" s="19" t="n"/>
+      <c r="F2" s="19" t="n"/>
+      <c r="G2" s="19" t="n"/>
+      <c r="H2" s="19" t="n"/>
+      <c r="I2" s="19" t="n"/>
+      <c r="J2" s="20" t="n"/>
+      <c r="K2" s="21" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="22" t="inlineStr">
         <is>
           <t>Empresa</t>
         </is>
@@ -612,7 +894,7 @@
       <c r="B4" s="9" t="n"/>
       <c r="C4" s="9" t="n"/>
       <c r="D4" s="9" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>Periodo</t>
         </is>
@@ -622,7 +904,7 @@
       <c r="I4" s="9" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
         <is>
           <t>Días del periodo</t>
         </is>
@@ -632,935 +914,935 @@
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>% retención IMSS (est.)</t>
         </is>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="23" t="n">
         <v>0.0275</v>
       </c>
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
     </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Empleado</t>
         </is>
       </c>
-      <c r="C7" s="11" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Sueldo diario</t>
         </is>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Días trab.</t>
         </is>
       </c>
-      <c r="E7" s="11" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>Horas extra</t>
         </is>
       </c>
-      <c r="F7" s="11" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>Sueldo</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>Pago horas extra</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr">
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>Bonos / otros</t>
         </is>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>Retención IMSS</t>
         </is>
       </c>
-      <c r="J7" s="11" t="inlineStr">
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t>ISR retenido</t>
         </is>
       </c>
-      <c r="K7" s="11" t="inlineStr">
+      <c r="K7" s="24" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="n"/>
-      <c r="C8" s="13" t="n"/>
+      <c r="C8" s="25" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
-      <c r="F8" s="14">
+      <c r="F8" s="26">
         <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="26">
         <f>IF(C8="","",E8*(C8/8)*2)</f>
         <v/>
       </c>
-      <c r="H8" s="13" t="n"/>
-      <c r="I8" s="14">
+      <c r="H8" s="25" t="n"/>
+      <c r="I8" s="26">
         <f>IF(C8="","",ROUND((F8+G8)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="14">
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="26">
         <f>IF(C8="","",F8+G8+H8-I8-J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="11" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="13" t="n"/>
+      <c r="C9" s="25" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
-      <c r="F9" s="14">
+      <c r="F9" s="26">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="26">
         <f>IF(C9="","",E9*(C9/8)*2)</f>
         <v/>
       </c>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="14">
+      <c r="H9" s="25" t="n"/>
+      <c r="I9" s="26">
         <f>IF(C9="","",ROUND((F9+G9)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="14">
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="26">
         <f>IF(C9="","",F9+G9+H9-I9-J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n">
+      <c r="A10" s="11" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="13" t="n"/>
+      <c r="C10" s="25" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
-      <c r="F10" s="14">
+      <c r="F10" s="26">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="26">
         <f>IF(C10="","",E10*(C10/8)*2)</f>
         <v/>
       </c>
-      <c r="H10" s="13" t="n"/>
-      <c r="I10" s="14">
+      <c r="H10" s="25" t="n"/>
+      <c r="I10" s="26">
         <f>IF(C10="","",ROUND((F10+G10)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="14">
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="26">
         <f>IF(C10="","",F10+G10+H10-I10-J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n">
+      <c r="A11" s="11" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="13" t="n"/>
+      <c r="C11" s="25" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="14">
+      <c r="F11" s="26">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="26">
         <f>IF(C11="","",E11*(C11/8)*2)</f>
         <v/>
       </c>
-      <c r="H11" s="13" t="n"/>
-      <c r="I11" s="14">
+      <c r="H11" s="25" t="n"/>
+      <c r="I11" s="26">
         <f>IF(C11="","",ROUND((F11+G11)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="14">
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="26">
         <f>IF(C11="","",F11+G11+H11-I11-J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n">
+      <c r="A12" s="11" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="13" t="n"/>
+      <c r="C12" s="25" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
-      <c r="F12" s="14">
+      <c r="F12" s="26">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="26">
         <f>IF(C12="","",E12*(C12/8)*2)</f>
         <v/>
       </c>
-      <c r="H12" s="13" t="n"/>
-      <c r="I12" s="14">
+      <c r="H12" s="25" t="n"/>
+      <c r="I12" s="26">
         <f>IF(C12="","",ROUND((F12+G12)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="14">
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="26">
         <f>IF(C12="","",F12+G12+H12-I12-J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n">
+      <c r="A13" s="11" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="13" t="n"/>
+      <c r="C13" s="25" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="14">
+      <c r="F13" s="26">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="26">
         <f>IF(C13="","",E13*(C13/8)*2)</f>
         <v/>
       </c>
-      <c r="H13" s="13" t="n"/>
-      <c r="I13" s="14">
+      <c r="H13" s="25" t="n"/>
+      <c r="I13" s="26">
         <f>IF(C13="","",ROUND((F13+G13)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="14">
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="26">
         <f>IF(C13="","",F13+G13+H13-I13-J13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n">
+      <c r="A14" s="11" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="13" t="n"/>
+      <c r="C14" s="25" t="n"/>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
-      <c r="F14" s="14">
+      <c r="F14" s="26">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="26">
         <f>IF(C14="","",E14*(C14/8)*2)</f>
         <v/>
       </c>
-      <c r="H14" s="13" t="n"/>
-      <c r="I14" s="14">
+      <c r="H14" s="25" t="n"/>
+      <c r="I14" s="26">
         <f>IF(C14="","",ROUND((F14+G14)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="14">
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="26">
         <f>IF(C14="","",F14+G14+H14-I14-J14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n">
+      <c r="A15" s="11" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="13" t="n"/>
+      <c r="C15" s="25" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="14">
+      <c r="F15" s="26">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="26">
         <f>IF(C15="","",E15*(C15/8)*2)</f>
         <v/>
       </c>
-      <c r="H15" s="13" t="n"/>
-      <c r="I15" s="14">
+      <c r="H15" s="25" t="n"/>
+      <c r="I15" s="26">
         <f>IF(C15="","",ROUND((F15+G15)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="14">
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="26">
         <f>IF(C15="","",F15+G15+H15-I15-J15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n">
+      <c r="A16" s="11" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="13" t="n"/>
+      <c r="C16" s="25" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="14">
+      <c r="F16" s="26">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="26">
         <f>IF(C16="","",E16*(C16/8)*2)</f>
         <v/>
       </c>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="14">
+      <c r="H16" s="25" t="n"/>
+      <c r="I16" s="26">
         <f>IF(C16="","",ROUND((F16+G16)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="14">
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="26">
         <f>IF(C16="","",F16+G16+H16-I16-J16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n">
+      <c r="A17" s="11" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="n"/>
-      <c r="C17" s="13" t="n"/>
+      <c r="C17" s="25" t="n"/>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
-      <c r="F17" s="14">
+      <c r="F17" s="26">
         <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="26">
         <f>IF(C17="","",E17*(C17/8)*2)</f>
         <v/>
       </c>
-      <c r="H17" s="13" t="n"/>
-      <c r="I17" s="14">
+      <c r="H17" s="25" t="n"/>
+      <c r="I17" s="26">
         <f>IF(C17="","",ROUND((F17+G17)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="14">
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="26">
         <f>IF(C17="","",F17+G17+H17-I17-J17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n">
+      <c r="A18" s="11" t="n">
         <v>11</v>
       </c>
       <c r="B18" s="9" t="n"/>
-      <c r="C18" s="13" t="n"/>
+      <c r="C18" s="25" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="14">
+      <c r="F18" s="26">
         <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="26">
         <f>IF(C18="","",E18*(C18/8)*2)</f>
         <v/>
       </c>
-      <c r="H18" s="13" t="n"/>
-      <c r="I18" s="14">
+      <c r="H18" s="25" t="n"/>
+      <c r="I18" s="26">
         <f>IF(C18="","",ROUND((F18+G18)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="14">
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="26">
         <f>IF(C18="","",F18+G18+H18-I18-J18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n">
+      <c r="A19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="n"/>
-      <c r="C19" s="13" t="n"/>
+      <c r="C19" s="25" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="14">
+      <c r="F19" s="26">
         <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="26">
         <f>IF(C19="","",E19*(C19/8)*2)</f>
         <v/>
       </c>
-      <c r="H19" s="13" t="n"/>
-      <c r="I19" s="14">
+      <c r="H19" s="25" t="n"/>
+      <c r="I19" s="26">
         <f>IF(C19="","",ROUND((F19+G19)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="14">
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="26">
         <f>IF(C19="","",F19+G19+H19-I19-J19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n">
+      <c r="A20" s="11" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="9" t="n"/>
-      <c r="C20" s="13" t="n"/>
+      <c r="C20" s="25" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="14">
+      <c r="F20" s="26">
         <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="26">
         <f>IF(C20="","",E20*(C20/8)*2)</f>
         <v/>
       </c>
-      <c r="H20" s="13" t="n"/>
-      <c r="I20" s="14">
+      <c r="H20" s="25" t="n"/>
+      <c r="I20" s="26">
         <f>IF(C20="","",ROUND((F20+G20)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J20" s="13" t="n"/>
-      <c r="K20" s="14">
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="26">
         <f>IF(C20="","",F20+G20+H20-I20-J20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n">
+      <c r="A21" s="11" t="n">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="n"/>
-      <c r="C21" s="13" t="n"/>
+      <c r="C21" s="25" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="14">
+      <c r="F21" s="26">
         <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="26">
         <f>IF(C21="","",E21*(C21/8)*2)</f>
         <v/>
       </c>
-      <c r="H21" s="13" t="n"/>
-      <c r="I21" s="14">
+      <c r="H21" s="25" t="n"/>
+      <c r="I21" s="26">
         <f>IF(C21="","",ROUND((F21+G21)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J21" s="13" t="n"/>
-      <c r="K21" s="14">
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="26">
         <f>IF(C21="","",F21+G21+H21-I21-J21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n">
+      <c r="A22" s="11" t="n">
         <v>15</v>
       </c>
       <c r="B22" s="9" t="n"/>
-      <c r="C22" s="13" t="n"/>
+      <c r="C22" s="25" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="14">
+      <c r="F22" s="26">
         <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="26">
         <f>IF(C22="","",E22*(C22/8)*2)</f>
         <v/>
       </c>
-      <c r="H22" s="13" t="n"/>
-      <c r="I22" s="14">
+      <c r="H22" s="25" t="n"/>
+      <c r="I22" s="26">
         <f>IF(C22="","",ROUND((F22+G22)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J22" s="13" t="n"/>
-      <c r="K22" s="14">
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="26">
         <f>IF(C22="","",F22+G22+H22-I22-J22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n">
+      <c r="A23" s="11" t="n">
         <v>16</v>
       </c>
       <c r="B23" s="9" t="n"/>
-      <c r="C23" s="13" t="n"/>
+      <c r="C23" s="25" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="14">
+      <c r="F23" s="26">
         <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="26">
         <f>IF(C23="","",E23*(C23/8)*2)</f>
         <v/>
       </c>
-      <c r="H23" s="13" t="n"/>
-      <c r="I23" s="14">
+      <c r="H23" s="25" t="n"/>
+      <c r="I23" s="26">
         <f>IF(C23="","",ROUND((F23+G23)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J23" s="13" t="n"/>
-      <c r="K23" s="14">
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="26">
         <f>IF(C23="","",F23+G23+H23-I23-J23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n">
+      <c r="A24" s="11" t="n">
         <v>17</v>
       </c>
       <c r="B24" s="9" t="n"/>
-      <c r="C24" s="13" t="n"/>
+      <c r="C24" s="25" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="14">
+      <c r="F24" s="26">
         <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="26">
         <f>IF(C24="","",E24*(C24/8)*2)</f>
         <v/>
       </c>
-      <c r="H24" s="13" t="n"/>
-      <c r="I24" s="14">
+      <c r="H24" s="25" t="n"/>
+      <c r="I24" s="26">
         <f>IF(C24="","",ROUND((F24+G24)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J24" s="13" t="n"/>
-      <c r="K24" s="14">
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="26">
         <f>IF(C24="","",F24+G24+H24-I24-J24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n">
+      <c r="A25" s="11" t="n">
         <v>18</v>
       </c>
       <c r="B25" s="9" t="n"/>
-      <c r="C25" s="13" t="n"/>
+      <c r="C25" s="25" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="14">
+      <c r="F25" s="26">
         <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="26">
         <f>IF(C25="","",E25*(C25/8)*2)</f>
         <v/>
       </c>
-      <c r="H25" s="13" t="n"/>
-      <c r="I25" s="14">
+      <c r="H25" s="25" t="n"/>
+      <c r="I25" s="26">
         <f>IF(C25="","",ROUND((F25+G25)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J25" s="13" t="n"/>
-      <c r="K25" s="14">
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="26">
         <f>IF(C25="","",F25+G25+H25-I25-J25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n">
+      <c r="A26" s="11" t="n">
         <v>19</v>
       </c>
       <c r="B26" s="9" t="n"/>
-      <c r="C26" s="13" t="n"/>
+      <c r="C26" s="25" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="14">
+      <c r="F26" s="26">
         <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="26">
         <f>IF(C26="","",E26*(C26/8)*2)</f>
         <v/>
       </c>
-      <c r="H26" s="13" t="n"/>
-      <c r="I26" s="14">
+      <c r="H26" s="25" t="n"/>
+      <c r="I26" s="26">
         <f>IF(C26="","",ROUND((F26+G26)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J26" s="13" t="n"/>
-      <c r="K26" s="14">
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="26">
         <f>IF(C26="","",F26+G26+H26-I26-J26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n">
+      <c r="A27" s="11" t="n">
         <v>20</v>
       </c>
       <c r="B27" s="9" t="n"/>
-      <c r="C27" s="13" t="n"/>
+      <c r="C27" s="25" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="14">
+      <c r="F27" s="26">
         <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="26">
         <f>IF(C27="","",E27*(C27/8)*2)</f>
         <v/>
       </c>
-      <c r="H27" s="13" t="n"/>
-      <c r="I27" s="14">
+      <c r="H27" s="25" t="n"/>
+      <c r="I27" s="26">
         <f>IF(C27="","",ROUND((F27+G27)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J27" s="13" t="n"/>
-      <c r="K27" s="14">
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="26">
         <f>IF(C27="","",F27+G27+H27-I27-J27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n">
+      <c r="A28" s="11" t="n">
         <v>21</v>
       </c>
       <c r="B28" s="9" t="n"/>
-      <c r="C28" s="13" t="n"/>
+      <c r="C28" s="25" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="14">
+      <c r="F28" s="26">
         <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="26">
         <f>IF(C28="","",E28*(C28/8)*2)</f>
         <v/>
       </c>
-      <c r="H28" s="13" t="n"/>
-      <c r="I28" s="14">
+      <c r="H28" s="25" t="n"/>
+      <c r="I28" s="26">
         <f>IF(C28="","",ROUND((F28+G28)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J28" s="13" t="n"/>
-      <c r="K28" s="14">
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="26">
         <f>IF(C28="","",F28+G28+H28-I28-J28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n">
+      <c r="A29" s="11" t="n">
         <v>22</v>
       </c>
       <c r="B29" s="9" t="n"/>
-      <c r="C29" s="13" t="n"/>
+      <c r="C29" s="25" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="14">
+      <c r="F29" s="26">
         <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="26">
         <f>IF(C29="","",E29*(C29/8)*2)</f>
         <v/>
       </c>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="14">
+      <c r="H29" s="25" t="n"/>
+      <c r="I29" s="26">
         <f>IF(C29="","",ROUND((F29+G29)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="14">
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="26">
         <f>IF(C29="","",F29+G29+H29-I29-J29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n">
+      <c r="A30" s="11" t="n">
         <v>23</v>
       </c>
       <c r="B30" s="9" t="n"/>
-      <c r="C30" s="13" t="n"/>
+      <c r="C30" s="25" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="14">
+      <c r="F30" s="26">
         <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="26">
         <f>IF(C30="","",E30*(C30/8)*2)</f>
         <v/>
       </c>
-      <c r="H30" s="13" t="n"/>
-      <c r="I30" s="14">
+      <c r="H30" s="25" t="n"/>
+      <c r="I30" s="26">
         <f>IF(C30="","",ROUND((F30+G30)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J30" s="13" t="n"/>
-      <c r="K30" s="14">
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="26">
         <f>IF(C30="","",F30+G30+H30-I30-J30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n">
+      <c r="A31" s="11" t="n">
         <v>24</v>
       </c>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="13" t="n"/>
+      <c r="C31" s="25" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
-      <c r="F31" s="14">
+      <c r="F31" s="26">
         <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="26">
         <f>IF(C31="","",E31*(C31/8)*2)</f>
         <v/>
       </c>
-      <c r="H31" s="13" t="n"/>
-      <c r="I31" s="14">
+      <c r="H31" s="25" t="n"/>
+      <c r="I31" s="26">
         <f>IF(C31="","",ROUND((F31+G31)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J31" s="13" t="n"/>
-      <c r="K31" s="14">
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="26">
         <f>IF(C31="","",F31+G31+H31-I31-J31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n">
+      <c r="A32" s="11" t="n">
         <v>25</v>
       </c>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="13" t="n"/>
+      <c r="C32" s="25" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="14">
+      <c r="F32" s="26">
         <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="26">
         <f>IF(C32="","",E32*(C32/8)*2)</f>
         <v/>
       </c>
-      <c r="H32" s="13" t="n"/>
-      <c r="I32" s="14">
+      <c r="H32" s="25" t="n"/>
+      <c r="I32" s="26">
         <f>IF(C32="","",ROUND((F32+G32)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J32" s="13" t="n"/>
-      <c r="K32" s="14">
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="26">
         <f>IF(C32="","",F32+G32+H32-I32-J32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n">
+      <c r="A33" s="11" t="n">
         <v>26</v>
       </c>
       <c r="B33" s="9" t="n"/>
-      <c r="C33" s="13" t="n"/>
+      <c r="C33" s="25" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
-      <c r="F33" s="14">
+      <c r="F33" s="26">
         <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="26">
         <f>IF(C33="","",E33*(C33/8)*2)</f>
         <v/>
       </c>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="14">
+      <c r="H33" s="25" t="n"/>
+      <c r="I33" s="26">
         <f>IF(C33="","",ROUND((F33+G33)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="14">
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="26">
         <f>IF(C33="","",F33+G33+H33-I33-J33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n">
+      <c r="A34" s="11" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="9" t="n"/>
-      <c r="C34" s="13" t="n"/>
+      <c r="C34" s="25" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="14">
+      <c r="F34" s="26">
         <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="26">
         <f>IF(C34="","",E34*(C34/8)*2)</f>
         <v/>
       </c>
-      <c r="H34" s="13" t="n"/>
-      <c r="I34" s="14">
+      <c r="H34" s="25" t="n"/>
+      <c r="I34" s="26">
         <f>IF(C34="","",ROUND((F34+G34)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="14">
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="26">
         <f>IF(C34="","",F34+G34+H34-I34-J34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n">
+      <c r="A35" s="11" t="n">
         <v>28</v>
       </c>
       <c r="B35" s="9" t="n"/>
-      <c r="C35" s="13" t="n"/>
+      <c r="C35" s="25" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
-      <c r="F35" s="14">
+      <c r="F35" s="26">
         <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="26">
         <f>IF(C35="","",E35*(C35/8)*2)</f>
         <v/>
       </c>
-      <c r="H35" s="13" t="n"/>
-      <c r="I35" s="14">
+      <c r="H35" s="25" t="n"/>
+      <c r="I35" s="26">
         <f>IF(C35="","",ROUND((F35+G35)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J35" s="13" t="n"/>
-      <c r="K35" s="14">
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="26">
         <f>IF(C35="","",F35+G35+H35-I35-J35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="n">
+      <c r="A36" s="11" t="n">
         <v>29</v>
       </c>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="13" t="n"/>
+      <c r="C36" s="25" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="14">
+      <c r="F36" s="26">
         <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="26">
         <f>IF(C36="","",E36*(C36/8)*2)</f>
         <v/>
       </c>
-      <c r="H36" s="13" t="n"/>
-      <c r="I36" s="14">
+      <c r="H36" s="25" t="n"/>
+      <c r="I36" s="26">
         <f>IF(C36="","",ROUND((F36+G36)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J36" s="13" t="n"/>
-      <c r="K36" s="14">
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="26">
         <f>IF(C36="","",F36+G36+H36-I36-J36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n">
+      <c r="A37" s="11" t="n">
         <v>30</v>
       </c>
       <c r="B37" s="9" t="n"/>
-      <c r="C37" s="13" t="n"/>
+      <c r="C37" s="25" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="14">
+      <c r="F37" s="26">
         <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="26">
         <f>IF(C37="","",E37*(C37/8)*2)</f>
         <v/>
       </c>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="14">
+      <c r="H37" s="25" t="n"/>
+      <c r="I37" s="26">
         <f>IF(C37="","",ROUND((F37+G37)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="14">
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="26">
         <f>IF(C37="","",F37+G37+H37-I37-J37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="15" t="inlineStr">
+      <c r="E38" s="27" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F38" s="16">
+      <c r="F38" s="28">
         <f>SUM(F8:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="28">
         <f>SUM(G8:G37)</f>
         <v/>
       </c>
-      <c r="H38" s="16">
+      <c r="H38" s="28">
         <f>SUM(H8:H37)</f>
         <v/>
       </c>
-      <c r="I38" s="16">
+      <c r="I38" s="28">
         <f>SUM(I8:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="16">
+      <c r="J38" s="28">
         <f>SUM(J8:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="16">
+      <c r="K38" s="28">
         <f>SUM(K8:K37)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="n"/>
-      <c r="B41" s="17" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="G41" s="17" t="n"/>
-      <c r="H41" s="17" t="n"/>
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="29" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="29" t="n"/>
+      <c r="G41" s="29" t="n"/>
+      <c r="H41" s="29" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D42" s="30" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
-      <c r="G42" s="18" t="inlineStr">
+      <c r="G42" s="30" t="inlineStr">
         <is>
           <t>Autorizó</t>
         </is>
@@ -1584,105 +1866,14 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="19" t="inlineStr">
-        <is>
-          <t>Nómina simplificada</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="20" t="inlineStr">
-        <is>
-          <t>Guía de uso</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="21" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="22" t="inlineStr">
-        <is>
-          <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="22" t="inlineStr">
-        <is>
-          <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="21" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="22" t="inlineStr">
-        <is>
-          <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="22" t="inlineStr">
-        <is>
-          <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="21" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="22" t="inlineStr">
-        <is>
-          <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="21" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas amarillas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>Celdas amarillas = captura · Celdas grises = cálculo automático (no modificar).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -223,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -237,7 +237,9 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -257,11 +259,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -706,6 +715,7 @@
       <c r="C8" s="5" t="n"/>
       <c r="D8" s="5" t="n"/>
     </row>
+    <row r="9"/>
     <row r="10">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -773,6 +783,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
@@ -804,6 +815,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="13" t="n"/>
@@ -818,6 +830,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -885,6 +898,7 @@
       <c r="J2" s="20" t="n"/>
       <c r="K2" s="21" t="n"/>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="22" t="inlineStr">
         <is>
@@ -925,6 +939,7 @@
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" s="24" t="inlineStr">
         <is>
@@ -983,872 +998,875 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="n">
+      <c r="A8" s="25" t="n">
         <v>1</v>
       </c>
       <c r="B8" s="9" t="n"/>
-      <c r="C8" s="25" t="n"/>
+      <c r="C8" s="26" t="n"/>
       <c r="D8" s="9" t="n"/>
       <c r="E8" s="9" t="n"/>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>IF(C8="","",E8*(C8/8)*2)</f>
         <v/>
       </c>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="26">
+      <c r="H8" s="26" t="n"/>
+      <c r="I8" s="27">
         <f>IF(C8="","",ROUND((F8+G8)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="26">
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="27">
         <f>IF(C8="","",F8+G8+H8-I8-J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="n">
+      <c r="A9" s="25" t="n">
         <v>2</v>
       </c>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="25" t="n"/>
+      <c r="C9" s="26" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
-      <c r="F9" s="26">
+      <c r="F9" s="27">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="27">
         <f>IF(C9="","",E9*(C9/8)*2)</f>
         <v/>
       </c>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="26">
+      <c r="H9" s="26" t="n"/>
+      <c r="I9" s="27">
         <f>IF(C9="","",ROUND((F9+G9)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="26">
+      <c r="J9" s="26" t="n"/>
+      <c r="K9" s="27">
         <f>IF(C9="","",F9+G9+H9-I9-J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="n">
+      <c r="A10" s="25" t="n">
         <v>3</v>
       </c>
       <c r="B10" s="9" t="n"/>
-      <c r="C10" s="25" t="n"/>
+      <c r="C10" s="26" t="n"/>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="9" t="n"/>
-      <c r="F10" s="26">
+      <c r="F10" s="27">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="27">
         <f>IF(C10="","",E10*(C10/8)*2)</f>
         <v/>
       </c>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="26">
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="27">
         <f>IF(C10="","",ROUND((F10+G10)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="26">
+      <c r="J10" s="26" t="n"/>
+      <c r="K10" s="27">
         <f>IF(C10="","",F10+G10+H10-I10-J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="n">
+      <c r="A11" s="25" t="n">
         <v>4</v>
       </c>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="25" t="n"/>
+      <c r="C11" s="26" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="27">
         <f>IF(C11="","",E11*(C11/8)*2)</f>
         <v/>
       </c>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="26">
+      <c r="H11" s="26" t="n"/>
+      <c r="I11" s="27">
         <f>IF(C11="","",ROUND((F11+G11)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="26">
+      <c r="J11" s="26" t="n"/>
+      <c r="K11" s="27">
         <f>IF(C11="","",F11+G11+H11-I11-J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n">
+      <c r="A12" s="25" t="n">
         <v>5</v>
       </c>
       <c r="B12" s="9" t="n"/>
-      <c r="C12" s="25" t="n"/>
+      <c r="C12" s="26" t="n"/>
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="27">
         <f>IF(C12="","",E12*(C12/8)*2)</f>
         <v/>
       </c>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="26">
+      <c r="H12" s="26" t="n"/>
+      <c r="I12" s="27">
         <f>IF(C12="","",ROUND((F12+G12)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="26">
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="27">
         <f>IF(C12="","",F12+G12+H12-I12-J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n">
+      <c r="A13" s="25" t="n">
         <v>6</v>
       </c>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="25" t="n"/>
+      <c r="C13" s="26" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>IF(C13="","",E13*(C13/8)*2)</f>
         <v/>
       </c>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="26">
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="27">
         <f>IF(C13="","",ROUND((F13+G13)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="26">
+      <c r="J13" s="26" t="n"/>
+      <c r="K13" s="27">
         <f>IF(C13="","",F13+G13+H13-I13-J13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n">
+      <c r="A14" s="25" t="n">
         <v>7</v>
       </c>
       <c r="B14" s="9" t="n"/>
-      <c r="C14" s="25" t="n"/>
+      <c r="C14" s="26" t="n"/>
       <c r="D14" s="9" t="n"/>
       <c r="E14" s="9" t="n"/>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>IF(C14="","",E14*(C14/8)*2)</f>
         <v/>
       </c>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="26">
+      <c r="H14" s="26" t="n"/>
+      <c r="I14" s="27">
         <f>IF(C14="","",ROUND((F14+G14)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="26">
+      <c r="J14" s="26" t="n"/>
+      <c r="K14" s="27">
         <f>IF(C14="","",F14+G14+H14-I14-J14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="n">
+      <c r="A15" s="25" t="n">
         <v>8</v>
       </c>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="25" t="n"/>
+      <c r="C15" s="26" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="26">
+      <c r="F15" s="27">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="G15" s="26">
+      <c r="G15" s="27">
         <f>IF(C15="","",E15*(C15/8)*2)</f>
         <v/>
       </c>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="26">
+      <c r="H15" s="26" t="n"/>
+      <c r="I15" s="27">
         <f>IF(C15="","",ROUND((F15+G15)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="26">
+      <c r="J15" s="26" t="n"/>
+      <c r="K15" s="27">
         <f>IF(C15="","",F15+G15+H15-I15-J15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="n">
+      <c r="A16" s="25" t="n">
         <v>9</v>
       </c>
       <c r="B16" s="9" t="n"/>
-      <c r="C16" s="25" t="n"/>
+      <c r="C16" s="26" t="n"/>
       <c r="D16" s="9" t="n"/>
       <c r="E16" s="9" t="n"/>
-      <c r="F16" s="26">
+      <c r="F16" s="27">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="27">
         <f>IF(C16="","",E16*(C16/8)*2)</f>
         <v/>
       </c>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="26">
+      <c r="H16" s="26" t="n"/>
+      <c r="I16" s="27">
         <f>IF(C16="","",ROUND((F16+G16)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="26">
+      <c r="J16" s="26" t="n"/>
+      <c r="K16" s="27">
         <f>IF(C16="","",F16+G16+H16-I16-J16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="n">
+      <c r="A17" s="25" t="n">
         <v>10</v>
       </c>
       <c r="B17" s="9" t="n"/>
-      <c r="C17" s="25" t="n"/>
+      <c r="C17" s="26" t="n"/>
       <c r="D17" s="9" t="n"/>
       <c r="E17" s="9" t="n"/>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
-      <c r="G17" s="26">
+      <c r="G17" s="27">
         <f>IF(C17="","",E17*(C17/8)*2)</f>
         <v/>
       </c>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="26">
+      <c r="H17" s="26" t="n"/>
+      <c r="I17" s="27">
         <f>IF(C17="","",ROUND((F17+G17)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="26">
+      <c r="J17" s="26" t="n"/>
+      <c r="K17" s="27">
         <f>IF(C17="","",F17+G17+H17-I17-J17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n">
+      <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
       <c r="B18" s="9" t="n"/>
-      <c r="C18" s="25" t="n"/>
+      <c r="C18" s="26" t="n"/>
       <c r="D18" s="9" t="n"/>
       <c r="E18" s="9" t="n"/>
-      <c r="F18" s="26">
+      <c r="F18" s="27">
         <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
-      <c r="G18" s="26">
+      <c r="G18" s="27">
         <f>IF(C18="","",E18*(C18/8)*2)</f>
         <v/>
       </c>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="26">
+      <c r="H18" s="26" t="n"/>
+      <c r="I18" s="27">
         <f>IF(C18="","",ROUND((F18+G18)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="26">
+      <c r="J18" s="26" t="n"/>
+      <c r="K18" s="27">
         <f>IF(C18="","",F18+G18+H18-I18-J18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="n">
+      <c r="A19" s="25" t="n">
         <v>12</v>
       </c>
       <c r="B19" s="9" t="n"/>
-      <c r="C19" s="25" t="n"/>
+      <c r="C19" s="26" t="n"/>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
-      <c r="F19" s="26">
+      <c r="F19" s="27">
         <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
-      <c r="G19" s="26">
+      <c r="G19" s="27">
         <f>IF(C19="","",E19*(C19/8)*2)</f>
         <v/>
       </c>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="26">
+      <c r="H19" s="26" t="n"/>
+      <c r="I19" s="27">
         <f>IF(C19="","",ROUND((F19+G19)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="26">
+      <c r="J19" s="26" t="n"/>
+      <c r="K19" s="27">
         <f>IF(C19="","",F19+G19+H19-I19-J19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="n">
+      <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
       <c r="B20" s="9" t="n"/>
-      <c r="C20" s="25" t="n"/>
+      <c r="C20" s="26" t="n"/>
       <c r="D20" s="9" t="n"/>
       <c r="E20" s="9" t="n"/>
-      <c r="F20" s="26">
+      <c r="F20" s="27">
         <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="27">
         <f>IF(C20="","",E20*(C20/8)*2)</f>
         <v/>
       </c>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="26">
+      <c r="H20" s="26" t="n"/>
+      <c r="I20" s="27">
         <f>IF(C20="","",ROUND((F20+G20)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="26">
+      <c r="J20" s="26" t="n"/>
+      <c r="K20" s="27">
         <f>IF(C20="","",F20+G20+H20-I20-J20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="n">
+      <c r="A21" s="25" t="n">
         <v>14</v>
       </c>
       <c r="B21" s="9" t="n"/>
-      <c r="C21" s="25" t="n"/>
+      <c r="C21" s="26" t="n"/>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
-      <c r="F21" s="26">
+      <c r="F21" s="27">
         <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="27">
         <f>IF(C21="","",E21*(C21/8)*2)</f>
         <v/>
       </c>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="26">
+      <c r="H21" s="26" t="n"/>
+      <c r="I21" s="27">
         <f>IF(C21="","",ROUND((F21+G21)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="26">
+      <c r="J21" s="26" t="n"/>
+      <c r="K21" s="27">
         <f>IF(C21="","",F21+G21+H21-I21-J21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="n">
+      <c r="A22" s="25" t="n">
         <v>15</v>
       </c>
       <c r="B22" s="9" t="n"/>
-      <c r="C22" s="25" t="n"/>
+      <c r="C22" s="26" t="n"/>
       <c r="D22" s="9" t="n"/>
       <c r="E22" s="9" t="n"/>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="27">
         <f>IF(C22="","",E22*(C22/8)*2)</f>
         <v/>
       </c>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="26">
+      <c r="H22" s="26" t="n"/>
+      <c r="I22" s="27">
         <f>IF(C22="","",ROUND((F22+G22)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="26">
+      <c r="J22" s="26" t="n"/>
+      <c r="K22" s="27">
         <f>IF(C22="","",F22+G22+H22-I22-J22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="25" t="n">
         <v>16</v>
       </c>
       <c r="B23" s="9" t="n"/>
-      <c r="C23" s="25" t="n"/>
+      <c r="C23" s="26" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
-      <c r="F23" s="26">
+      <c r="F23" s="27">
         <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="27">
         <f>IF(C23="","",E23*(C23/8)*2)</f>
         <v/>
       </c>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="26">
+      <c r="H23" s="26" t="n"/>
+      <c r="I23" s="27">
         <f>IF(C23="","",ROUND((F23+G23)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="26">
+      <c r="J23" s="26" t="n"/>
+      <c r="K23" s="27">
         <f>IF(C23="","",F23+G23+H23-I23-J23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="n">
+      <c r="A24" s="25" t="n">
         <v>17</v>
       </c>
       <c r="B24" s="9" t="n"/>
-      <c r="C24" s="25" t="n"/>
+      <c r="C24" s="26" t="n"/>
       <c r="D24" s="9" t="n"/>
       <c r="E24" s="9" t="n"/>
-      <c r="F24" s="26">
+      <c r="F24" s="27">
         <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="27">
         <f>IF(C24="","",E24*(C24/8)*2)</f>
         <v/>
       </c>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="26">
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="27">
         <f>IF(C24="","",ROUND((F24+G24)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="26">
+      <c r="J24" s="26" t="n"/>
+      <c r="K24" s="27">
         <f>IF(C24="","",F24+G24+H24-I24-J24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="n">
+      <c r="A25" s="25" t="n">
         <v>18</v>
       </c>
       <c r="B25" s="9" t="n"/>
-      <c r="C25" s="25" t="n"/>
+      <c r="C25" s="26" t="n"/>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
-      <c r="F25" s="26">
+      <c r="F25" s="27">
         <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="27">
         <f>IF(C25="","",E25*(C25/8)*2)</f>
         <v/>
       </c>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="26">
+      <c r="H25" s="26" t="n"/>
+      <c r="I25" s="27">
         <f>IF(C25="","",ROUND((F25+G25)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="26">
+      <c r="J25" s="26" t="n"/>
+      <c r="K25" s="27">
         <f>IF(C25="","",F25+G25+H25-I25-J25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="n">
+      <c r="A26" s="25" t="n">
         <v>19</v>
       </c>
       <c r="B26" s="9" t="n"/>
-      <c r="C26" s="25" t="n"/>
+      <c r="C26" s="26" t="n"/>
       <c r="D26" s="9" t="n"/>
       <c r="E26" s="9" t="n"/>
-      <c r="F26" s="26">
+      <c r="F26" s="27">
         <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="27">
         <f>IF(C26="","",E26*(C26/8)*2)</f>
         <v/>
       </c>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="26">
+      <c r="H26" s="26" t="n"/>
+      <c r="I26" s="27">
         <f>IF(C26="","",ROUND((F26+G26)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="26">
+      <c r="J26" s="26" t="n"/>
+      <c r="K26" s="27">
         <f>IF(C26="","",F26+G26+H26-I26-J26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="n">
+      <c r="A27" s="25" t="n">
         <v>20</v>
       </c>
       <c r="B27" s="9" t="n"/>
-      <c r="C27" s="25" t="n"/>
+      <c r="C27" s="26" t="n"/>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
-      <c r="F27" s="26">
+      <c r="F27" s="27">
         <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="27">
         <f>IF(C27="","",E27*(C27/8)*2)</f>
         <v/>
       </c>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="26">
+      <c r="H27" s="26" t="n"/>
+      <c r="I27" s="27">
         <f>IF(C27="","",ROUND((F27+G27)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="26">
+      <c r="J27" s="26" t="n"/>
+      <c r="K27" s="27">
         <f>IF(C27="","",F27+G27+H27-I27-J27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="n">
+      <c r="A28" s="25" t="n">
         <v>21</v>
       </c>
       <c r="B28" s="9" t="n"/>
-      <c r="C28" s="25" t="n"/>
+      <c r="C28" s="26" t="n"/>
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
-      <c r="F28" s="26">
+      <c r="F28" s="27">
         <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
-      <c r="G28" s="26">
+      <c r="G28" s="27">
         <f>IF(C28="","",E28*(C28/8)*2)</f>
         <v/>
       </c>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="26">
+      <c r="H28" s="26" t="n"/>
+      <c r="I28" s="27">
         <f>IF(C28="","",ROUND((F28+G28)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="26">
+      <c r="J28" s="26" t="n"/>
+      <c r="K28" s="27">
         <f>IF(C28="","",F28+G28+H28-I28-J28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="n">
+      <c r="A29" s="25" t="n">
         <v>22</v>
       </c>
       <c r="B29" s="9" t="n"/>
-      <c r="C29" s="25" t="n"/>
+      <c r="C29" s="26" t="n"/>
       <c r="D29" s="9" t="n"/>
       <c r="E29" s="9" t="n"/>
-      <c r="F29" s="26">
+      <c r="F29" s="27">
         <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
-      <c r="G29" s="26">
+      <c r="G29" s="27">
         <f>IF(C29="","",E29*(C29/8)*2)</f>
         <v/>
       </c>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="26">
+      <c r="H29" s="26" t="n"/>
+      <c r="I29" s="27">
         <f>IF(C29="","",ROUND((F29+G29)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="26">
+      <c r="J29" s="26" t="n"/>
+      <c r="K29" s="27">
         <f>IF(C29="","",F29+G29+H29-I29-J29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="n">
+      <c r="A30" s="25" t="n">
         <v>23</v>
       </c>
       <c r="B30" s="9" t="n"/>
-      <c r="C30" s="25" t="n"/>
+      <c r="C30" s="26" t="n"/>
       <c r="D30" s="9" t="n"/>
       <c r="E30" s="9" t="n"/>
-      <c r="F30" s="26">
+      <c r="F30" s="27">
         <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
-      <c r="G30" s="26">
+      <c r="G30" s="27">
         <f>IF(C30="","",E30*(C30/8)*2)</f>
         <v/>
       </c>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="26">
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="27">
         <f>IF(C30="","",ROUND((F30+G30)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="26">
+      <c r="J30" s="26" t="n"/>
+      <c r="K30" s="27">
         <f>IF(C30="","",F30+G30+H30-I30-J30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="n">
+      <c r="A31" s="25" t="n">
         <v>24</v>
       </c>
       <c r="B31" s="9" t="n"/>
-      <c r="C31" s="25" t="n"/>
+      <c r="C31" s="26" t="n"/>
       <c r="D31" s="9" t="n"/>
       <c r="E31" s="9" t="n"/>
-      <c r="F31" s="26">
+      <c r="F31" s="27">
         <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
-      <c r="G31" s="26">
+      <c r="G31" s="27">
         <f>IF(C31="","",E31*(C31/8)*2)</f>
         <v/>
       </c>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="26">
+      <c r="H31" s="26" t="n"/>
+      <c r="I31" s="27">
         <f>IF(C31="","",ROUND((F31+G31)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="26">
+      <c r="J31" s="26" t="n"/>
+      <c r="K31" s="27">
         <f>IF(C31="","",F31+G31+H31-I31-J31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="n">
+      <c r="A32" s="25" t="n">
         <v>25</v>
       </c>
       <c r="B32" s="9" t="n"/>
-      <c r="C32" s="25" t="n"/>
+      <c r="C32" s="26" t="n"/>
       <c r="D32" s="9" t="n"/>
       <c r="E32" s="9" t="n"/>
-      <c r="F32" s="26">
+      <c r="F32" s="27">
         <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="27">
         <f>IF(C32="","",E32*(C32/8)*2)</f>
         <v/>
       </c>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="26">
+      <c r="H32" s="26" t="n"/>
+      <c r="I32" s="27">
         <f>IF(C32="","",ROUND((F32+G32)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="26">
+      <c r="J32" s="26" t="n"/>
+      <c r="K32" s="27">
         <f>IF(C32="","",F32+G32+H32-I32-J32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="n">
+      <c r="A33" s="25" t="n">
         <v>26</v>
       </c>
       <c r="B33" s="9" t="n"/>
-      <c r="C33" s="25" t="n"/>
+      <c r="C33" s="26" t="n"/>
       <c r="D33" s="9" t="n"/>
       <c r="E33" s="9" t="n"/>
-      <c r="F33" s="26">
+      <c r="F33" s="27">
         <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="27">
         <f>IF(C33="","",E33*(C33/8)*2)</f>
         <v/>
       </c>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="26">
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="27">
         <f>IF(C33="","",ROUND((F33+G33)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J33" s="25" t="n"/>
-      <c r="K33" s="26">
+      <c r="J33" s="26" t="n"/>
+      <c r="K33" s="27">
         <f>IF(C33="","",F33+G33+H33-I33-J33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="n">
+      <c r="A34" s="25" t="n">
         <v>27</v>
       </c>
       <c r="B34" s="9" t="n"/>
-      <c r="C34" s="25" t="n"/>
+      <c r="C34" s="26" t="n"/>
       <c r="D34" s="9" t="n"/>
       <c r="E34" s="9" t="n"/>
-      <c r="F34" s="26">
+      <c r="F34" s="27">
         <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="27">
         <f>IF(C34="","",E34*(C34/8)*2)</f>
         <v/>
       </c>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="26">
+      <c r="H34" s="26" t="n"/>
+      <c r="I34" s="27">
         <f>IF(C34="","",ROUND((F34+G34)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="26">
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="27">
         <f>IF(C34="","",F34+G34+H34-I34-J34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="n">
+      <c r="A35" s="25" t="n">
         <v>28</v>
       </c>
       <c r="B35" s="9" t="n"/>
-      <c r="C35" s="25" t="n"/>
+      <c r="C35" s="26" t="n"/>
       <c r="D35" s="9" t="n"/>
       <c r="E35" s="9" t="n"/>
-      <c r="F35" s="26">
+      <c r="F35" s="27">
         <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="27">
         <f>IF(C35="","",E35*(C35/8)*2)</f>
         <v/>
       </c>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="26">
+      <c r="H35" s="26" t="n"/>
+      <c r="I35" s="27">
         <f>IF(C35="","",ROUND((F35+G35)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J35" s="25" t="n"/>
-      <c r="K35" s="26">
+      <c r="J35" s="26" t="n"/>
+      <c r="K35" s="27">
         <f>IF(C35="","",F35+G35+H35-I35-J35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="n">
+      <c r="A36" s="25" t="n">
         <v>29</v>
       </c>
       <c r="B36" s="9" t="n"/>
-      <c r="C36" s="25" t="n"/>
+      <c r="C36" s="26" t="n"/>
       <c r="D36" s="9" t="n"/>
       <c r="E36" s="9" t="n"/>
-      <c r="F36" s="26">
+      <c r="F36" s="27">
         <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="27">
         <f>IF(C36="","",E36*(C36/8)*2)</f>
         <v/>
       </c>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="26">
+      <c r="H36" s="26" t="n"/>
+      <c r="I36" s="27">
         <f>IF(C36="","",ROUND((F36+G36)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="26">
+      <c r="J36" s="26" t="n"/>
+      <c r="K36" s="27">
         <f>IF(C36="","",F36+G36+H36-I36-J36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="n">
+      <c r="A37" s="25" t="n">
         <v>30</v>
       </c>
       <c r="B37" s="9" t="n"/>
-      <c r="C37" s="25" t="n"/>
+      <c r="C37" s="26" t="n"/>
       <c r="D37" s="9" t="n"/>
       <c r="E37" s="9" t="n"/>
-      <c r="F37" s="26">
+      <c r="F37" s="27">
         <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
-      <c r="G37" s="26">
+      <c r="G37" s="27">
         <f>IF(C37="","",E37*(C37/8)*2)</f>
         <v/>
       </c>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="26">
+      <c r="H37" s="26" t="n"/>
+      <c r="I37" s="27">
         <f>IF(C37="","",ROUND((F37+G37)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="26">
+      <c r="J37" s="26" t="n"/>
+      <c r="K37" s="27">
         <f>IF(C37="","",F37+G37+H37-I37-J37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="27" t="inlineStr">
+      <c r="E38" s="28" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F38" s="28">
+      <c r="F38" s="29">
         <f>SUM(F8:F37)</f>
         <v/>
       </c>
-      <c r="G38" s="28">
+      <c r="G38" s="29">
         <f>SUM(G8:G37)</f>
         <v/>
       </c>
-      <c r="H38" s="28">
+      <c r="H38" s="29">
         <f>SUM(H8:H37)</f>
         <v/>
       </c>
-      <c r="I38" s="28">
+      <c r="I38" s="29">
         <f>SUM(I8:I37)</f>
         <v/>
       </c>
-      <c r="J38" s="28">
+      <c r="J38" s="29">
         <f>SUM(J8:J37)</f>
         <v/>
       </c>
-      <c r="K38" s="28">
+      <c r="K38" s="29">
         <f>SUM(K8:K37)</f>
         <v/>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="29" t="n"/>
-      <c r="D41" s="29" t="n"/>
-      <c r="E41" s="29" t="n"/>
-      <c r="G41" s="29" t="n"/>
-      <c r="H41" s="29" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
+      <c r="G41" s="30" t="n"/>
+      <c r="H41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="inlineStr">
+      <c r="A42" s="31" t="inlineStr">
         <is>
           <t>Elaboró</t>
         </is>
       </c>
-      <c r="D42" s="30" t="inlineStr">
+      <c r="D42" s="31" t="inlineStr">
         <is>
           <t>Revisó</t>
         </is>
       </c>
-      <c r="G42" s="30" t="inlineStr">
+      <c r="G42" s="31" t="inlineStr">
         <is>
           <t>Autorizó</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="13">
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A2:I2"/>

--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -7,8 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Formato" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PORTADA" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FORMATO" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,88 +31,153 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="001B6B73"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="30"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <i val="1"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00C9A227"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="001B6B73"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="005B6B78"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <color rgb="00C9D3DB"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="Abadi"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
+      <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="26"/>
+      <color rgb="001B6B73"/>
+      <sz val="10"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="00C9D3DB"/>
+      <name val="Abadi"/>
+      <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="001B6B73"/>
+      <name val="Abadi"/>
+      <color theme="1"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00C9A227"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="002B2B2B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="005B6B78"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <color rgb="008A97A3"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -137,8 +204,13 @@
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -210,76 +282,186 @@
       <bottom style="thin"/>
     </border>
     <border>
+      <top style="dashed">
+        <color rgb="00A6A6A6"/>
+      </top>
+    </border>
+    <border>
+      <bottom style="dashed">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C9A227"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9A227"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9A227"/>
+      </bottom>
+    </border>
+    <border>
       <top style="thick">
         <color rgb="00C9A227"/>
       </top>
     </border>
     <border>
-      <top style="thin">
-        <color rgb="00C9A227"/>
-      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -354,6 +536,120 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Neto a pagar por empleado</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'RESUMEN'!C25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="1B6B73"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="1B6B73"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'RESUMEN'!$B$26:$B$40</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'RESUMEN'!$C$26:$C$40</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8460000" cy="3096000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -646,22 +942,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="5" customWidth="1" min="2" max="2"/>
-    <col width="88" customWidth="1" min="3" max="3"/>
-    <col width="4" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="3" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="8" customHeight="1">
       <c r="A1" s="1" t="n"/>
       <c r="B1" s="1" t="n"/>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -670,167 +972,529 @@
       </c>
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>VERSIÓN 2.0  ·  MÉXICO</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="1" t="n"/>
       <c r="C3" s="1" t="n"/>
       <c r="D3" s="1" t="n"/>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="n"/>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Nómina simplificada</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="n"/>
-      <c r="D4" s="1" t="n"/>
-    </row>
-    <row r="5">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>NÓMINA SIMPLIFICADA</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
+      <c r="G4" s="1" t="n"/>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="1" t="n"/>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Formato administrativo editable · México</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="n"/>
-      <c r="D5" s="1" t="n"/>
-    </row>
-    <row r="6">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="1" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="n"/>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Formato administrativo profesional · editable · listo para imprimir</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="1" t="n"/>
       <c r="C7" s="1" t="n"/>
       <c r="D7" s="1" t="n"/>
-    </row>
-    <row r="8" ht="6" customHeight="1">
-      <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="n"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="n"/>
-    </row>
-    <row r="9"/>
+      <c r="E7" s="1" t="n"/>
+      <c r="F7" s="1" t="n"/>
+      <c r="G7" s="1" t="n"/>
+    </row>
+    <row r="8" ht="4" customHeight="1">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="1" t="n"/>
+      <c r="C8" s="1" t="n"/>
+      <c r="D8" s="1" t="n"/>
+      <c r="E8" s="1" t="n"/>
+      <c r="F8" s="1" t="n"/>
+      <c r="G8" s="1" t="n"/>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="1" t="n"/>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>FÓRMULAS AUTOMÁTICAS</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>LISTAS DESPLEGABLES</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>HOJAS PROTEGIDAS</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>LISTO PARA IMPRIMIR</t>
+        </is>
+      </c>
+      <c r="G9" s="1" t="n"/>
+    </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="1" t="n"/>
+      <c r="C10" s="1" t="n"/>
+      <c r="D10" s="1" t="n"/>
+      <c r="E10" s="1" t="n"/>
+      <c r="F10" s="1" t="n"/>
+      <c r="G10" s="1" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="1" t="n"/>
+      <c r="C11" s="1" t="n"/>
+      <c r="D11" s="1" t="n"/>
+      <c r="E11" s="1" t="n"/>
+      <c r="F11" s="1" t="n"/>
+      <c r="G11" s="1" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="1" t="n"/>
+      <c r="C12" s="1" t="n"/>
+      <c r="D12" s="1" t="n"/>
+      <c r="E12" s="1" t="n"/>
+      <c r="F12" s="1" t="n"/>
+      <c r="G12" s="1" t="n"/>
+    </row>
+    <row r="13" ht="6" customHeight="1">
+      <c r="A13" s="8" t="n"/>
+      <c r="B13" s="8" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="8" t="n"/>
+      <c r="F13" s="8" t="n"/>
+      <c r="G13" s="8" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>¿QUÉ INCLUYE ESTE ARCHIVO?</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>FORMATO</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Hoja principal de captura. Aquí registras tu información; las celdas grises calculan solas.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>RESUMEN</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Tablero con indicadores y gráficas que se actualizan automáticamente con tus datos.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>▸</t>
+        </is>
+      </c>
+      <c r="C18" s="14" t="inlineStr">
+        <is>
+          <t>AYUDA</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Preguntas frecuentes, glosario y lista de verificación para cerrar tu periodo.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>CÓMO USARLO</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="21" customHeight="1">
-      <c r="B11" s="7" t="n">
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="10" t="n"/>
+      <c r="F20" s="10" t="n"/>
+      <c r="G20" s="4" t="n"/>
+    </row>
+    <row r="21" ht="21" customHeight="1">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="21" customHeight="1">
-      <c r="B12" s="7" t="n">
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="21" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
         </is>
       </c>
-    </row>
-    <row r="13" ht="21" customHeight="1">
-      <c r="B13" s="7" t="n">
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="21" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="B14" s="7" t="n">
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="21" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="36" customHeight="1">
-      <c r="B15" s="7" t="n">
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="21" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="B16" s="7" t="n">
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Personaliza: en el recuadro punteado de la esquina superior derecha inserta tu logo (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
-    <row r="18">
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>LEYENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="9" t="inlineStr"/>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>Celda de captura: escribe aquí.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="11" t="inlineStr"/>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>Cálculo automático: no la modifiques.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="12" t="inlineStr"/>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Encabezados y títulos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="13" t="n"/>
-      <c r="B23" s="13" t="n"/>
-      <c r="C23" s="13" t="n"/>
-      <c r="D23" s="13" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>GRUPO CANVILLE · Formatos administrativos · v1.0</t>
-        </is>
-      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="10" t="n"/>
+      <c r="F28" s="10" t="n"/>
+      <c r="G28" s="4" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Este formato sirve para control interno y estimaciones; el cálculo oficial debe hacerse con tablas vigentes del SAT e IMSS.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+    </row>
+    <row r="30" ht="21" customHeight="1">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>Captura el ISR retenido que te arroje tu sistema de nómina o tu contador.</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>Las horas extra dobles tienen un límite semanal; verifica la LFT antes de pagar.</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="21" customHeight="1">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>Guarda un archivo por periodo (semana, quincena o mes).</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="4" t="n"/>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="10" t="n"/>
+      <c r="F34" s="10" t="n"/>
+      <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="17" t="inlineStr"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="19" t="inlineStr"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="20" t="inlineStr"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="4" t="n"/>
+      <c r="C38" s="4" t="n"/>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="1" t="n"/>
+      <c r="B39" s="21" t="inlineStr">
+        <is>
+          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="17">
+    <mergeCell ref="C22:F22"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C25:F25"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C24:F24"/>
+    <mergeCell ref="B4:F5"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
 </worksheet>
@@ -843,7 +1507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.4" customWidth="1" min="1" max="1"/>
@@ -860,7 +1524,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>NÓMINA SIMPLIFICADA</t>
         </is>
@@ -873,1014 +1537,1895 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="16" t="inlineStr">
+      <c r="J1" s="23" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="K1" s="17" t="n"/>
+      <c r="K1" s="24" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="25" t="inlineStr">
         <is>
           <t>Cálculo estimado por periodo (referencia administrativa, no sustituye cálculo fiscal)</t>
         </is>
       </c>
-      <c r="B2" s="19" t="n"/>
-      <c r="C2" s="19" t="n"/>
-      <c r="D2" s="19" t="n"/>
-      <c r="E2" s="19" t="n"/>
-      <c r="F2" s="19" t="n"/>
-      <c r="G2" s="19" t="n"/>
-      <c r="H2" s="19" t="n"/>
-      <c r="I2" s="19" t="n"/>
-      <c r="J2" s="20" t="n"/>
-      <c r="K2" s="21" t="n"/>
-    </row>
-    <row r="3"/>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="26" t="n"/>
+      <c r="I2" s="26" t="n"/>
+      <c r="J2" s="27" t="n"/>
+      <c r="K2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="4" t="n"/>
+    </row>
     <row r="4">
-      <c r="A4" s="22" t="inlineStr">
-        <is>
-          <t>Empresa</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n"/>
-      <c r="C4" s="9" t="n"/>
-      <c r="D4" s="9" t="n"/>
-      <c r="F4" s="22" t="inlineStr">
-        <is>
-          <t>Periodo</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>EMPRESA</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="29" t="inlineStr">
+        <is>
+          <t>PERIODO</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="n"/>
+      <c r="H4" s="17" t="n"/>
+      <c r="I4" s="17" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="22" t="inlineStr">
-        <is>
-          <t>Días del periodo</t>
-        </is>
-      </c>
-      <c r="B5" s="9" t="n">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>DÍAS DEL PERIODO</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-      <c r="F5" s="22" t="inlineStr">
-        <is>
-          <t>% retención IMSS (est.)</t>
-        </is>
-      </c>
-      <c r="G5" s="23" t="n">
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="29" t="inlineStr">
+        <is>
+          <t>% RETENCIÓN IMSS (EST.)</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
         <v>0.0275</v>
       </c>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-    </row>
-    <row r="6"/>
+      <c r="H5" s="17" t="n"/>
+      <c r="I5" s="17" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+    </row>
     <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B7" s="24" t="inlineStr">
-        <is>
-          <t>Empleado</t>
-        </is>
-      </c>
-      <c r="C7" s="24" t="inlineStr">
-        <is>
-          <t>Sueldo diario</t>
-        </is>
-      </c>
-      <c r="D7" s="24" t="inlineStr">
-        <is>
-          <t>Días trab.</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="inlineStr">
-        <is>
-          <t>Horas extra</t>
-        </is>
-      </c>
-      <c r="F7" s="24" t="inlineStr">
-        <is>
-          <t>Sueldo</t>
-        </is>
-      </c>
-      <c r="G7" s="24" t="inlineStr">
-        <is>
-          <t>Pago horas extra</t>
-        </is>
-      </c>
-      <c r="H7" s="24" t="inlineStr">
-        <is>
-          <t>Bonos / otros</t>
-        </is>
-      </c>
-      <c r="I7" s="24" t="inlineStr">
-        <is>
-          <t>Retención IMSS</t>
-        </is>
-      </c>
-      <c r="J7" s="24" t="inlineStr">
-        <is>
-          <t>ISR retenido</t>
-        </is>
-      </c>
-      <c r="K7" s="24" t="inlineStr">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>NO.</t>
+        </is>
+      </c>
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>EMPLEADO</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>SUELDO DIARIO</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>DÍAS TRAB.</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>HORAS EXTRA</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>SUELDO</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>PAGO HORAS EXTRA</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>BONOS / OTROS</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>RETENCIÓN IMSS</t>
+        </is>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>ISR RETENIDO</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n">
+      <c r="A8" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="27">
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="34">
         <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="34">
         <f>IF(C8="","",E8*(C8/8)*2)</f>
         <v/>
       </c>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="27">
+      <c r="H8" s="33" t="n"/>
+      <c r="I8" s="34">
         <f>IF(C8="","",ROUND((F8+G8)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="27">
+      <c r="J8" s="33" t="n"/>
+      <c r="K8" s="34">
         <f>IF(C8="","",F8+G8+H8-I8-J8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="n">
+      <c r="A9" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="27">
+      <c r="B9" s="17" t="n"/>
+      <c r="C9" s="33" t="n"/>
+      <c r="D9" s="17" t="n"/>
+      <c r="E9" s="17" t="n"/>
+      <c r="F9" s="34">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="G9" s="27">
+      <c r="G9" s="34">
         <f>IF(C9="","",E9*(C9/8)*2)</f>
         <v/>
       </c>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="27">
+      <c r="H9" s="33" t="n"/>
+      <c r="I9" s="34">
         <f>IF(C9="","",ROUND((F9+G9)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J9" s="26" t="n"/>
-      <c r="K9" s="27">
+      <c r="J9" s="33" t="n"/>
+      <c r="K9" s="34">
         <f>IF(C9="","",F9+G9+H9-I9-J9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n">
+      <c r="A10" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="27">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="34">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="G10" s="27">
+      <c r="G10" s="34">
         <f>IF(C10="","",E10*(C10/8)*2)</f>
         <v/>
       </c>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="27">
+      <c r="H10" s="33" t="n"/>
+      <c r="I10" s="34">
         <f>IF(C10="","",ROUND((F10+G10)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="27">
+      <c r="J10" s="33" t="n"/>
+      <c r="K10" s="34">
         <f>IF(C10="","",F10+G10+H10-I10-J10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="25" t="n">
+      <c r="A11" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
-      <c r="F11" s="27">
+      <c r="B11" s="17" t="n"/>
+      <c r="C11" s="33" t="n"/>
+      <c r="D11" s="17" t="n"/>
+      <c r="E11" s="17" t="n"/>
+      <c r="F11" s="34">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="34">
         <f>IF(C11="","",E11*(C11/8)*2)</f>
         <v/>
       </c>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="27">
+      <c r="H11" s="33" t="n"/>
+      <c r="I11" s="34">
         <f>IF(C11="","",ROUND((F11+G11)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J11" s="26" t="n"/>
-      <c r="K11" s="27">
+      <c r="J11" s="33" t="n"/>
+      <c r="K11" s="34">
         <f>IF(C11="","",F11+G11+H11-I11-J11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n">
+      <c r="A12" s="32" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="27">
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="34">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="G12" s="27">
+      <c r="G12" s="34">
         <f>IF(C12="","",E12*(C12/8)*2)</f>
         <v/>
       </c>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="27">
+      <c r="H12" s="33" t="n"/>
+      <c r="I12" s="34">
         <f>IF(C12="","",ROUND((F12+G12)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="27">
+      <c r="J12" s="33" t="n"/>
+      <c r="K12" s="34">
         <f>IF(C12="","",F12+G12+H12-I12-J12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="25" t="n">
+      <c r="A13" s="32" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="27">
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="33" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="34">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="34">
         <f>IF(C13="","",E13*(C13/8)*2)</f>
         <v/>
       </c>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="27">
+      <c r="H13" s="33" t="n"/>
+      <c r="I13" s="34">
         <f>IF(C13="","",ROUND((F13+G13)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="27">
+      <c r="J13" s="33" t="n"/>
+      <c r="K13" s="34">
         <f>IF(C13="","",F13+G13+H13-I13-J13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n">
+      <c r="A14" s="32" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="27">
+      <c r="B14" s="17" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="17" t="n"/>
+      <c r="E14" s="17" t="n"/>
+      <c r="F14" s="34">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="34">
         <f>IF(C14="","",E14*(C14/8)*2)</f>
         <v/>
       </c>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="27">
+      <c r="H14" s="33" t="n"/>
+      <c r="I14" s="34">
         <f>IF(C14="","",ROUND((F14+G14)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="27">
+      <c r="J14" s="33" t="n"/>
+      <c r="K14" s="34">
         <f>IF(C14="","",F14+G14+H14-I14-J14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="32" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="27">
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="33" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="34">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="G15" s="27">
+      <c r="G15" s="34">
         <f>IF(C15="","",E15*(C15/8)*2)</f>
         <v/>
       </c>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="27">
+      <c r="H15" s="33" t="n"/>
+      <c r="I15" s="34">
         <f>IF(C15="","",ROUND((F15+G15)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="27">
+      <c r="J15" s="33" t="n"/>
+      <c r="K15" s="34">
         <f>IF(C15="","",F15+G15+H15-I15-J15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n">
+      <c r="A16" s="32" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="9" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="27">
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="34">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="G16" s="27">
+      <c r="G16" s="34">
         <f>IF(C16="","",E16*(C16/8)*2)</f>
         <v/>
       </c>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="27">
+      <c r="H16" s="33" t="n"/>
+      <c r="I16" s="34">
         <f>IF(C16="","",ROUND((F16+G16)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="27">
+      <c r="J16" s="33" t="n"/>
+      <c r="K16" s="34">
         <f>IF(C16="","",F16+G16+H16-I16-J16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="25" t="n">
+      <c r="A17" s="32" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="27">
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="33" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="34">
         <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
-      <c r="G17" s="27">
+      <c r="G17" s="34">
         <f>IF(C17="","",E17*(C17/8)*2)</f>
         <v/>
       </c>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="27">
+      <c r="H17" s="33" t="n"/>
+      <c r="I17" s="34">
         <f>IF(C17="","",ROUND((F17+G17)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J17" s="26" t="n"/>
-      <c r="K17" s="27">
+      <c r="J17" s="33" t="n"/>
+      <c r="K17" s="34">
         <f>IF(C17="","",F17+G17+H17-I17-J17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n">
+      <c r="A18" s="32" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="9" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="27">
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="34">
         <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
-      <c r="G18" s="27">
+      <c r="G18" s="34">
         <f>IF(C18="","",E18*(C18/8)*2)</f>
         <v/>
       </c>
-      <c r="H18" s="26" t="n"/>
-      <c r="I18" s="27">
+      <c r="H18" s="33" t="n"/>
+      <c r="I18" s="34">
         <f>IF(C18="","",ROUND((F18+G18)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J18" s="26" t="n"/>
-      <c r="K18" s="27">
+      <c r="J18" s="33" t="n"/>
+      <c r="K18" s="34">
         <f>IF(C18="","",F18+G18+H18-I18-J18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="25" t="n">
+      <c r="A19" s="32" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="27">
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="33" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="34">
         <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
-      <c r="G19" s="27">
+      <c r="G19" s="34">
         <f>IF(C19="","",E19*(C19/8)*2)</f>
         <v/>
       </c>
-      <c r="H19" s="26" t="n"/>
-      <c r="I19" s="27">
+      <c r="H19" s="33" t="n"/>
+      <c r="I19" s="34">
         <f>IF(C19="","",ROUND((F19+G19)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J19" s="26" t="n"/>
-      <c r="K19" s="27">
+      <c r="J19" s="33" t="n"/>
+      <c r="K19" s="34">
         <f>IF(C19="","",F19+G19+H19-I19-J19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n">
+      <c r="A20" s="32" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="9" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="27">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="34">
         <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
-      <c r="G20" s="27">
+      <c r="G20" s="34">
         <f>IF(C20="","",E20*(C20/8)*2)</f>
         <v/>
       </c>
-      <c r="H20" s="26" t="n"/>
-      <c r="I20" s="27">
+      <c r="H20" s="33" t="n"/>
+      <c r="I20" s="34">
         <f>IF(C20="","",ROUND((F20+G20)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J20" s="26" t="n"/>
-      <c r="K20" s="27">
+      <c r="J20" s="33" t="n"/>
+      <c r="K20" s="34">
         <f>IF(C20="","",F20+G20+H20-I20-J20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="n">
+      <c r="A21" s="32" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="27">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="33" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="34">
         <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
-      <c r="G21" s="27">
+      <c r="G21" s="34">
         <f>IF(C21="","",E21*(C21/8)*2)</f>
         <v/>
       </c>
-      <c r="H21" s="26" t="n"/>
-      <c r="I21" s="27">
+      <c r="H21" s="33" t="n"/>
+      <c r="I21" s="34">
         <f>IF(C21="","",ROUND((F21+G21)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J21" s="26" t="n"/>
-      <c r="K21" s="27">
+      <c r="J21" s="33" t="n"/>
+      <c r="K21" s="34">
         <f>IF(C21="","",F21+G21+H21-I21-J21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n">
+      <c r="A22" s="32" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="27">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="34">
         <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
-      <c r="G22" s="27">
+      <c r="G22" s="34">
         <f>IF(C22="","",E22*(C22/8)*2)</f>
         <v/>
       </c>
-      <c r="H22" s="26" t="n"/>
-      <c r="I22" s="27">
+      <c r="H22" s="33" t="n"/>
+      <c r="I22" s="34">
         <f>IF(C22="","",ROUND((F22+G22)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J22" s="26" t="n"/>
-      <c r="K22" s="27">
+      <c r="J22" s="33" t="n"/>
+      <c r="K22" s="34">
         <f>IF(C22="","",F22+G22+H22-I22-J22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="25" t="n">
+      <c r="A23" s="32" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="27">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="33" t="n"/>
+      <c r="D23" s="17" t="n"/>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="34">
         <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
-      <c r="G23" s="27">
+      <c r="G23" s="34">
         <f>IF(C23="","",E23*(C23/8)*2)</f>
         <v/>
       </c>
-      <c r="H23" s="26" t="n"/>
-      <c r="I23" s="27">
+      <c r="H23" s="33" t="n"/>
+      <c r="I23" s="34">
         <f>IF(C23="","",ROUND((F23+G23)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J23" s="26" t="n"/>
-      <c r="K23" s="27">
+      <c r="J23" s="33" t="n"/>
+      <c r="K23" s="34">
         <f>IF(C23="","",F23+G23+H23-I23-J23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n">
+      <c r="A24" s="32" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="27">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="34">
         <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="34">
         <f>IF(C24="","",E24*(C24/8)*2)</f>
         <v/>
       </c>
-      <c r="H24" s="26" t="n"/>
-      <c r="I24" s="27">
+      <c r="H24" s="33" t="n"/>
+      <c r="I24" s="34">
         <f>IF(C24="","",ROUND((F24+G24)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J24" s="26" t="n"/>
-      <c r="K24" s="27">
+      <c r="J24" s="33" t="n"/>
+      <c r="K24" s="34">
         <f>IF(C24="","",F24+G24+H24-I24-J24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="25" t="n">
+      <c r="A25" s="32" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="27">
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="33" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="34">
         <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
-      <c r="G25" s="27">
+      <c r="G25" s="34">
         <f>IF(C25="","",E25*(C25/8)*2)</f>
         <v/>
       </c>
-      <c r="H25" s="26" t="n"/>
-      <c r="I25" s="27">
+      <c r="H25" s="33" t="n"/>
+      <c r="I25" s="34">
         <f>IF(C25="","",ROUND((F25+G25)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J25" s="26" t="n"/>
-      <c r="K25" s="27">
+      <c r="J25" s="33" t="n"/>
+      <c r="K25" s="34">
         <f>IF(C25="","",F25+G25+H25-I25-J25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n">
+      <c r="A26" s="32" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="9" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="27">
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="17" t="n"/>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="34">
         <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
-      <c r="G26" s="27">
+      <c r="G26" s="34">
         <f>IF(C26="","",E26*(C26/8)*2)</f>
         <v/>
       </c>
-      <c r="H26" s="26" t="n"/>
-      <c r="I26" s="27">
+      <c r="H26" s="33" t="n"/>
+      <c r="I26" s="34">
         <f>IF(C26="","",ROUND((F26+G26)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J26" s="26" t="n"/>
-      <c r="K26" s="27">
+      <c r="J26" s="33" t="n"/>
+      <c r="K26" s="34">
         <f>IF(C26="","",F26+G26+H26-I26-J26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="25" t="n">
+      <c r="A27" s="32" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="9" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="9" t="n"/>
-      <c r="F27" s="27">
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="33" t="n"/>
+      <c r="D27" s="17" t="n"/>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="34">
         <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="34">
         <f>IF(C27="","",E27*(C27/8)*2)</f>
         <v/>
       </c>
-      <c r="H27" s="26" t="n"/>
-      <c r="I27" s="27">
+      <c r="H27" s="33" t="n"/>
+      <c r="I27" s="34">
         <f>IF(C27="","",ROUND((F27+G27)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J27" s="26" t="n"/>
-      <c r="K27" s="27">
+      <c r="J27" s="33" t="n"/>
+      <c r="K27" s="34">
         <f>IF(C27="","",F27+G27+H27-I27-J27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n">
+      <c r="A28" s="32" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="9" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="9" t="n"/>
-      <c r="F28" s="27">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="34">
         <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
-      <c r="G28" s="27">
+      <c r="G28" s="34">
         <f>IF(C28="","",E28*(C28/8)*2)</f>
         <v/>
       </c>
-      <c r="H28" s="26" t="n"/>
-      <c r="I28" s="27">
+      <c r="H28" s="33" t="n"/>
+      <c r="I28" s="34">
         <f>IF(C28="","",ROUND((F28+G28)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J28" s="26" t="n"/>
-      <c r="K28" s="27">
+      <c r="J28" s="33" t="n"/>
+      <c r="K28" s="34">
         <f>IF(C28="","",F28+G28+H28-I28-J28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="n">
+      <c r="A29" s="32" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="9" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="27">
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="33" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="34">
         <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
-      <c r="G29" s="27">
+      <c r="G29" s="34">
         <f>IF(C29="","",E29*(C29/8)*2)</f>
         <v/>
       </c>
-      <c r="H29" s="26" t="n"/>
-      <c r="I29" s="27">
+      <c r="H29" s="33" t="n"/>
+      <c r="I29" s="34">
         <f>IF(C29="","",ROUND((F29+G29)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J29" s="26" t="n"/>
-      <c r="K29" s="27">
+      <c r="J29" s="33" t="n"/>
+      <c r="K29" s="34">
         <f>IF(C29="","",F29+G29+H29-I29-J29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n">
+      <c r="A30" s="32" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="27">
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="34">
         <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
-      <c r="G30" s="27">
+      <c r="G30" s="34">
         <f>IF(C30="","",E30*(C30/8)*2)</f>
         <v/>
       </c>
-      <c r="H30" s="26" t="n"/>
-      <c r="I30" s="27">
+      <c r="H30" s="33" t="n"/>
+      <c r="I30" s="34">
         <f>IF(C30="","",ROUND((F30+G30)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J30" s="26" t="n"/>
-      <c r="K30" s="27">
+      <c r="J30" s="33" t="n"/>
+      <c r="K30" s="34">
         <f>IF(C30="","",F30+G30+H30-I30-J30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="n">
+      <c r="A31" s="32" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="26" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="27">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="33" t="n"/>
+      <c r="D31" s="17" t="n"/>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="34">
         <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
-      <c r="G31" s="27">
+      <c r="G31" s="34">
         <f>IF(C31="","",E31*(C31/8)*2)</f>
         <v/>
       </c>
-      <c r="H31" s="26" t="n"/>
-      <c r="I31" s="27">
+      <c r="H31" s="33" t="n"/>
+      <c r="I31" s="34">
         <f>IF(C31="","",ROUND((F31+G31)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J31" s="26" t="n"/>
-      <c r="K31" s="27">
+      <c r="J31" s="33" t="n"/>
+      <c r="K31" s="34">
         <f>IF(C31="","",F31+G31+H31-I31-J31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n">
+      <c r="A32" s="32" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="27">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="34">
         <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
-      <c r="G32" s="27">
+      <c r="G32" s="34">
         <f>IF(C32="","",E32*(C32/8)*2)</f>
         <v/>
       </c>
-      <c r="H32" s="26" t="n"/>
-      <c r="I32" s="27">
+      <c r="H32" s="33" t="n"/>
+      <c r="I32" s="34">
         <f>IF(C32="","",ROUND((F32+G32)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J32" s="26" t="n"/>
-      <c r="K32" s="27">
+      <c r="J32" s="33" t="n"/>
+      <c r="K32" s="34">
         <f>IF(C32="","",F32+G32+H32-I32-J32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="n">
+      <c r="A33" s="32" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="26" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="27">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="33" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="34">
         <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
-      <c r="G33" s="27">
+      <c r="G33" s="34">
         <f>IF(C33="","",E33*(C33/8)*2)</f>
         <v/>
       </c>
-      <c r="H33" s="26" t="n"/>
-      <c r="I33" s="27">
+      <c r="H33" s="33" t="n"/>
+      <c r="I33" s="34">
         <f>IF(C33="","",ROUND((F33+G33)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J33" s="26" t="n"/>
-      <c r="K33" s="27">
+      <c r="J33" s="33" t="n"/>
+      <c r="K33" s="34">
         <f>IF(C33="","",F33+G33+H33-I33-J33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n">
+      <c r="A34" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="9" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="27">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="34">
         <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
-      <c r="G34" s="27">
+      <c r="G34" s="34">
         <f>IF(C34="","",E34*(C34/8)*2)</f>
         <v/>
       </c>
-      <c r="H34" s="26" t="n"/>
-      <c r="I34" s="27">
+      <c r="H34" s="33" t="n"/>
+      <c r="I34" s="34">
         <f>IF(C34="","",ROUND((F34+G34)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J34" s="26" t="n"/>
-      <c r="K34" s="27">
+      <c r="J34" s="33" t="n"/>
+      <c r="K34" s="34">
         <f>IF(C34="","",F34+G34+H34-I34-J34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="25" t="n">
+      <c r="A35" s="32" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="9" t="n"/>
-      <c r="C35" s="26" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="27">
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="33" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="34">
         <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
-      <c r="G35" s="27">
+      <c r="G35" s="34">
         <f>IF(C35="","",E35*(C35/8)*2)</f>
         <v/>
       </c>
-      <c r="H35" s="26" t="n"/>
-      <c r="I35" s="27">
+      <c r="H35" s="33" t="n"/>
+      <c r="I35" s="34">
         <f>IF(C35="","",ROUND((F35+G35)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J35" s="26" t="n"/>
-      <c r="K35" s="27">
+      <c r="J35" s="33" t="n"/>
+      <c r="K35" s="34">
         <f>IF(C35="","",F35+G35+H35-I35-J35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n">
+      <c r="A36" s="32" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="9" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="9" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="27">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="34">
         <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
-      <c r="G36" s="27">
+      <c r="G36" s="34">
         <f>IF(C36="","",E36*(C36/8)*2)</f>
         <v/>
       </c>
-      <c r="H36" s="26" t="n"/>
-      <c r="I36" s="27">
+      <c r="H36" s="33" t="n"/>
+      <c r="I36" s="34">
         <f>IF(C36="","",ROUND((F36+G36)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J36" s="26" t="n"/>
-      <c r="K36" s="27">
+      <c r="J36" s="33" t="n"/>
+      <c r="K36" s="34">
         <f>IF(C36="","",F36+G36+H36-I36-J36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="25" t="n">
+      <c r="A37" s="32" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="26" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="27">
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="33" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="34">
         <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
-      <c r="G37" s="27">
+      <c r="G37" s="34">
         <f>IF(C37="","",E37*(C37/8)*2)</f>
         <v/>
       </c>
-      <c r="H37" s="26" t="n"/>
-      <c r="I37" s="27">
+      <c r="H37" s="33" t="n"/>
+      <c r="I37" s="34">
         <f>IF(C37="","",ROUND((F37+G37)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J37" s="26" t="n"/>
-      <c r="K37" s="27">
+      <c r="J37" s="33" t="n"/>
+      <c r="K37" s="34">
         <f>IF(C37="","",F37+G37+H37-I37-J37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="E38" s="28" t="inlineStr">
+      <c r="A38" s="32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="17" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="34">
+        <f>IF(C38="","",C38*D38)</f>
+        <v/>
+      </c>
+      <c r="G38" s="34">
+        <f>IF(C38="","",E38*(C38/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H38" s="33" t="n"/>
+      <c r="I38" s="34">
+        <f>IF(C38="","",ROUND((F38+G38)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J38" s="33" t="n"/>
+      <c r="K38" s="34">
+        <f>IF(C38="","",F38+G38+H38-I38-J38)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="32" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="33" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="34">
+        <f>IF(C39="","",C39*D39)</f>
+        <v/>
+      </c>
+      <c r="G39" s="34">
+        <f>IF(C39="","",E39*(C39/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H39" s="33" t="n"/>
+      <c r="I39" s="34">
+        <f>IF(C39="","",ROUND((F39+G39)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J39" s="33" t="n"/>
+      <c r="K39" s="34">
+        <f>IF(C39="","",F39+G39+H39-I39-J39)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="32" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="34">
+        <f>IF(C40="","",C40*D40)</f>
+        <v/>
+      </c>
+      <c r="G40" s="34">
+        <f>IF(C40="","",E40*(C40/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H40" s="33" t="n"/>
+      <c r="I40" s="34">
+        <f>IF(C40="","",ROUND((F40+G40)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J40" s="33" t="n"/>
+      <c r="K40" s="34">
+        <f>IF(C40="","",F40+G40+H40-I40-J40)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="33" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="34">
+        <f>IF(C41="","",C41*D41)</f>
+        <v/>
+      </c>
+      <c r="G41" s="34">
+        <f>IF(C41="","",E41*(C41/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H41" s="33" t="n"/>
+      <c r="I41" s="34">
+        <f>IF(C41="","",ROUND((F41+G41)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J41" s="33" t="n"/>
+      <c r="K41" s="34">
+        <f>IF(C41="","",F41+G41+H41-I41-J41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="32" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="33" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="34">
+        <f>IF(C42="","",C42*D42)</f>
+        <v/>
+      </c>
+      <c r="G42" s="34">
+        <f>IF(C42="","",E42*(C42/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H42" s="33" t="n"/>
+      <c r="I42" s="34">
+        <f>IF(C42="","",ROUND((F42+G42)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J42" s="33" t="n"/>
+      <c r="K42" s="34">
+        <f>IF(C42="","",F42+G42+H42-I42-J42)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="32" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="33" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="34">
+        <f>IF(C43="","",C43*D43)</f>
+        <v/>
+      </c>
+      <c r="G43" s="34">
+        <f>IF(C43="","",E43*(C43/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H43" s="33" t="n"/>
+      <c r="I43" s="34">
+        <f>IF(C43="","",ROUND((F43+G43)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J43" s="33" t="n"/>
+      <c r="K43" s="34">
+        <f>IF(C43="","",F43+G43+H43-I43-J43)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="32" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="33" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="34">
+        <f>IF(C44="","",C44*D44)</f>
+        <v/>
+      </c>
+      <c r="G44" s="34">
+        <f>IF(C44="","",E44*(C44/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H44" s="33" t="n"/>
+      <c r="I44" s="34">
+        <f>IF(C44="","",ROUND((F44+G44)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J44" s="33" t="n"/>
+      <c r="K44" s="34">
+        <f>IF(C44="","",F44+G44+H44-I44-J44)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="32" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="33" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="34">
+        <f>IF(C45="","",C45*D45)</f>
+        <v/>
+      </c>
+      <c r="G45" s="34">
+        <f>IF(C45="","",E45*(C45/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H45" s="33" t="n"/>
+      <c r="I45" s="34">
+        <f>IF(C45="","",ROUND((F45+G45)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J45" s="33" t="n"/>
+      <c r="K45" s="34">
+        <f>IF(C45="","",F45+G45+H45-I45-J45)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="32" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="33" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="34">
+        <f>IF(C46="","",C46*D46)</f>
+        <v/>
+      </c>
+      <c r="G46" s="34">
+        <f>IF(C46="","",E46*(C46/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H46" s="33" t="n"/>
+      <c r="I46" s="34">
+        <f>IF(C46="","",ROUND((F46+G46)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J46" s="33" t="n"/>
+      <c r="K46" s="34">
+        <f>IF(C46="","",F46+G46+H46-I46-J46)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="32" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="33" t="n"/>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="34">
+        <f>IF(C47="","",C47*D47)</f>
+        <v/>
+      </c>
+      <c r="G47" s="34">
+        <f>IF(C47="","",E47*(C47/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H47" s="33" t="n"/>
+      <c r="I47" s="34">
+        <f>IF(C47="","",ROUND((F47+G47)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J47" s="33" t="n"/>
+      <c r="K47" s="34">
+        <f>IF(C47="","",F47+G47+H47-I47-J47)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="33" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="34">
+        <f>IF(C48="","",C48*D48)</f>
+        <v/>
+      </c>
+      <c r="G48" s="34">
+        <f>IF(C48="","",E48*(C48/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H48" s="33" t="n"/>
+      <c r="I48" s="34">
+        <f>IF(C48="","",ROUND((F48+G48)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J48" s="33" t="n"/>
+      <c r="K48" s="34">
+        <f>IF(C48="","",F48+G48+H48-I48-J48)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="32" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="33" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="34">
+        <f>IF(C49="","",C49*D49)</f>
+        <v/>
+      </c>
+      <c r="G49" s="34">
+        <f>IF(C49="","",E49*(C49/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H49" s="33" t="n"/>
+      <c r="I49" s="34">
+        <f>IF(C49="","",ROUND((F49+G49)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J49" s="33" t="n"/>
+      <c r="K49" s="34">
+        <f>IF(C49="","",F49+G49+H49-I49-J49)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="32" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="33" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="34">
+        <f>IF(C50="","",C50*D50)</f>
+        <v/>
+      </c>
+      <c r="G50" s="34">
+        <f>IF(C50="","",E50*(C50/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H50" s="33" t="n"/>
+      <c r="I50" s="34">
+        <f>IF(C50="","",ROUND((F50+G50)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J50" s="33" t="n"/>
+      <c r="K50" s="34">
+        <f>IF(C50="","",F50+G50+H50-I50-J50)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="32" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="33" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="34">
+        <f>IF(C51="","",C51*D51)</f>
+        <v/>
+      </c>
+      <c r="G51" s="34">
+        <f>IF(C51="","",E51*(C51/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H51" s="33" t="n"/>
+      <c r="I51" s="34">
+        <f>IF(C51="","",ROUND((F51+G51)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J51" s="33" t="n"/>
+      <c r="K51" s="34">
+        <f>IF(C51="","",F51+G51+H51-I51-J51)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="33" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="34">
+        <f>IF(C52="","",C52*D52)</f>
+        <v/>
+      </c>
+      <c r="G52" s="34">
+        <f>IF(C52="","",E52*(C52/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H52" s="33" t="n"/>
+      <c r="I52" s="34">
+        <f>IF(C52="","",ROUND((F52+G52)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J52" s="33" t="n"/>
+      <c r="K52" s="34">
+        <f>IF(C52="","",F52+G52+H52-I52-J52)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="32" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="33" t="n"/>
+      <c r="D53" s="17" t="n"/>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="34">
+        <f>IF(C53="","",C53*D53)</f>
+        <v/>
+      </c>
+      <c r="G53" s="34">
+        <f>IF(C53="","",E53*(C53/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H53" s="33" t="n"/>
+      <c r="I53" s="34">
+        <f>IF(C53="","",ROUND((F53+G53)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J53" s="33" t="n"/>
+      <c r="K53" s="34">
+        <f>IF(C53="","",F53+G53+H53-I53-J53)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="32" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="33" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="34">
+        <f>IF(C54="","",C54*D54)</f>
+        <v/>
+      </c>
+      <c r="G54" s="34">
+        <f>IF(C54="","",E54*(C54/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H54" s="33" t="n"/>
+      <c r="I54" s="34">
+        <f>IF(C54="","",ROUND((F54+G54)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J54" s="33" t="n"/>
+      <c r="K54" s="34">
+        <f>IF(C54="","",F54+G54+H54-I54-J54)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="32" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="33" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="34">
+        <f>IF(C55="","",C55*D55)</f>
+        <v/>
+      </c>
+      <c r="G55" s="34">
+        <f>IF(C55="","",E55*(C55/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H55" s="33" t="n"/>
+      <c r="I55" s="34">
+        <f>IF(C55="","",ROUND((F55+G55)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J55" s="33" t="n"/>
+      <c r="K55" s="34">
+        <f>IF(C55="","",F55+G55+H55-I55-J55)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="32" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="33" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="34">
+        <f>IF(C56="","",C56*D56)</f>
+        <v/>
+      </c>
+      <c r="G56" s="34">
+        <f>IF(C56="","",E56*(C56/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H56" s="33" t="n"/>
+      <c r="I56" s="34">
+        <f>IF(C56="","",ROUND((F56+G56)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J56" s="33" t="n"/>
+      <c r="K56" s="34">
+        <f>IF(C56="","",F56+G56+H56-I56-J56)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="32" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="33" t="n"/>
+      <c r="D57" s="17" t="n"/>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="34">
+        <f>IF(C57="","",C57*D57)</f>
+        <v/>
+      </c>
+      <c r="G57" s="34">
+        <f>IF(C57="","",E57*(C57/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H57" s="33" t="n"/>
+      <c r="I57" s="34">
+        <f>IF(C57="","",ROUND((F57+G57)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J57" s="33" t="n"/>
+      <c r="K57" s="34">
+        <f>IF(C57="","",F57+G57+H57-I57-J57)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="n">
+        <v>51</v>
+      </c>
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="33" t="n"/>
+      <c r="D58" s="17" t="n"/>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="34">
+        <f>IF(C58="","",C58*D58)</f>
+        <v/>
+      </c>
+      <c r="G58" s="34">
+        <f>IF(C58="","",E58*(C58/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H58" s="33" t="n"/>
+      <c r="I58" s="34">
+        <f>IF(C58="","",ROUND((F58+G58)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J58" s="33" t="n"/>
+      <c r="K58" s="34">
+        <f>IF(C58="","",F58+G58+H58-I58-J58)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="32" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="33" t="n"/>
+      <c r="D59" s="17" t="n"/>
+      <c r="E59" s="17" t="n"/>
+      <c r="F59" s="34">
+        <f>IF(C59="","",C59*D59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="34">
+        <f>IF(C59="","",E59*(C59/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H59" s="33" t="n"/>
+      <c r="I59" s="34">
+        <f>IF(C59="","",ROUND((F59+G59)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J59" s="33" t="n"/>
+      <c r="K59" s="34">
+        <f>IF(C59="","",F59+G59+H59-I59-J59)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="32" t="n">
+        <v>53</v>
+      </c>
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="33" t="n"/>
+      <c r="D60" s="17" t="n"/>
+      <c r="E60" s="17" t="n"/>
+      <c r="F60" s="34">
+        <f>IF(C60="","",C60*D60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="34">
+        <f>IF(C60="","",E60*(C60/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H60" s="33" t="n"/>
+      <c r="I60" s="34">
+        <f>IF(C60="","",ROUND((F60+G60)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J60" s="33" t="n"/>
+      <c r="K60" s="34">
+        <f>IF(C60="","",F60+G60+H60-I60-J60)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="32" t="n">
+        <v>54</v>
+      </c>
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="33" t="n"/>
+      <c r="D61" s="17" t="n"/>
+      <c r="E61" s="17" t="n"/>
+      <c r="F61" s="34">
+        <f>IF(C61="","",C61*D61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="34">
+        <f>IF(C61="","",E61*(C61/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H61" s="33" t="n"/>
+      <c r="I61" s="34">
+        <f>IF(C61="","",ROUND((F61+G61)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J61" s="33" t="n"/>
+      <c r="K61" s="34">
+        <f>IF(C61="","",F61+G61+H61-I61-J61)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="32" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="33" t="n"/>
+      <c r="D62" s="17" t="n"/>
+      <c r="E62" s="17" t="n"/>
+      <c r="F62" s="34">
+        <f>IF(C62="","",C62*D62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="34">
+        <f>IF(C62="","",E62*(C62/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H62" s="33" t="n"/>
+      <c r="I62" s="34">
+        <f>IF(C62="","",ROUND((F62+G62)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J62" s="33" t="n"/>
+      <c r="K62" s="34">
+        <f>IF(C62="","",F62+G62+H62-I62-J62)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="32" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="33" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="n"/>
+      <c r="F63" s="34">
+        <f>IF(C63="","",C63*D63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="34">
+        <f>IF(C63="","",E63*(C63/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H63" s="33" t="n"/>
+      <c r="I63" s="34">
+        <f>IF(C63="","",ROUND((F63+G63)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J63" s="33" t="n"/>
+      <c r="K63" s="34">
+        <f>IF(C63="","",F63+G63+H63-I63-J63)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="32" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="33" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="n"/>
+      <c r="F64" s="34">
+        <f>IF(C64="","",C64*D64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="34">
+        <f>IF(C64="","",E64*(C64/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H64" s="33" t="n"/>
+      <c r="I64" s="34">
+        <f>IF(C64="","",ROUND((F64+G64)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J64" s="33" t="n"/>
+      <c r="K64" s="34">
+        <f>IF(C64="","",F64+G64+H64-I64-J64)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="33" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="n"/>
+      <c r="F65" s="34">
+        <f>IF(C65="","",C65*D65)</f>
+        <v/>
+      </c>
+      <c r="G65" s="34">
+        <f>IF(C65="","",E65*(C65/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H65" s="33" t="n"/>
+      <c r="I65" s="34">
+        <f>IF(C65="","",ROUND((F65+G65)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J65" s="33" t="n"/>
+      <c r="K65" s="34">
+        <f>IF(C65="","",F65+G65+H65-I65-J65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="32" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="17" t="n"/>
+      <c r="C66" s="33" t="n"/>
+      <c r="D66" s="17" t="n"/>
+      <c r="E66" s="17" t="n"/>
+      <c r="F66" s="34">
+        <f>IF(C66="","",C66*D66)</f>
+        <v/>
+      </c>
+      <c r="G66" s="34">
+        <f>IF(C66="","",E66*(C66/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H66" s="33" t="n"/>
+      <c r="I66" s="34">
+        <f>IF(C66="","",ROUND((F66+G66)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J66" s="33" t="n"/>
+      <c r="K66" s="34">
+        <f>IF(C66="","",F66+G66+H66-I66-J66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="32" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="17" t="n"/>
+      <c r="C67" s="33" t="n"/>
+      <c r="D67" s="17" t="n"/>
+      <c r="E67" s="17" t="n"/>
+      <c r="F67" s="34">
+        <f>IF(C67="","",C67*D67)</f>
+        <v/>
+      </c>
+      <c r="G67" s="34">
+        <f>IF(C67="","",E67*(C67/8)*2)</f>
+        <v/>
+      </c>
+      <c r="H67" s="33" t="n"/>
+      <c r="I67" s="34">
+        <f>IF(C67="","",ROUND((F67+G67)*$G$5,2))</f>
+        <v/>
+      </c>
+      <c r="J67" s="33" t="n"/>
+      <c r="K67" s="34">
+        <f>IF(C67="","",F67+G67+H67-I67-J67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n"/>
+      <c r="B68" s="4" t="n"/>
+      <c r="C68" s="4" t="n"/>
+      <c r="D68" s="4" t="n"/>
+      <c r="E68" s="35" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F38" s="29">
-        <f>SUM(F8:F37)</f>
-        <v/>
-      </c>
-      <c r="G38" s="29">
-        <f>SUM(G8:G37)</f>
-        <v/>
-      </c>
-      <c r="H38" s="29">
-        <f>SUM(H8:H37)</f>
-        <v/>
-      </c>
-      <c r="I38" s="29">
-        <f>SUM(I8:I37)</f>
-        <v/>
-      </c>
-      <c r="J38" s="29">
-        <f>SUM(J8:J37)</f>
-        <v/>
-      </c>
-      <c r="K38" s="29">
-        <f>SUM(K8:K37)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="30" t="n"/>
-      <c r="B41" s="30" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
-      <c r="H41" s="30" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="31" t="inlineStr">
-        <is>
-          <t>Elaboró</t>
-        </is>
-      </c>
-      <c r="D42" s="31" t="inlineStr">
-        <is>
-          <t>Revisó</t>
-        </is>
-      </c>
-      <c r="G42" s="31" t="inlineStr">
-        <is>
-          <t>Autorizó</t>
-        </is>
-      </c>
+      <c r="F68" s="36">
+        <f>SUM(F8:F67)</f>
+        <v/>
+      </c>
+      <c r="G68" s="36">
+        <f>SUM(G8:G67)</f>
+        <v/>
+      </c>
+      <c r="H68" s="36">
+        <f>SUM(H8:H67)</f>
+        <v/>
+      </c>
+      <c r="I68" s="36">
+        <f>SUM(I8:I67)</f>
+        <v/>
+      </c>
+      <c r="J68" s="36">
+        <f>SUM(J8:J67)</f>
+        <v/>
+      </c>
+      <c r="K68" s="36">
+        <f>SUM(K8:K67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n"/>
+      <c r="B69" s="4" t="n"/>
+      <c r="C69" s="4" t="n"/>
+      <c r="D69" s="4" t="n"/>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n"/>
+      <c r="B70" s="4" t="n"/>
+      <c r="C70" s="4" t="n"/>
+      <c r="D70" s="4" t="n"/>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="37" t="n"/>
+      <c r="B71" s="37" t="n"/>
+      <c r="C71" s="4" t="n"/>
+      <c r="D71" s="37" t="n"/>
+      <c r="E71" s="37" t="n"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="37" t="n"/>
+      <c r="H71" s="37" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="38" t="inlineStr">
+        <is>
+          <t>ELABORÓ</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="n"/>
+      <c r="C72" s="4" t="n"/>
+      <c r="D72" s="38" t="inlineStr">
+        <is>
+          <t>REVISÓ</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="38" t="inlineStr">
+        <is>
+          <t>AUTORIZÓ</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="13">
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="D72:E72"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="A71:B71"/>
     <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="G71:H71"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="J1:K2"/>
-    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D71:E71"/>
+    <mergeCell ref="G72:H72"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1894,4 +3439,1050 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00C9A227"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="2" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="44" customHeight="1">
+      <c r="A1" s="22" t="inlineStr">
+        <is>
+          <t>RESUMEN DE NÓMINA</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="23" t="inlineStr">
+        <is>
+          <t>INSERTE SU LOGO
+(clic derecho &gt; Insertar imagen)</t>
+        </is>
+      </c>
+      <c r="I1" s="39" t="n"/>
+      <c r="J1" s="24" t="n"/>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="25" t="inlineStr">
+        <is>
+          <t>Percepciones, deducciones y neto del periodo</t>
+        </is>
+      </c>
+      <c r="B2" s="26" t="n"/>
+      <c r="C2" s="26" t="n"/>
+      <c r="D2" s="26" t="n"/>
+      <c r="E2" s="26" t="n"/>
+      <c r="F2" s="26" t="n"/>
+      <c r="G2" s="26" t="n"/>
+      <c r="H2" s="27" t="n"/>
+      <c r="I2" s="40" t="n"/>
+      <c r="J2" s="28" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
+      <c r="F3" s="4" t="n"/>
+      <c r="G3" s="4" t="n"/>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>PERCEPCIONES</t>
+        </is>
+      </c>
+      <c r="C4" s="42" t="n"/>
+      <c r="D4" s="41" t="inlineStr">
+        <is>
+          <t>DEDUCCIONES</t>
+        </is>
+      </c>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="41" t="inlineStr">
+        <is>
+          <t>NETO A PAGAR</t>
+        </is>
+      </c>
+      <c r="G4" s="42" t="n"/>
+      <c r="H4" s="41" t="inlineStr">
+        <is>
+          <t>EMPLEADOS</t>
+        </is>
+      </c>
+      <c r="I4" s="42" t="n"/>
+      <c r="J4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="43">
+        <f>FORMATO!F68+FORMATO!G68+FORMATO!H68</f>
+        <v/>
+      </c>
+      <c r="C5" s="44" t="n"/>
+      <c r="D5" s="43">
+        <f>FORMATO!I68+FORMATO!J68</f>
+        <v/>
+      </c>
+      <c r="E5" s="44" t="n"/>
+      <c r="F5" s="43">
+        <f>FORMATO!K68</f>
+        <v/>
+      </c>
+      <c r="G5" s="44" t="n"/>
+      <c r="H5" s="45">
+        <f>COUNT(FORMATO!C8:C67)</f>
+        <v/>
+      </c>
+      <c r="I5" s="44" t="n"/>
+      <c r="J5" s="4" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="n"/>
+      <c r="E7" s="4" t="n"/>
+      <c r="F7" s="4" t="n"/>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
+      <c r="F9" s="4" t="n"/>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="n"/>
+      <c r="F10" s="4" t="n"/>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="4" t="n"/>
+      <c r="F12" s="4" t="n"/>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n"/>
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="4" t="n"/>
+      <c r="F20" s="4" t="n"/>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="32" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>EMPLEADO</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>NETO A PAGAR</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="46">
+        <f>IF(FORMATO!B8="","",FORMATO!B8)</f>
+        <v/>
+      </c>
+      <c r="C26" s="34">
+        <f>IF(FORMATO!K8="",0,FORMATO!K8)</f>
+        <v/>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n"/>
+      <c r="B27" s="46">
+        <f>IF(FORMATO!B9="","",FORMATO!B9)</f>
+        <v/>
+      </c>
+      <c r="C27" s="34">
+        <f>IF(FORMATO!K9="",0,FORMATO!K9)</f>
+        <v/>
+      </c>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n"/>
+      <c r="B28" s="46">
+        <f>IF(FORMATO!B10="","",FORMATO!B10)</f>
+        <v/>
+      </c>
+      <c r="C28" s="34">
+        <f>IF(FORMATO!K10="",0,FORMATO!K10)</f>
+        <v/>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n"/>
+      <c r="B29" s="46">
+        <f>IF(FORMATO!B11="","",FORMATO!B11)</f>
+        <v/>
+      </c>
+      <c r="C29" s="34">
+        <f>IF(FORMATO!K11="",0,FORMATO!K11)</f>
+        <v/>
+      </c>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n"/>
+      <c r="B30" s="46">
+        <f>IF(FORMATO!B12="","",FORMATO!B12)</f>
+        <v/>
+      </c>
+      <c r="C30" s="34">
+        <f>IF(FORMATO!K12="",0,FORMATO!K12)</f>
+        <v/>
+      </c>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n"/>
+      <c r="B31" s="46">
+        <f>IF(FORMATO!B13="","",FORMATO!B13)</f>
+        <v/>
+      </c>
+      <c r="C31" s="34">
+        <f>IF(FORMATO!K13="",0,FORMATO!K13)</f>
+        <v/>
+      </c>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n"/>
+      <c r="B32" s="46">
+        <f>IF(FORMATO!B14="","",FORMATO!B14)</f>
+        <v/>
+      </c>
+      <c r="C32" s="34">
+        <f>IF(FORMATO!K14="",0,FORMATO!K14)</f>
+        <v/>
+      </c>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n"/>
+      <c r="B33" s="46">
+        <f>IF(FORMATO!B15="","",FORMATO!B15)</f>
+        <v/>
+      </c>
+      <c r="C33" s="34">
+        <f>IF(FORMATO!K15="",0,FORMATO!K15)</f>
+        <v/>
+      </c>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n"/>
+      <c r="B34" s="46">
+        <f>IF(FORMATO!B16="","",FORMATO!B16)</f>
+        <v/>
+      </c>
+      <c r="C34" s="34">
+        <f>IF(FORMATO!K16="",0,FORMATO!K16)</f>
+        <v/>
+      </c>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n"/>
+      <c r="B35" s="46">
+        <f>IF(FORMATO!B17="","",FORMATO!B17)</f>
+        <v/>
+      </c>
+      <c r="C35" s="34">
+        <f>IF(FORMATO!K17="",0,FORMATO!K17)</f>
+        <v/>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n"/>
+      <c r="B36" s="46">
+        <f>IF(FORMATO!B18="","",FORMATO!B18)</f>
+        <v/>
+      </c>
+      <c r="C36" s="34">
+        <f>IF(FORMATO!K18="",0,FORMATO!K18)</f>
+        <v/>
+      </c>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n"/>
+      <c r="B37" s="46">
+        <f>IF(FORMATO!B19="","",FORMATO!B19)</f>
+        <v/>
+      </c>
+      <c r="C37" s="34">
+        <f>IF(FORMATO!K19="",0,FORMATO!K19)</f>
+        <v/>
+      </c>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n"/>
+      <c r="B38" s="46">
+        <f>IF(FORMATO!B20="","",FORMATO!B20)</f>
+        <v/>
+      </c>
+      <c r="C38" s="34">
+        <f>IF(FORMATO!K20="",0,FORMATO!K20)</f>
+        <v/>
+      </c>
+      <c r="D38" s="4" t="n"/>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="46">
+        <f>IF(FORMATO!B21="","",FORMATO!B21)</f>
+        <v/>
+      </c>
+      <c r="C39" s="34">
+        <f>IF(FORMATO!K21="",0,FORMATO!K21)</f>
+        <v/>
+      </c>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="46">
+        <f>IF(FORMATO!B22="","",FORMATO!B22)</f>
+        <v/>
+      </c>
+      <c r="C40" s="34">
+        <f>IF(FORMATO!K22="",0,FORMATO!K22)</f>
+        <v/>
+      </c>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="11">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H1:J2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 Página &amp;P&amp;R&amp;8 Impreso: &amp;D</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001B6B73"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="47" t="inlineStr">
+        <is>
+          <t>AYUDA Y PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="1" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="48" t="inlineStr">
+        <is>
+          <t>NÓMINA SIMPLIFICADA</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="n"/>
+      <c r="B3" s="8" t="n"/>
+      <c r="C3" s="8" t="n"/>
+      <c r="D3" s="8" t="n"/>
+      <c r="E3" s="8" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>PREGUNTAS FRECUENTES</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>¿El % de IMSS es exacto?</t>
+        </is>
+      </c>
+      <c r="D6" s="50" t="inlineStr">
+        <is>
+          <t>No. Es una referencia editable; la cuota real varía por ramo, salario base de cotización y prima de riesgo.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="4" t="n"/>
+      <c r="B7" s="4" t="n"/>
+      <c r="C7" s="49" t="inlineStr">
+        <is>
+          <t>¿Sirve para timbrar recibos?</t>
+        </is>
+      </c>
+      <c r="D7" s="50" t="inlineStr">
+        <is>
+          <t>No. Para recibos CFDI de nómina usa tu sistema de timbrado.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="53" customHeight="1">
+      <c r="A8" s="4" t="n"/>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>¿Por qué no puedo escribir en algunas celdas?</t>
+        </is>
+      </c>
+      <c r="D8" s="50" t="inlineStr">
+        <is>
+          <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="38" customHeight="1">
+      <c r="A9" s="4" t="n"/>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="49" t="inlineStr">
+        <is>
+          <t>¿Cómo agrego mi logotipo?</t>
+        </is>
+      </c>
+      <c r="D9" s="50" t="inlineStr">
+        <is>
+          <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="38" customHeight="1">
+      <c r="A10" s="4" t="n"/>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
+        </is>
+      </c>
+      <c r="D10" s="50" t="inlineStr">
+        <is>
+          <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="38" customHeight="1">
+      <c r="A11" s="4" t="n"/>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="49" t="inlineStr">
+        <is>
+          <t>¿Con qué versiones de Excel funciona?</t>
+        </is>
+      </c>
+      <c r="D11" s="50" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="38" customHeight="1">
+      <c r="A12" s="4" t="n"/>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>¿Por qué la letra se ve diferente?</t>
+        </is>
+      </c>
+      <c r="D12" s="50" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="38" customHeight="1">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="49" t="inlineStr">
+        <is>
+          <t>¿Puedo usarlo en varias empresas o por varios años?</t>
+        </is>
+      </c>
+      <c r="D13" s="50" t="inlineStr">
+        <is>
+          <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n"/>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>GLOSARIO</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="21" customHeight="1">
+      <c r="A16" s="4" t="n"/>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="51" t="inlineStr">
+        <is>
+          <t>SUELDO DIARIO</t>
+        </is>
+      </c>
+      <c r="D16" s="52" t="inlineStr">
+        <is>
+          <t>Pago por día laborado.</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n"/>
+    </row>
+    <row r="17" ht="21" customHeight="1">
+      <c r="A17" s="4" t="n"/>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="51" t="inlineStr">
+        <is>
+          <t>SDI</t>
+        </is>
+      </c>
+      <c r="D17" s="52" t="inlineStr">
+        <is>
+          <t>Salario diario integrado, base de cotización al IMSS.</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n"/>
+    </row>
+    <row r="18" ht="21" customHeight="1">
+      <c r="A18" s="4" t="n"/>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="51" t="inlineStr">
+        <is>
+          <t>PERCEPCIONES</t>
+        </is>
+      </c>
+      <c r="D18" s="52" t="inlineStr">
+        <is>
+          <t>Sueldos, horas extra, bonos y demás pagos.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n"/>
+    </row>
+    <row r="19" ht="21" customHeight="1">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="51" t="inlineStr">
+        <is>
+          <t>DEDUCCIONES</t>
+        </is>
+      </c>
+      <c r="D19" s="52" t="inlineStr">
+        <is>
+          <t>ISR, IMSS y otros descuentos.</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n"/>
+    </row>
+    <row r="20" ht="21" customHeight="1">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="51" t="inlineStr">
+        <is>
+          <t>NETO</t>
+        </is>
+      </c>
+      <c r="D20" s="52" t="inlineStr">
+        <is>
+          <t>Percepciones - deducciones.</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="4" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>LISTA DE VERIFICACIÓN (marca ☑ al completar)</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="4" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="4" t="n"/>
+      <c r="B23" s="53" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr">
+        <is>
+          <t>Asistencia del periodo validada</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="4" t="n"/>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C24" s="54" t="inlineStr">
+        <is>
+          <t>Horas extra autorizadas</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="53" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C25" s="54" t="inlineStr">
+        <is>
+          <t>ISR/IMSS calculados</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="4" t="n"/>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="C26" s="54" t="inlineStr">
+        <is>
+          <t>Dispersión y recibos entregados</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="6">
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="B23 B24 B25 B26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+      <formula1>"☐,☑"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -51,7 +51,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
     </font>
     <font>
       <name val="Abadi"/>
@@ -70,7 +70,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
@@ -112,7 +112,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
@@ -135,7 +135,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
@@ -163,7 +163,7 @@
     <font>
       <name val="Abadi"/>
       <b val="1"/>
-      <color rgb="001B6B73"/>
+      <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
@@ -570,11 +570,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="1B6B73"/>
+              <a:srgbClr val="0E7C8B"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="1B6B73"/>
+                <a:srgbClr val="0E7C8B"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -4115,7 +4115,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001B6B73"/>
+    <tabColor rgb="000E7C8B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -967,7 +967,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE</t>
+          <t>FORMATOS ADMINISTRATIVOS</t>
         </is>
       </c>
       <c r="C2" s="1" t="n"/>
@@ -1464,7 +1464,7 @@
       <c r="A39" s="1" t="n"/>
       <c r="B39" s="21" t="inlineStr">
         <is>
-          <t>GRUPO CANVILLE  ·  Formatos administrativos  ·  Para uso interno de tu empresa</t>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
         </is>
       </c>
       <c r="C39" s="4" t="n"/>

--- a/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
+++ b/plantillas/2_Recursos_Humanos/02_Nomina_Simplificada.xlsx
@@ -12,7 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMEN" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AYUDA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'FORMATO'!$7:$7</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,153 +33,166 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="20"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00A6A6A6"/>
       <sz val="8"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
-      <sz val="18"/>
+      <sz val="24"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="000B2A4A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="30"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <i val="1"/>
       <color rgb="00C9D3DB"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E7C8B"/>
+      <sz val="10"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002B2B2B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000B2A4A"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
-      <color rgb="002B2B2B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="11"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="005B6B78"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="00C9D3DB"/>
       <sz val="9"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="18"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="00C9A227"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="000E7C8B"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color rgb="000B2A4A"/>
       <sz val="12"/>
     </font>
     <font>
-      <name val="Abadi"/>
+      <name val="Arial"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -200,6 +215,16 @@
       </patternFill>
     </fill>
     <fill>
+      <gradientFill type="linear" degree="90">
+        <stop position="0">
+          <color rgb="0017426B"/>
+        </stop>
+        <stop position="1">
+          <color rgb="000B2A4A"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EEF2F5"/>
       </patternFill>
@@ -209,8 +234,13 @@
         <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -279,6 +309,20 @@
       </bottom>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C9D3DB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C9D3DB"/>
+      </right>
+      <top style="medium">
+        <color rgb="00C9A227"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C9D3DB"/>
+      </bottom>
+    </border>
+    <border>
       <bottom style="thin"/>
     </border>
     <border>
@@ -324,6 +368,11 @@
       </bottom>
     </border>
     <border>
+      <left style="thick">
+        <color rgb="00C9A227"/>
+      </left>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="00C9A227"/>
       </left>
@@ -344,6 +393,11 @@
     </border>
     <border>
       <bottom style="thin">
+        <color rgb="00E3E8ED"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
         <color rgb="00C9D3DB"/>
       </bottom>
     </border>
@@ -351,47 +405,55 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -400,68 +462,79 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="28" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="5" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="4" borderId="7" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="5" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="3" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="6" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="9" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="28" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="4" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -540,6 +613,7 @@
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <roundedCorners val="0"/>
   <chart>
     <title>
       <tx>
@@ -570,11 +644,11 @@
           </tx>
           <spPr>
             <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:srgbClr val="0E7C8B"/>
+              <a:srgbClr val="12A0A8"/>
             </a:solidFill>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:solidFill>
-                <a:srgbClr val="0E7C8B"/>
+                <a:srgbClr val="12A0A8"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -590,7 +664,7 @@
             </numRef>
           </val>
         </ser>
-        <gapWidth val="150"/>
+        <gapWidth val="70"/>
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
@@ -613,6 +687,16 @@
         </scaling>
         <delete val="0"/>
         <axPos val="l"/>
+        <majorGridlines>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="6350">
+              <a:solidFill>
+                <a:srgbClr val="E3E8ED"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+        </majorGridlines>
         <numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -622,6 +706,12 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:noFill/>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -942,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1201,7 +1291,7 @@
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>CÓMO USARLO</t>
+          <t>FICHA TÉCNICA</t>
         </is>
       </c>
       <c r="C20" s="10" t="n"/>
@@ -1212,126 +1302,134 @@
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="4" t="n"/>
-      <c r="B21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="4" t="n"/>
-      <c r="F21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>Capacidad</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>60 empleados</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
       <c r="G21" s="4" t="n"/>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="4" t="n"/>
-      <c r="B22" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>Compatibilidad</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac)</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
       <c r="G22" s="4" t="n"/>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>Idioma y moneda</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>Español (México) · Pesos mexicanos (MXN) · IVA 16%</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
       <c r="G23" s="4" t="n"/>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>Protección</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>Hojas protegidas sin contraseña (Revisar &gt; Desproteger hoja)</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
       <c r="G24" s="4" t="n"/>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="15" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>Arial (disponible en Windows, Mac y Google Sheets)</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
       <c r="G25" s="4" t="n"/>
     </row>
-    <row r="26" ht="36" customHeight="1">
+    <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
-        </is>
-      </c>
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
       <c r="G26" s="4" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="24" customHeight="1">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>CÓMO USARLO</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="10" t="n"/>
+      <c r="F27" s="10" t="n"/>
       <c r="G27" s="4" t="n"/>
     </row>
-    <row r="28" ht="24" customHeight="1">
+    <row r="28" ht="21" customHeight="1">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="9" t="inlineStr">
-        <is>
-          <t>RECOMENDACIONES DE USO</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-      <c r="E28" s="10" t="n"/>
-      <c r="F28" s="10" t="n"/>
+      <c r="B28" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>Captura sueldo diario, días trabajados y horas extra de cada empleado.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
       <c r="G28" s="4" t="n"/>
     </row>
-    <row r="29" ht="36" customHeight="1">
+    <row r="29" ht="21" customHeight="1">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B29" s="18" t="n">
+        <v>2</v>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>Este formato sirve para control interno y estimaciones; el cálculo oficial debe hacerse con tablas vigentes del SAT e IMSS.</t>
+          <t>Las horas extra se pagan al doble de la hora ordinaria (jornada de 8 h).</t>
         </is>
       </c>
       <c r="D29" s="4" t="n"/>
@@ -1341,14 +1439,12 @@
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B30" s="18" t="n">
+        <v>3</v>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>Captura el ISR retenido que te arroje tu sistema de nómina o tu contador.</t>
+          <t>El ISR retenido se captura manualmente según la tabla del SAT vigente.</t>
         </is>
       </c>
       <c r="D30" s="4" t="n"/>
@@ -1358,14 +1454,12 @@
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B31" s="18" t="n">
+        <v>4</v>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>Las horas extra dobles tienen un límite semanal; verifica la LFT antes de pagar.</t>
+          <t>Ajusta el % de retención IMSS según tu cálculo; el valor incluido es solo una referencia.</t>
         </is>
       </c>
       <c r="D31" s="4" t="n"/>
@@ -1375,14 +1469,12 @@
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="B32" s="18" t="n">
+        <v>5</v>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>Guarda un archivo por periodo (semana, quincena o mes).</t>
+          <t>Este formato es de control administrativo. Para timbrado de recibos usa tu sistema de nómina CFDI.</t>
         </is>
       </c>
       <c r="D32" s="4" t="n"/>
@@ -1390,47 +1482,53 @@
       <c r="F32" s="4" t="n"/>
       <c r="G32" s="4" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="36" customHeight="1">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
+      <c r="B33" s="18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Personaliza: inserta tu logotipo en el recuadro punteado de la esquina superior derecha (Insertar &gt; Imágenes) y captura los datos de tu empresa en las celdas de captura.</t>
+        </is>
+      </c>
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
       <c r="G33" s="4" t="n"/>
     </row>
-    <row r="34" ht="24" customHeight="1">
+    <row r="34">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>LEYENDA DE COLORES</t>
-        </is>
-      </c>
-      <c r="C34" s="10" t="n"/>
-      <c r="D34" s="10" t="n"/>
-      <c r="E34" s="10" t="n"/>
-      <c r="F34" s="10" t="n"/>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
       <c r="G34" s="4" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="24" customHeight="1">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="17" t="inlineStr"/>
-      <c r="C35" s="18" t="inlineStr">
-        <is>
-          <t>CELDA DE CAPTURA: escribe aquí.</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="n"/>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>RECOMENDACIONES DE USO</t>
+        </is>
+      </c>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="10" t="n"/>
+      <c r="F35" s="10" t="n"/>
       <c r="G35" s="4" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="19" t="inlineStr"/>
-      <c r="C36" s="18" t="inlineStr">
-        <is>
-          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>Este formato sirve para control interno y estimaciones; el cálculo oficial debe hacerse con tablas vigentes del SAT e IMSS.</t>
         </is>
       </c>
       <c r="D36" s="4" t="n"/>
@@ -1438,12 +1536,16 @@
       <c r="F36" s="4" t="n"/>
       <c r="G36" s="4" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="21" customHeight="1">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="20" t="inlineStr"/>
-      <c r="C37" s="18" t="inlineStr">
-        <is>
-          <t>ENCABEZADOS Y TÍTULOS.</t>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>Captura el ISR retenido que te arroje tu sistema de nómina o tu contador.</t>
         </is>
       </c>
       <c r="D37" s="4" t="n"/>
@@ -1451,49 +1553,167 @@
       <c r="F37" s="4" t="n"/>
       <c r="G37" s="4" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="21" customHeight="1">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>Las horas extra dobles tienen un límite semanal; verifica la LFT antes de pagar.</t>
+        </is>
+      </c>
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
       <c r="G38" s="4" t="n"/>
     </row>
-    <row r="39" ht="26" customHeight="1">
-      <c r="A39" s="1" t="n"/>
-      <c r="B39" s="21" t="inlineStr">
-        <is>
-          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="n"/>
+    <row r="39" ht="21" customHeight="1">
+      <c r="A39" s="4" t="n"/>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>Guarda un archivo por periodo (semana, quincena o mes).</t>
+        </is>
+      </c>
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
-      <c r="G39" s="1" t="n"/>
+      <c r="G39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n"/>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="4" t="n"/>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>LEYENDA DE COLORES</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="10" t="n"/>
+      <c r="F41" s="10" t="n"/>
+      <c r="G41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n"/>
+      <c r="B42" s="20" t="inlineStr"/>
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>CELDA DE CAPTURA: escribe aquí.</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="n"/>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n"/>
+      <c r="B43" s="22" t="inlineStr"/>
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>CÁLCULO AUTOMÁTICO: no la modifiques.</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="n"/>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n"/>
+      <c r="B44" s="23" t="inlineStr"/>
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>ENCABEZADOS Y TÍTULOS.</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="n"/>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n"/>
+      <c r="B45" s="24" t="inlineStr"/>
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>* CAMPO OBLIGATORIO: complétalo antes de imprimir o enviar.</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n"/>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="1" t="n"/>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>Formatos administrativos  ·  Para uso interno de tu empresa</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="n"/>
+      <c r="D47" s="4" t="n"/>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="1" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="17">
-    <mergeCell ref="C22:F22"/>
+  <mergeCells count="22">
+    <mergeCell ref="C39:F39"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C32:F32"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C24:F24"/>
-    <mergeCell ref="B4:F5"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="C36:F36"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId3"/>
+  </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="1" fitToWidth="1"/>
@@ -1524,7 +1744,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>NÓMINA SIMPLIFICADA</t>
         </is>
@@ -1537,30 +1757,30 @@
       <c r="G1" s="1" t="n"/>
       <c r="H1" s="1" t="n"/>
       <c r="I1" s="1" t="n"/>
-      <c r="J1" s="23" t="inlineStr">
+      <c r="J1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="K1" s="24" t="n"/>
+      <c r="K1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Cálculo estimado por periodo (referencia administrativa, no sustituye cálculo fiscal)</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="26" t="n"/>
-      <c r="J2" s="27" t="n"/>
-      <c r="K2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="30" t="n"/>
+      <c r="I2" s="30" t="n"/>
+      <c r="J2" s="31" t="n"/>
+      <c r="K2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -1576,48 +1796,48 @@
       <c r="K3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="inlineStr">
-        <is>
-          <t>EMPRESA</t>
-        </is>
-      </c>
-      <c r="B4" s="17" t="n"/>
-      <c r="C4" s="17" t="n"/>
-      <c r="D4" s="17" t="n"/>
+      <c r="A4" s="33" t="inlineStr">
+        <is>
+          <t>EMPRESA *</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="n"/>
+      <c r="C4" s="20" t="n"/>
+      <c r="D4" s="20" t="n"/>
       <c r="E4" s="4" t="n"/>
-      <c r="F4" s="29" t="inlineStr">
-        <is>
-          <t>PERIODO</t>
-        </is>
-      </c>
-      <c r="G4" s="17" t="n"/>
-      <c r="H4" s="17" t="n"/>
-      <c r="I4" s="17" t="n"/>
+      <c r="F4" s="33" t="inlineStr">
+        <is>
+          <t>PERIODO *</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="n"/>
+      <c r="H4" s="20" t="n"/>
+      <c r="I4" s="20" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="33" t="inlineStr">
         <is>
           <t>DÍAS DEL PERIODO</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="C5" s="17" t="n"/>
-      <c r="D5" s="17" t="n"/>
+      <c r="C5" s="20" t="n"/>
+      <c r="D5" s="20" t="n"/>
       <c r="E5" s="4" t="n"/>
-      <c r="F5" s="29" t="inlineStr">
+      <c r="F5" s="33" t="inlineStr">
         <is>
           <t>% RETENCIÓN IMSS (EST.)</t>
         </is>
       </c>
-      <c r="G5" s="30" t="n">
+      <c r="G5" s="34" t="n">
         <v>0.0275</v>
       </c>
-      <c r="H5" s="17" t="n"/>
-      <c r="I5" s="17" t="n"/>
+      <c r="H5" s="20" t="n"/>
+      <c r="I5" s="20" t="n"/>
       <c r="J5" s="4" t="n"/>
       <c r="K5" s="4" t="n"/>
     </row>
@@ -1634,1679 +1854,1679 @@
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
     </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="31" t="inlineStr">
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="35" t="inlineStr">
         <is>
           <t>NO.</t>
         </is>
       </c>
-      <c r="B7" s="31" t="inlineStr">
+      <c r="B7" s="35" t="inlineStr">
         <is>
           <t>EMPLEADO</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
+      <c r="C7" s="35" t="inlineStr">
         <is>
           <t>SUELDO DIARIO</t>
         </is>
       </c>
-      <c r="D7" s="31" t="inlineStr">
+      <c r="D7" s="35" t="inlineStr">
         <is>
           <t>DÍAS TRAB.</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="35" t="inlineStr">
         <is>
           <t>HORAS EXTRA</t>
         </is>
       </c>
-      <c r="F7" s="31" t="inlineStr">
+      <c r="F7" s="35" t="inlineStr">
         <is>
           <t>SUELDO</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
+      <c r="G7" s="35" t="inlineStr">
         <is>
           <t>PAGO HORAS EXTRA</t>
         </is>
       </c>
-      <c r="H7" s="31" t="inlineStr">
+      <c r="H7" s="35" t="inlineStr">
         <is>
           <t>BONOS / OTROS</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
+      <c r="I7" s="35" t="inlineStr">
         <is>
           <t>RETENCIÓN IMSS</t>
         </is>
       </c>
-      <c r="J7" s="31" t="inlineStr">
+      <c r="J7" s="35" t="inlineStr">
         <is>
           <t>ISR RETENIDO</t>
         </is>
       </c>
-      <c r="K7" s="31" t="inlineStr">
+      <c r="K7" s="35" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="32" t="n">
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="36" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="17" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="17" t="n"/>
-      <c r="E8" s="17" t="n"/>
-      <c r="F8" s="34">
+      <c r="B8" s="37" t="n"/>
+      <c r="C8" s="38" t="n"/>
+      <c r="D8" s="37" t="n"/>
+      <c r="E8" s="37" t="n"/>
+      <c r="F8" s="39">
         <f>IF(C8="","",C8*D8)</f>
         <v/>
       </c>
-      <c r="G8" s="34">
+      <c r="G8" s="39">
         <f>IF(C8="","",E8*(C8/8)*2)</f>
         <v/>
       </c>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="34">
+      <c r="H8" s="38" t="n"/>
+      <c r="I8" s="39">
         <f>IF(C8="","",ROUND((F8+G8)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J8" s="33" t="n"/>
-      <c r="K8" s="34">
+      <c r="J8" s="38" t="n"/>
+      <c r="K8" s="39">
         <f>IF(C8="","",F8+G8+H8-I8-J8)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="32" t="n">
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
-      <c r="F9" s="34">
+      <c r="B9" s="37" t="n"/>
+      <c r="C9" s="38" t="n"/>
+      <c r="D9" s="37" t="n"/>
+      <c r="E9" s="37" t="n"/>
+      <c r="F9" s="39">
         <f>IF(C9="","",C9*D9)</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="39">
         <f>IF(C9="","",E9*(C9/8)*2)</f>
         <v/>
       </c>
-      <c r="H9" s="33" t="n"/>
-      <c r="I9" s="34">
+      <c r="H9" s="38" t="n"/>
+      <c r="I9" s="39">
         <f>IF(C9="","",ROUND((F9+G9)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J9" s="33" t="n"/>
-      <c r="K9" s="34">
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="39">
         <f>IF(C9="","",F9+G9+H9-I9-J9)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="32" t="n">
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="17" t="n"/>
-      <c r="E10" s="17" t="n"/>
-      <c r="F10" s="34">
+      <c r="B10" s="37" t="n"/>
+      <c r="C10" s="38" t="n"/>
+      <c r="D10" s="37" t="n"/>
+      <c r="E10" s="37" t="n"/>
+      <c r="F10" s="39">
         <f>IF(C10="","",C10*D10)</f>
         <v/>
       </c>
-      <c r="G10" s="34">
+      <c r="G10" s="39">
         <f>IF(C10="","",E10*(C10/8)*2)</f>
         <v/>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="34">
+      <c r="H10" s="38" t="n"/>
+      <c r="I10" s="39">
         <f>IF(C10="","",ROUND((F10+G10)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J10" s="33" t="n"/>
-      <c r="K10" s="34">
+      <c r="J10" s="38" t="n"/>
+      <c r="K10" s="39">
         <f>IF(C10="","",F10+G10+H10-I10-J10)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="32" t="n">
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="17" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="17" t="n"/>
-      <c r="E11" s="17" t="n"/>
-      <c r="F11" s="34">
+      <c r="B11" s="37" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="37" t="n"/>
+      <c r="E11" s="37" t="n"/>
+      <c r="F11" s="39">
         <f>IF(C11="","",C11*D11)</f>
         <v/>
       </c>
-      <c r="G11" s="34">
+      <c r="G11" s="39">
         <f>IF(C11="","",E11*(C11/8)*2)</f>
         <v/>
       </c>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="34">
+      <c r="H11" s="38" t="n"/>
+      <c r="I11" s="39">
         <f>IF(C11="","",ROUND((F11+G11)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J11" s="33" t="n"/>
-      <c r="K11" s="34">
+      <c r="J11" s="38" t="n"/>
+      <c r="K11" s="39">
         <f>IF(C11="","",F11+G11+H11-I11-J11)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="32" t="n">
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="17" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="17" t="n"/>
-      <c r="E12" s="17" t="n"/>
-      <c r="F12" s="34">
+      <c r="B12" s="37" t="n"/>
+      <c r="C12" s="38" t="n"/>
+      <c r="D12" s="37" t="n"/>
+      <c r="E12" s="37" t="n"/>
+      <c r="F12" s="39">
         <f>IF(C12="","",C12*D12)</f>
         <v/>
       </c>
-      <c r="G12" s="34">
+      <c r="G12" s="39">
         <f>IF(C12="","",E12*(C12/8)*2)</f>
         <v/>
       </c>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="34">
+      <c r="H12" s="38" t="n"/>
+      <c r="I12" s="39">
         <f>IF(C12="","",ROUND((F12+G12)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J12" s="33" t="n"/>
-      <c r="K12" s="34">
+      <c r="J12" s="38" t="n"/>
+      <c r="K12" s="39">
         <f>IF(C12="","",F12+G12+H12-I12-J12)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="32" t="n">
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="36" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="17" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="17" t="n"/>
-      <c r="E13" s="17" t="n"/>
-      <c r="F13" s="34">
+      <c r="B13" s="37" t="n"/>
+      <c r="C13" s="38" t="n"/>
+      <c r="D13" s="37" t="n"/>
+      <c r="E13" s="37" t="n"/>
+      <c r="F13" s="39">
         <f>IF(C13="","",C13*D13)</f>
         <v/>
       </c>
-      <c r="G13" s="34">
+      <c r="G13" s="39">
         <f>IF(C13="","",E13*(C13/8)*2)</f>
         <v/>
       </c>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="34">
+      <c r="H13" s="38" t="n"/>
+      <c r="I13" s="39">
         <f>IF(C13="","",ROUND((F13+G13)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J13" s="33" t="n"/>
-      <c r="K13" s="34">
+      <c r="J13" s="38" t="n"/>
+      <c r="K13" s="39">
         <f>IF(C13="","",F13+G13+H13-I13-J13)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="32" t="n">
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="36" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="17" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="17" t="n"/>
-      <c r="E14" s="17" t="n"/>
-      <c r="F14" s="34">
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="38" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="39">
         <f>IF(C14="","",C14*D14)</f>
         <v/>
       </c>
-      <c r="G14" s="34">
+      <c r="G14" s="39">
         <f>IF(C14="","",E14*(C14/8)*2)</f>
         <v/>
       </c>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="34">
+      <c r="H14" s="38" t="n"/>
+      <c r="I14" s="39">
         <f>IF(C14="","",ROUND((F14+G14)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J14" s="33" t="n"/>
-      <c r="K14" s="34">
+      <c r="J14" s="38" t="n"/>
+      <c r="K14" s="39">
         <f>IF(C14="","",F14+G14+H14-I14-J14)</f>
         <v/>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="32" t="n">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="36" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="17" t="n"/>
-      <c r="E15" s="17" t="n"/>
-      <c r="F15" s="34">
+      <c r="B15" s="37" t="n"/>
+      <c r="C15" s="38" t="n"/>
+      <c r="D15" s="37" t="n"/>
+      <c r="E15" s="37" t="n"/>
+      <c r="F15" s="39">
         <f>IF(C15="","",C15*D15)</f>
         <v/>
       </c>
-      <c r="G15" s="34">
+      <c r="G15" s="39">
         <f>IF(C15="","",E15*(C15/8)*2)</f>
         <v/>
       </c>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="34">
+      <c r="H15" s="38" t="n"/>
+      <c r="I15" s="39">
         <f>IF(C15="","",ROUND((F15+G15)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J15" s="33" t="n"/>
-      <c r="K15" s="34">
+      <c r="J15" s="38" t="n"/>
+      <c r="K15" s="39">
         <f>IF(C15="","",F15+G15+H15-I15-J15)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="32" t="n">
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="36" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="34">
+      <c r="B16" s="37" t="n"/>
+      <c r="C16" s="38" t="n"/>
+      <c r="D16" s="37" t="n"/>
+      <c r="E16" s="37" t="n"/>
+      <c r="F16" s="39">
         <f>IF(C16="","",C16*D16)</f>
         <v/>
       </c>
-      <c r="G16" s="34">
+      <c r="G16" s="39">
         <f>IF(C16="","",E16*(C16/8)*2)</f>
         <v/>
       </c>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="34">
+      <c r="H16" s="38" t="n"/>
+      <c r="I16" s="39">
         <f>IF(C16="","",ROUND((F16+G16)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J16" s="33" t="n"/>
-      <c r="K16" s="34">
+      <c r="J16" s="38" t="n"/>
+      <c r="K16" s="39">
         <f>IF(C16="","",F16+G16+H16-I16-J16)</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="32" t="n">
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="36" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-      <c r="F17" s="34">
+      <c r="B17" s="37" t="n"/>
+      <c r="C17" s="38" t="n"/>
+      <c r="D17" s="37" t="n"/>
+      <c r="E17" s="37" t="n"/>
+      <c r="F17" s="39">
         <f>IF(C17="","",C17*D17)</f>
         <v/>
       </c>
-      <c r="G17" s="34">
+      <c r="G17" s="39">
         <f>IF(C17="","",E17*(C17/8)*2)</f>
         <v/>
       </c>
-      <c r="H17" s="33" t="n"/>
-      <c r="I17" s="34">
+      <c r="H17" s="38" t="n"/>
+      <c r="I17" s="39">
         <f>IF(C17="","",ROUND((F17+G17)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J17" s="33" t="n"/>
-      <c r="K17" s="34">
+      <c r="J17" s="38" t="n"/>
+      <c r="K17" s="39">
         <f>IF(C17="","",F17+G17+H17-I17-J17)</f>
         <v/>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="32" t="n">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="36" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="33" t="n"/>
-      <c r="D18" s="17" t="n"/>
-      <c r="E18" s="17" t="n"/>
-      <c r="F18" s="34">
+      <c r="B18" s="37" t="n"/>
+      <c r="C18" s="38" t="n"/>
+      <c r="D18" s="37" t="n"/>
+      <c r="E18" s="37" t="n"/>
+      <c r="F18" s="39">
         <f>IF(C18="","",C18*D18)</f>
         <v/>
       </c>
-      <c r="G18" s="34">
+      <c r="G18" s="39">
         <f>IF(C18="","",E18*(C18/8)*2)</f>
         <v/>
       </c>
-      <c r="H18" s="33" t="n"/>
-      <c r="I18" s="34">
+      <c r="H18" s="38" t="n"/>
+      <c r="I18" s="39">
         <f>IF(C18="","",ROUND((F18+G18)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J18" s="33" t="n"/>
-      <c r="K18" s="34">
+      <c r="J18" s="38" t="n"/>
+      <c r="K18" s="39">
         <f>IF(C18="","",F18+G18+H18-I18-J18)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="32" t="n">
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="36" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="17" t="n"/>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="34">
+      <c r="B19" s="37" t="n"/>
+      <c r="C19" s="38" t="n"/>
+      <c r="D19" s="37" t="n"/>
+      <c r="E19" s="37" t="n"/>
+      <c r="F19" s="39">
         <f>IF(C19="","",C19*D19)</f>
         <v/>
       </c>
-      <c r="G19" s="34">
+      <c r="G19" s="39">
         <f>IF(C19="","",E19*(C19/8)*2)</f>
         <v/>
       </c>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="34">
+      <c r="H19" s="38" t="n"/>
+      <c r="I19" s="39">
         <f>IF(C19="","",ROUND((F19+G19)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J19" s="33" t="n"/>
-      <c r="K19" s="34">
+      <c r="J19" s="38" t="n"/>
+      <c r="K19" s="39">
         <f>IF(C19="","",F19+G19+H19-I19-J19)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="32" t="n">
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="36" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="33" t="n"/>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="34">
+      <c r="B20" s="37" t="n"/>
+      <c r="C20" s="38" t="n"/>
+      <c r="D20" s="37" t="n"/>
+      <c r="E20" s="37" t="n"/>
+      <c r="F20" s="39">
         <f>IF(C20="","",C20*D20)</f>
         <v/>
       </c>
-      <c r="G20" s="34">
+      <c r="G20" s="39">
         <f>IF(C20="","",E20*(C20/8)*2)</f>
         <v/>
       </c>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="34">
+      <c r="H20" s="38" t="n"/>
+      <c r="I20" s="39">
         <f>IF(C20="","",ROUND((F20+G20)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J20" s="33" t="n"/>
-      <c r="K20" s="34">
+      <c r="J20" s="38" t="n"/>
+      <c r="K20" s="39">
         <f>IF(C20="","",F20+G20+H20-I20-J20)</f>
         <v/>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="32" t="n">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="36" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="17" t="n"/>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="34">
+      <c r="B21" s="37" t="n"/>
+      <c r="C21" s="38" t="n"/>
+      <c r="D21" s="37" t="n"/>
+      <c r="E21" s="37" t="n"/>
+      <c r="F21" s="39">
         <f>IF(C21="","",C21*D21)</f>
         <v/>
       </c>
-      <c r="G21" s="34">
+      <c r="G21" s="39">
         <f>IF(C21="","",E21*(C21/8)*2)</f>
         <v/>
       </c>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="34">
+      <c r="H21" s="38" t="n"/>
+      <c r="I21" s="39">
         <f>IF(C21="","",ROUND((F21+G21)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J21" s="33" t="n"/>
-      <c r="K21" s="34">
+      <c r="J21" s="38" t="n"/>
+      <c r="K21" s="39">
         <f>IF(C21="","",F21+G21+H21-I21-J21)</f>
         <v/>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="32" t="n">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="36" t="n">
         <v>15</v>
       </c>
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="17" t="n"/>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="34">
+      <c r="B22" s="37" t="n"/>
+      <c r="C22" s="38" t="n"/>
+      <c r="D22" s="37" t="n"/>
+      <c r="E22" s="37" t="n"/>
+      <c r="F22" s="39">
         <f>IF(C22="","",C22*D22)</f>
         <v/>
       </c>
-      <c r="G22" s="34">
+      <c r="G22" s="39">
         <f>IF(C22="","",E22*(C22/8)*2)</f>
         <v/>
       </c>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="34">
+      <c r="H22" s="38" t="n"/>
+      <c r="I22" s="39">
         <f>IF(C22="","",ROUND((F22+G22)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J22" s="33" t="n"/>
-      <c r="K22" s="34">
+      <c r="J22" s="38" t="n"/>
+      <c r="K22" s="39">
         <f>IF(C22="","",F22+G22+H22-I22-J22)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="32" t="n">
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="36" t="n">
         <v>16</v>
       </c>
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="17" t="n"/>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="34">
+      <c r="B23" s="37" t="n"/>
+      <c r="C23" s="38" t="n"/>
+      <c r="D23" s="37" t="n"/>
+      <c r="E23" s="37" t="n"/>
+      <c r="F23" s="39">
         <f>IF(C23="","",C23*D23)</f>
         <v/>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="39">
         <f>IF(C23="","",E23*(C23/8)*2)</f>
         <v/>
       </c>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="34">
+      <c r="H23" s="38" t="n"/>
+      <c r="I23" s="39">
         <f>IF(C23="","",ROUND((F23+G23)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J23" s="33" t="n"/>
-      <c r="K23" s="34">
+      <c r="J23" s="38" t="n"/>
+      <c r="K23" s="39">
         <f>IF(C23="","",F23+G23+H23-I23-J23)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="32" t="n">
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="36" t="n">
         <v>17</v>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="34">
+      <c r="B24" s="37" t="n"/>
+      <c r="C24" s="38" t="n"/>
+      <c r="D24" s="37" t="n"/>
+      <c r="E24" s="37" t="n"/>
+      <c r="F24" s="39">
         <f>IF(C24="","",C24*D24)</f>
         <v/>
       </c>
-      <c r="G24" s="34">
+      <c r="G24" s="39">
         <f>IF(C24="","",E24*(C24/8)*2)</f>
         <v/>
       </c>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="34">
+      <c r="H24" s="38" t="n"/>
+      <c r="I24" s="39">
         <f>IF(C24="","",ROUND((F24+G24)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J24" s="33" t="n"/>
-      <c r="K24" s="34">
+      <c r="J24" s="38" t="n"/>
+      <c r="K24" s="39">
         <f>IF(C24="","",F24+G24+H24-I24-J24)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="32" t="n">
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="36" t="n">
         <v>18</v>
       </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="34">
+      <c r="B25" s="37" t="n"/>
+      <c r="C25" s="38" t="n"/>
+      <c r="D25" s="37" t="n"/>
+      <c r="E25" s="37" t="n"/>
+      <c r="F25" s="39">
         <f>IF(C25="","",C25*D25)</f>
         <v/>
       </c>
-      <c r="G25" s="34">
+      <c r="G25" s="39">
         <f>IF(C25="","",E25*(C25/8)*2)</f>
         <v/>
       </c>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="34">
+      <c r="H25" s="38" t="n"/>
+      <c r="I25" s="39">
         <f>IF(C25="","",ROUND((F25+G25)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J25" s="33" t="n"/>
-      <c r="K25" s="34">
+      <c r="J25" s="38" t="n"/>
+      <c r="K25" s="39">
         <f>IF(C25="","",F25+G25+H25-I25-J25)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="32" t="n">
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="36" t="n">
         <v>19</v>
       </c>
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="33" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="34">
+      <c r="B26" s="37" t="n"/>
+      <c r="C26" s="38" t="n"/>
+      <c r="D26" s="37" t="n"/>
+      <c r="E26" s="37" t="n"/>
+      <c r="F26" s="39">
         <f>IF(C26="","",C26*D26)</f>
         <v/>
       </c>
-      <c r="G26" s="34">
+      <c r="G26" s="39">
         <f>IF(C26="","",E26*(C26/8)*2)</f>
         <v/>
       </c>
-      <c r="H26" s="33" t="n"/>
-      <c r="I26" s="34">
+      <c r="H26" s="38" t="n"/>
+      <c r="I26" s="39">
         <f>IF(C26="","",ROUND((F26+G26)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J26" s="33" t="n"/>
-      <c r="K26" s="34">
+      <c r="J26" s="38" t="n"/>
+      <c r="K26" s="39">
         <f>IF(C26="","",F26+G26+H26-I26-J26)</f>
         <v/>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="32" t="n">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="36" t="n">
         <v>20</v>
       </c>
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="34">
+      <c r="B27" s="37" t="n"/>
+      <c r="C27" s="38" t="n"/>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="37" t="n"/>
+      <c r="F27" s="39">
         <f>IF(C27="","",C27*D27)</f>
         <v/>
       </c>
-      <c r="G27" s="34">
+      <c r="G27" s="39">
         <f>IF(C27="","",E27*(C27/8)*2)</f>
         <v/>
       </c>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="34">
+      <c r="H27" s="38" t="n"/>
+      <c r="I27" s="39">
         <f>IF(C27="","",ROUND((F27+G27)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J27" s="33" t="n"/>
-      <c r="K27" s="34">
+      <c r="J27" s="38" t="n"/>
+      <c r="K27" s="39">
         <f>IF(C27="","",F27+G27+H27-I27-J27)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="32" t="n">
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="36" t="n">
         <v>21</v>
       </c>
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="34">
+      <c r="B28" s="37" t="n"/>
+      <c r="C28" s="38" t="n"/>
+      <c r="D28" s="37" t="n"/>
+      <c r="E28" s="37" t="n"/>
+      <c r="F28" s="39">
         <f>IF(C28="","",C28*D28)</f>
         <v/>
       </c>
-      <c r="G28" s="34">
+      <c r="G28" s="39">
         <f>IF(C28="","",E28*(C28/8)*2)</f>
         <v/>
       </c>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="34">
+      <c r="H28" s="38" t="n"/>
+      <c r="I28" s="39">
         <f>IF(C28="","",ROUND((F28+G28)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J28" s="33" t="n"/>
-      <c r="K28" s="34">
+      <c r="J28" s="38" t="n"/>
+      <c r="K28" s="39">
         <f>IF(C28="","",F28+G28+H28-I28-J28)</f>
         <v/>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="32" t="n">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="36" t="n">
         <v>22</v>
       </c>
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="34">
+      <c r="B29" s="37" t="n"/>
+      <c r="C29" s="38" t="n"/>
+      <c r="D29" s="37" t="n"/>
+      <c r="E29" s="37" t="n"/>
+      <c r="F29" s="39">
         <f>IF(C29="","",C29*D29)</f>
         <v/>
       </c>
-      <c r="G29" s="34">
+      <c r="G29" s="39">
         <f>IF(C29="","",E29*(C29/8)*2)</f>
         <v/>
       </c>
-      <c r="H29" s="33" t="n"/>
-      <c r="I29" s="34">
+      <c r="H29" s="38" t="n"/>
+      <c r="I29" s="39">
         <f>IF(C29="","",ROUND((F29+G29)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J29" s="33" t="n"/>
-      <c r="K29" s="34">
+      <c r="J29" s="38" t="n"/>
+      <c r="K29" s="39">
         <f>IF(C29="","",F29+G29+H29-I29-J29)</f>
         <v/>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="32" t="n">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="36" t="n">
         <v>23</v>
       </c>
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="33" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="34">
+      <c r="B30" s="37" t="n"/>
+      <c r="C30" s="38" t="n"/>
+      <c r="D30" s="37" t="n"/>
+      <c r="E30" s="37" t="n"/>
+      <c r="F30" s="39">
         <f>IF(C30="","",C30*D30)</f>
         <v/>
       </c>
-      <c r="G30" s="34">
+      <c r="G30" s="39">
         <f>IF(C30="","",E30*(C30/8)*2)</f>
         <v/>
       </c>
-      <c r="H30" s="33" t="n"/>
-      <c r="I30" s="34">
+      <c r="H30" s="38" t="n"/>
+      <c r="I30" s="39">
         <f>IF(C30="","",ROUND((F30+G30)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J30" s="33" t="n"/>
-      <c r="K30" s="34">
+      <c r="J30" s="38" t="n"/>
+      <c r="K30" s="39">
         <f>IF(C30="","",F30+G30+H30-I30-J30)</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="32" t="n">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="36" t="n">
         <v>24</v>
       </c>
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="34">
+      <c r="B31" s="37" t="n"/>
+      <c r="C31" s="38" t="n"/>
+      <c r="D31" s="37" t="n"/>
+      <c r="E31" s="37" t="n"/>
+      <c r="F31" s="39">
         <f>IF(C31="","",C31*D31)</f>
         <v/>
       </c>
-      <c r="G31" s="34">
+      <c r="G31" s="39">
         <f>IF(C31="","",E31*(C31/8)*2)</f>
         <v/>
       </c>
-      <c r="H31" s="33" t="n"/>
-      <c r="I31" s="34">
+      <c r="H31" s="38" t="n"/>
+      <c r="I31" s="39">
         <f>IF(C31="","",ROUND((F31+G31)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J31" s="33" t="n"/>
-      <c r="K31" s="34">
+      <c r="J31" s="38" t="n"/>
+      <c r="K31" s="39">
         <f>IF(C31="","",F31+G31+H31-I31-J31)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="32" t="n">
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="36" t="n">
         <v>25</v>
       </c>
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="33" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="34">
+      <c r="B32" s="37" t="n"/>
+      <c r="C32" s="38" t="n"/>
+      <c r="D32" s="37" t="n"/>
+      <c r="E32" s="37" t="n"/>
+      <c r="F32" s="39">
         <f>IF(C32="","",C32*D32)</f>
         <v/>
       </c>
-      <c r="G32" s="34">
+      <c r="G32" s="39">
         <f>IF(C32="","",E32*(C32/8)*2)</f>
         <v/>
       </c>
-      <c r="H32" s="33" t="n"/>
-      <c r="I32" s="34">
+      <c r="H32" s="38" t="n"/>
+      <c r="I32" s="39">
         <f>IF(C32="","",ROUND((F32+G32)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J32" s="33" t="n"/>
-      <c r="K32" s="34">
+      <c r="J32" s="38" t="n"/>
+      <c r="K32" s="39">
         <f>IF(C32="","",F32+G32+H32-I32-J32)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="32" t="n">
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="36" t="n">
         <v>26</v>
       </c>
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="n"/>
-      <c r="F33" s="34">
+      <c r="B33" s="37" t="n"/>
+      <c r="C33" s="38" t="n"/>
+      <c r="D33" s="37" t="n"/>
+      <c r="E33" s="37" t="n"/>
+      <c r="F33" s="39">
         <f>IF(C33="","",C33*D33)</f>
         <v/>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="39">
         <f>IF(C33="","",E33*(C33/8)*2)</f>
         <v/>
       </c>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="34">
+      <c r="H33" s="38" t="n"/>
+      <c r="I33" s="39">
         <f>IF(C33="","",ROUND((F33+G33)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J33" s="33" t="n"/>
-      <c r="K33" s="34">
+      <c r="J33" s="38" t="n"/>
+      <c r="K33" s="39">
         <f>IF(C33="","",F33+G33+H33-I33-J33)</f>
         <v/>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="32" t="n">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="36" t="n">
         <v>27</v>
       </c>
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="n"/>
-      <c r="F34" s="34">
+      <c r="B34" s="37" t="n"/>
+      <c r="C34" s="38" t="n"/>
+      <c r="D34" s="37" t="n"/>
+      <c r="E34" s="37" t="n"/>
+      <c r="F34" s="39">
         <f>IF(C34="","",C34*D34)</f>
         <v/>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="39">
         <f>IF(C34="","",E34*(C34/8)*2)</f>
         <v/>
       </c>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="34">
+      <c r="H34" s="38" t="n"/>
+      <c r="I34" s="39">
         <f>IF(C34="","",ROUND((F34+G34)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J34" s="33" t="n"/>
-      <c r="K34" s="34">
+      <c r="J34" s="38" t="n"/>
+      <c r="K34" s="39">
         <f>IF(C34="","",F34+G34+H34-I34-J34)</f>
         <v/>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="32" t="n">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="36" t="n">
         <v>28</v>
       </c>
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="n"/>
-      <c r="F35" s="34">
+      <c r="B35" s="37" t="n"/>
+      <c r="C35" s="38" t="n"/>
+      <c r="D35" s="37" t="n"/>
+      <c r="E35" s="37" t="n"/>
+      <c r="F35" s="39">
         <f>IF(C35="","",C35*D35)</f>
         <v/>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="39">
         <f>IF(C35="","",E35*(C35/8)*2)</f>
         <v/>
       </c>
-      <c r="H35" s="33" t="n"/>
-      <c r="I35" s="34">
+      <c r="H35" s="38" t="n"/>
+      <c r="I35" s="39">
         <f>IF(C35="","",ROUND((F35+G35)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J35" s="33" t="n"/>
-      <c r="K35" s="34">
+      <c r="J35" s="38" t="n"/>
+      <c r="K35" s="39">
         <f>IF(C35="","",F35+G35+H35-I35-J35)</f>
         <v/>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="32" t="n">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="36" t="n">
         <v>29</v>
       </c>
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="34">
+      <c r="B36" s="37" t="n"/>
+      <c r="C36" s="38" t="n"/>
+      <c r="D36" s="37" t="n"/>
+      <c r="E36" s="37" t="n"/>
+      <c r="F36" s="39">
         <f>IF(C36="","",C36*D36)</f>
         <v/>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="39">
         <f>IF(C36="","",E36*(C36/8)*2)</f>
         <v/>
       </c>
-      <c r="H36" s="33" t="n"/>
-      <c r="I36" s="34">
+      <c r="H36" s="38" t="n"/>
+      <c r="I36" s="39">
         <f>IF(C36="","",ROUND((F36+G36)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J36" s="33" t="n"/>
-      <c r="K36" s="34">
+      <c r="J36" s="38" t="n"/>
+      <c r="K36" s="39">
         <f>IF(C36="","",F36+G36+H36-I36-J36)</f>
         <v/>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="32" t="n">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="34">
+      <c r="B37" s="37" t="n"/>
+      <c r="C37" s="38" t="n"/>
+      <c r="D37" s="37" t="n"/>
+      <c r="E37" s="37" t="n"/>
+      <c r="F37" s="39">
         <f>IF(C37="","",C37*D37)</f>
         <v/>
       </c>
-      <c r="G37" s="34">
+      <c r="G37" s="39">
         <f>IF(C37="","",E37*(C37/8)*2)</f>
         <v/>
       </c>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="34">
+      <c r="H37" s="38" t="n"/>
+      <c r="I37" s="39">
         <f>IF(C37="","",ROUND((F37+G37)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J37" s="33" t="n"/>
-      <c r="K37" s="34">
+      <c r="J37" s="38" t="n"/>
+      <c r="K37" s="39">
         <f>IF(C37="","",F37+G37+H37-I37-J37)</f>
         <v/>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="32" t="n">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="36" t="n">
         <v>31</v>
       </c>
-      <c r="B38" s="17" t="n"/>
-      <c r="C38" s="33" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="34">
+      <c r="B38" s="37" t="n"/>
+      <c r="C38" s="38" t="n"/>
+      <c r="D38" s="37" t="n"/>
+      <c r="E38" s="37" t="n"/>
+      <c r="F38" s="39">
         <f>IF(C38="","",C38*D38)</f>
         <v/>
       </c>
-      <c r="G38" s="34">
+      <c r="G38" s="39">
         <f>IF(C38="","",E38*(C38/8)*2)</f>
         <v/>
       </c>
-      <c r="H38" s="33" t="n"/>
-      <c r="I38" s="34">
+      <c r="H38" s="38" t="n"/>
+      <c r="I38" s="39">
         <f>IF(C38="","",ROUND((F38+G38)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J38" s="33" t="n"/>
-      <c r="K38" s="34">
+      <c r="J38" s="38" t="n"/>
+      <c r="K38" s="39">
         <f>IF(C38="","",F38+G38+H38-I38-J38)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="32" t="n">
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="36" t="n">
         <v>32</v>
       </c>
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="34">
+      <c r="B39" s="37" t="n"/>
+      <c r="C39" s="38" t="n"/>
+      <c r="D39" s="37" t="n"/>
+      <c r="E39" s="37" t="n"/>
+      <c r="F39" s="39">
         <f>IF(C39="","",C39*D39)</f>
         <v/>
       </c>
-      <c r="G39" s="34">
+      <c r="G39" s="39">
         <f>IF(C39="","",E39*(C39/8)*2)</f>
         <v/>
       </c>
-      <c r="H39" s="33" t="n"/>
-      <c r="I39" s="34">
+      <c r="H39" s="38" t="n"/>
+      <c r="I39" s="39">
         <f>IF(C39="","",ROUND((F39+G39)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J39" s="33" t="n"/>
-      <c r="K39" s="34">
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="39">
         <f>IF(C39="","",F39+G39+H39-I39-J39)</f>
         <v/>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="32" t="n">
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="36" t="n">
         <v>33</v>
       </c>
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="33" t="n"/>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="n"/>
-      <c r="F40" s="34">
+      <c r="B40" s="37" t="n"/>
+      <c r="C40" s="38" t="n"/>
+      <c r="D40" s="37" t="n"/>
+      <c r="E40" s="37" t="n"/>
+      <c r="F40" s="39">
         <f>IF(C40="","",C40*D40)</f>
         <v/>
       </c>
-      <c r="G40" s="34">
+      <c r="G40" s="39">
         <f>IF(C40="","",E40*(C40/8)*2)</f>
         <v/>
       </c>
-      <c r="H40" s="33" t="n"/>
-      <c r="I40" s="34">
+      <c r="H40" s="38" t="n"/>
+      <c r="I40" s="39">
         <f>IF(C40="","",ROUND((F40+G40)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J40" s="33" t="n"/>
-      <c r="K40" s="34">
+      <c r="J40" s="38" t="n"/>
+      <c r="K40" s="39">
         <f>IF(C40="","",F40+G40+H40-I40-J40)</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="32" t="n">
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="34">
+      <c r="B41" s="37" t="n"/>
+      <c r="C41" s="38" t="n"/>
+      <c r="D41" s="37" t="n"/>
+      <c r="E41" s="37" t="n"/>
+      <c r="F41" s="39">
         <f>IF(C41="","",C41*D41)</f>
         <v/>
       </c>
-      <c r="G41" s="34">
+      <c r="G41" s="39">
         <f>IF(C41="","",E41*(C41/8)*2)</f>
         <v/>
       </c>
-      <c r="H41" s="33" t="n"/>
-      <c r="I41" s="34">
+      <c r="H41" s="38" t="n"/>
+      <c r="I41" s="39">
         <f>IF(C41="","",ROUND((F41+G41)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J41" s="33" t="n"/>
-      <c r="K41" s="34">
+      <c r="J41" s="38" t="n"/>
+      <c r="K41" s="39">
         <f>IF(C41="","",F41+G41+H41-I41-J41)</f>
         <v/>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="32" t="n">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="36" t="n">
         <v>35</v>
       </c>
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="33" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="34">
+      <c r="B42" s="37" t="n"/>
+      <c r="C42" s="38" t="n"/>
+      <c r="D42" s="37" t="n"/>
+      <c r="E42" s="37" t="n"/>
+      <c r="F42" s="39">
         <f>IF(C42="","",C42*D42)</f>
         <v/>
       </c>
-      <c r="G42" s="34">
+      <c r="G42" s="39">
         <f>IF(C42="","",E42*(C42/8)*2)</f>
         <v/>
       </c>
-      <c r="H42" s="33" t="n"/>
-      <c r="I42" s="34">
+      <c r="H42" s="38" t="n"/>
+      <c r="I42" s="39">
         <f>IF(C42="","",ROUND((F42+G42)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J42" s="33" t="n"/>
-      <c r="K42" s="34">
+      <c r="J42" s="38" t="n"/>
+      <c r="K42" s="39">
         <f>IF(C42="","",F42+G42+H42-I42-J42)</f>
         <v/>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="32" t="n">
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="36" t="n">
         <v>36</v>
       </c>
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="34">
+      <c r="B43" s="37" t="n"/>
+      <c r="C43" s="38" t="n"/>
+      <c r="D43" s="37" t="n"/>
+      <c r="E43" s="37" t="n"/>
+      <c r="F43" s="39">
         <f>IF(C43="","",C43*D43)</f>
         <v/>
       </c>
-      <c r="G43" s="34">
+      <c r="G43" s="39">
         <f>IF(C43="","",E43*(C43/8)*2)</f>
         <v/>
       </c>
-      <c r="H43" s="33" t="n"/>
-      <c r="I43" s="34">
+      <c r="H43" s="38" t="n"/>
+      <c r="I43" s="39">
         <f>IF(C43="","",ROUND((F43+G43)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J43" s="33" t="n"/>
-      <c r="K43" s="34">
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="39">
         <f>IF(C43="","",F43+G43+H43-I43-J43)</f>
         <v/>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="32" t="n">
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="36" t="n">
         <v>37</v>
       </c>
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="33" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
-      <c r="F44" s="34">
+      <c r="B44" s="37" t="n"/>
+      <c r="C44" s="38" t="n"/>
+      <c r="D44" s="37" t="n"/>
+      <c r="E44" s="37" t="n"/>
+      <c r="F44" s="39">
         <f>IF(C44="","",C44*D44)</f>
         <v/>
       </c>
-      <c r="G44" s="34">
+      <c r="G44" s="39">
         <f>IF(C44="","",E44*(C44/8)*2)</f>
         <v/>
       </c>
-      <c r="H44" s="33" t="n"/>
-      <c r="I44" s="34">
+      <c r="H44" s="38" t="n"/>
+      <c r="I44" s="39">
         <f>IF(C44="","",ROUND((F44+G44)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J44" s="33" t="n"/>
-      <c r="K44" s="34">
+      <c r="J44" s="38" t="n"/>
+      <c r="K44" s="39">
         <f>IF(C44="","",F44+G44+H44-I44-J44)</f>
         <v/>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="32" t="n">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="36" t="n">
         <v>38</v>
       </c>
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="33" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="34">
+      <c r="B45" s="37" t="n"/>
+      <c r="C45" s="38" t="n"/>
+      <c r="D45" s="37" t="n"/>
+      <c r="E45" s="37" t="n"/>
+      <c r="F45" s="39">
         <f>IF(C45="","",C45*D45)</f>
         <v/>
       </c>
-      <c r="G45" s="34">
+      <c r="G45" s="39">
         <f>IF(C45="","",E45*(C45/8)*2)</f>
         <v/>
       </c>
-      <c r="H45" s="33" t="n"/>
-      <c r="I45" s="34">
+      <c r="H45" s="38" t="n"/>
+      <c r="I45" s="39">
         <f>IF(C45="","",ROUND((F45+G45)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J45" s="33" t="n"/>
-      <c r="K45" s="34">
+      <c r="J45" s="38" t="n"/>
+      <c r="K45" s="39">
         <f>IF(C45="","",F45+G45+H45-I45-J45)</f>
         <v/>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="32" t="n">
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="36" t="n">
         <v>39</v>
       </c>
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="33" t="n"/>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="34">
+      <c r="B46" s="37" t="n"/>
+      <c r="C46" s="38" t="n"/>
+      <c r="D46" s="37" t="n"/>
+      <c r="E46" s="37" t="n"/>
+      <c r="F46" s="39">
         <f>IF(C46="","",C46*D46)</f>
         <v/>
       </c>
-      <c r="G46" s="34">
+      <c r="G46" s="39">
         <f>IF(C46="","",E46*(C46/8)*2)</f>
         <v/>
       </c>
-      <c r="H46" s="33" t="n"/>
-      <c r="I46" s="34">
+      <c r="H46" s="38" t="n"/>
+      <c r="I46" s="39">
         <f>IF(C46="","",ROUND((F46+G46)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J46" s="33" t="n"/>
-      <c r="K46" s="34">
+      <c r="J46" s="38" t="n"/>
+      <c r="K46" s="39">
         <f>IF(C46="","",F46+G46+H46-I46-J46)</f>
         <v/>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="32" t="n">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="33" t="n"/>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="34">
+      <c r="B47" s="37" t="n"/>
+      <c r="C47" s="38" t="n"/>
+      <c r="D47" s="37" t="n"/>
+      <c r="E47" s="37" t="n"/>
+      <c r="F47" s="39">
         <f>IF(C47="","",C47*D47)</f>
         <v/>
       </c>
-      <c r="G47" s="34">
+      <c r="G47" s="39">
         <f>IF(C47="","",E47*(C47/8)*2)</f>
         <v/>
       </c>
-      <c r="H47" s="33" t="n"/>
-      <c r="I47" s="34">
+      <c r="H47" s="38" t="n"/>
+      <c r="I47" s="39">
         <f>IF(C47="","",ROUND((F47+G47)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J47" s="33" t="n"/>
-      <c r="K47" s="34">
+      <c r="J47" s="38" t="n"/>
+      <c r="K47" s="39">
         <f>IF(C47="","",F47+G47+H47-I47-J47)</f>
         <v/>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="32" t="n">
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="36" t="n">
         <v>41</v>
       </c>
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="33" t="n"/>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="34">
+      <c r="B48" s="37" t="n"/>
+      <c r="C48" s="38" t="n"/>
+      <c r="D48" s="37" t="n"/>
+      <c r="E48" s="37" t="n"/>
+      <c r="F48" s="39">
         <f>IF(C48="","",C48*D48)</f>
         <v/>
       </c>
-      <c r="G48" s="34">
+      <c r="G48" s="39">
         <f>IF(C48="","",E48*(C48/8)*2)</f>
         <v/>
       </c>
-      <c r="H48" s="33" t="n"/>
-      <c r="I48" s="34">
+      <c r="H48" s="38" t="n"/>
+      <c r="I48" s="39">
         <f>IF(C48="","",ROUND((F48+G48)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J48" s="33" t="n"/>
-      <c r="K48" s="34">
+      <c r="J48" s="38" t="n"/>
+      <c r="K48" s="39">
         <f>IF(C48="","",F48+G48+H48-I48-J48)</f>
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="32" t="n">
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="36" t="n">
         <v>42</v>
       </c>
-      <c r="B49" s="17" t="n"/>
-      <c r="C49" s="33" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="34">
+      <c r="B49" s="37" t="n"/>
+      <c r="C49" s="38" t="n"/>
+      <c r="D49" s="37" t="n"/>
+      <c r="E49" s="37" t="n"/>
+      <c r="F49" s="39">
         <f>IF(C49="","",C49*D49)</f>
         <v/>
       </c>
-      <c r="G49" s="34">
+      <c r="G49" s="39">
         <f>IF(C49="","",E49*(C49/8)*2)</f>
         <v/>
       </c>
-      <c r="H49" s="33" t="n"/>
-      <c r="I49" s="34">
+      <c r="H49" s="38" t="n"/>
+      <c r="I49" s="39">
         <f>IF(C49="","",ROUND((F49+G49)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J49" s="33" t="n"/>
-      <c r="K49" s="34">
+      <c r="J49" s="38" t="n"/>
+      <c r="K49" s="39">
         <f>IF(C49="","",F49+G49+H49-I49-J49)</f>
         <v/>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="32" t="n">
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="36" t="n">
         <v>43</v>
       </c>
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="33" t="n"/>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="F50" s="34">
+      <c r="B50" s="37" t="n"/>
+      <c r="C50" s="38" t="n"/>
+      <c r="D50" s="37" t="n"/>
+      <c r="E50" s="37" t="n"/>
+      <c r="F50" s="39">
         <f>IF(C50="","",C50*D50)</f>
         <v/>
       </c>
-      <c r="G50" s="34">
+      <c r="G50" s="39">
         <f>IF(C50="","",E50*(C50/8)*2)</f>
         <v/>
       </c>
-      <c r="H50" s="33" t="n"/>
-      <c r="I50" s="34">
+      <c r="H50" s="38" t="n"/>
+      <c r="I50" s="39">
         <f>IF(C50="","",ROUND((F50+G50)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J50" s="33" t="n"/>
-      <c r="K50" s="34">
+      <c r="J50" s="38" t="n"/>
+      <c r="K50" s="39">
         <f>IF(C50="","",F50+G50+H50-I50-J50)</f>
         <v/>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="32" t="n">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="36" t="n">
         <v>44</v>
       </c>
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="33" t="n"/>
-      <c r="D51" s="17" t="n"/>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="34">
+      <c r="B51" s="37" t="n"/>
+      <c r="C51" s="38" t="n"/>
+      <c r="D51" s="37" t="n"/>
+      <c r="E51" s="37" t="n"/>
+      <c r="F51" s="39">
         <f>IF(C51="","",C51*D51)</f>
         <v/>
       </c>
-      <c r="G51" s="34">
+      <c r="G51" s="39">
         <f>IF(C51="","",E51*(C51/8)*2)</f>
         <v/>
       </c>
-      <c r="H51" s="33" t="n"/>
-      <c r="I51" s="34">
+      <c r="H51" s="38" t="n"/>
+      <c r="I51" s="39">
         <f>IF(C51="","",ROUND((F51+G51)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J51" s="33" t="n"/>
-      <c r="K51" s="34">
+      <c r="J51" s="38" t="n"/>
+      <c r="K51" s="39">
         <f>IF(C51="","",F51+G51+H51-I51-J51)</f>
         <v/>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="32" t="n">
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="36" t="n">
         <v>45</v>
       </c>
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="33" t="n"/>
-      <c r="D52" s="17" t="n"/>
-      <c r="E52" s="17" t="n"/>
-      <c r="F52" s="34">
+      <c r="B52" s="37" t="n"/>
+      <c r="C52" s="38" t="n"/>
+      <c r="D52" s="37" t="n"/>
+      <c r="E52" s="37" t="n"/>
+      <c r="F52" s="39">
         <f>IF(C52="","",C52*D52)</f>
         <v/>
       </c>
-      <c r="G52" s="34">
+      <c r="G52" s="39">
         <f>IF(C52="","",E52*(C52/8)*2)</f>
         <v/>
       </c>
-      <c r="H52" s="33" t="n"/>
-      <c r="I52" s="34">
+      <c r="H52" s="38" t="n"/>
+      <c r="I52" s="39">
         <f>IF(C52="","",ROUND((F52+G52)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J52" s="33" t="n"/>
-      <c r="K52" s="34">
+      <c r="J52" s="38" t="n"/>
+      <c r="K52" s="39">
         <f>IF(C52="","",F52+G52+H52-I52-J52)</f>
         <v/>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="32" t="n">
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="36" t="n">
         <v>46</v>
       </c>
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="33" t="n"/>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="34">
+      <c r="B53" s="37" t="n"/>
+      <c r="C53" s="38" t="n"/>
+      <c r="D53" s="37" t="n"/>
+      <c r="E53" s="37" t="n"/>
+      <c r="F53" s="39">
         <f>IF(C53="","",C53*D53)</f>
         <v/>
       </c>
-      <c r="G53" s="34">
+      <c r="G53" s="39">
         <f>IF(C53="","",E53*(C53/8)*2)</f>
         <v/>
       </c>
-      <c r="H53" s="33" t="n"/>
-      <c r="I53" s="34">
+      <c r="H53" s="38" t="n"/>
+      <c r="I53" s="39">
         <f>IF(C53="","",ROUND((F53+G53)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J53" s="33" t="n"/>
-      <c r="K53" s="34">
+      <c r="J53" s="38" t="n"/>
+      <c r="K53" s="39">
         <f>IF(C53="","",F53+G53+H53-I53-J53)</f>
         <v/>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="32" t="n">
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="36" t="n">
         <v>47</v>
       </c>
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="33" t="n"/>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
-      <c r="F54" s="34">
+      <c r="B54" s="37" t="n"/>
+      <c r="C54" s="38" t="n"/>
+      <c r="D54" s="37" t="n"/>
+      <c r="E54" s="37" t="n"/>
+      <c r="F54" s="39">
         <f>IF(C54="","",C54*D54)</f>
         <v/>
       </c>
-      <c r="G54" s="34">
+      <c r="G54" s="39">
         <f>IF(C54="","",E54*(C54/8)*2)</f>
         <v/>
       </c>
-      <c r="H54" s="33" t="n"/>
-      <c r="I54" s="34">
+      <c r="H54" s="38" t="n"/>
+      <c r="I54" s="39">
         <f>IF(C54="","",ROUND((F54+G54)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J54" s="33" t="n"/>
-      <c r="K54" s="34">
+      <c r="J54" s="38" t="n"/>
+      <c r="K54" s="39">
         <f>IF(C54="","",F54+G54+H54-I54-J54)</f>
         <v/>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="32" t="n">
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="36" t="n">
         <v>48</v>
       </c>
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="33" t="n"/>
-      <c r="D55" s="17" t="n"/>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="34">
+      <c r="B55" s="37" t="n"/>
+      <c r="C55" s="38" t="n"/>
+      <c r="D55" s="37" t="n"/>
+      <c r="E55" s="37" t="n"/>
+      <c r="F55" s="39">
         <f>IF(C55="","",C55*D55)</f>
         <v/>
       </c>
-      <c r="G55" s="34">
+      <c r="G55" s="39">
         <f>IF(C55="","",E55*(C55/8)*2)</f>
         <v/>
       </c>
-      <c r="H55" s="33" t="n"/>
-      <c r="I55" s="34">
+      <c r="H55" s="38" t="n"/>
+      <c r="I55" s="39">
         <f>IF(C55="","",ROUND((F55+G55)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J55" s="33" t="n"/>
-      <c r="K55" s="34">
+      <c r="J55" s="38" t="n"/>
+      <c r="K55" s="39">
         <f>IF(C55="","",F55+G55+H55-I55-J55)</f>
         <v/>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="32" t="n">
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="36" t="n">
         <v>49</v>
       </c>
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="33" t="n"/>
-      <c r="D56" s="17" t="n"/>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="34">
+      <c r="B56" s="37" t="n"/>
+      <c r="C56" s="38" t="n"/>
+      <c r="D56" s="37" t="n"/>
+      <c r="E56" s="37" t="n"/>
+      <c r="F56" s="39">
         <f>IF(C56="","",C56*D56)</f>
         <v/>
       </c>
-      <c r="G56" s="34">
+      <c r="G56" s="39">
         <f>IF(C56="","",E56*(C56/8)*2)</f>
         <v/>
       </c>
-      <c r="H56" s="33" t="n"/>
-      <c r="I56" s="34">
+      <c r="H56" s="38" t="n"/>
+      <c r="I56" s="39">
         <f>IF(C56="","",ROUND((F56+G56)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J56" s="33" t="n"/>
-      <c r="K56" s="34">
+      <c r="J56" s="38" t="n"/>
+      <c r="K56" s="39">
         <f>IF(C56="","",F56+G56+H56-I56-J56)</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="32" t="n">
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="33" t="n"/>
-      <c r="D57" s="17" t="n"/>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="34">
+      <c r="B57" s="37" t="n"/>
+      <c r="C57" s="38" t="n"/>
+      <c r="D57" s="37" t="n"/>
+      <c r="E57" s="37" t="n"/>
+      <c r="F57" s="39">
         <f>IF(C57="","",C57*D57)</f>
         <v/>
       </c>
-      <c r="G57" s="34">
+      <c r="G57" s="39">
         <f>IF(C57="","",E57*(C57/8)*2)</f>
         <v/>
       </c>
-      <c r="H57" s="33" t="n"/>
-      <c r="I57" s="34">
+      <c r="H57" s="38" t="n"/>
+      <c r="I57" s="39">
         <f>IF(C57="","",ROUND((F57+G57)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J57" s="33" t="n"/>
-      <c r="K57" s="34">
+      <c r="J57" s="38" t="n"/>
+      <c r="K57" s="39">
         <f>IF(C57="","",F57+G57+H57-I57-J57)</f>
         <v/>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="32" t="n">
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="36" t="n">
         <v>51</v>
       </c>
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="33" t="n"/>
-      <c r="D58" s="17" t="n"/>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="34">
+      <c r="B58" s="37" t="n"/>
+      <c r="C58" s="38" t="n"/>
+      <c r="D58" s="37" t="n"/>
+      <c r="E58" s="37" t="n"/>
+      <c r="F58" s="39">
         <f>IF(C58="","",C58*D58)</f>
         <v/>
       </c>
-      <c r="G58" s="34">
+      <c r="G58" s="39">
         <f>IF(C58="","",E58*(C58/8)*2)</f>
         <v/>
       </c>
-      <c r="H58" s="33" t="n"/>
-      <c r="I58" s="34">
+      <c r="H58" s="38" t="n"/>
+      <c r="I58" s="39">
         <f>IF(C58="","",ROUND((F58+G58)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J58" s="33" t="n"/>
-      <c r="K58" s="34">
+      <c r="J58" s="38" t="n"/>
+      <c r="K58" s="39">
         <f>IF(C58="","",F58+G58+H58-I58-J58)</f>
         <v/>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="32" t="n">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="36" t="n">
         <v>52</v>
       </c>
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="33" t="n"/>
-      <c r="D59" s="17" t="n"/>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="34">
+      <c r="B59" s="37" t="n"/>
+      <c r="C59" s="38" t="n"/>
+      <c r="D59" s="37" t="n"/>
+      <c r="E59" s="37" t="n"/>
+      <c r="F59" s="39">
         <f>IF(C59="","",C59*D59)</f>
         <v/>
       </c>
-      <c r="G59" s="34">
+      <c r="G59" s="39">
         <f>IF(C59="","",E59*(C59/8)*2)</f>
         <v/>
       </c>
-      <c r="H59" s="33" t="n"/>
-      <c r="I59" s="34">
+      <c r="H59" s="38" t="n"/>
+      <c r="I59" s="39">
         <f>IF(C59="","",ROUND((F59+G59)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J59" s="33" t="n"/>
-      <c r="K59" s="34">
+      <c r="J59" s="38" t="n"/>
+      <c r="K59" s="39">
         <f>IF(C59="","",F59+G59+H59-I59-J59)</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="32" t="n">
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="36" t="n">
         <v>53</v>
       </c>
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="33" t="n"/>
-      <c r="D60" s="17" t="n"/>
-      <c r="E60" s="17" t="n"/>
-      <c r="F60" s="34">
+      <c r="B60" s="37" t="n"/>
+      <c r="C60" s="38" t="n"/>
+      <c r="D60" s="37" t="n"/>
+      <c r="E60" s="37" t="n"/>
+      <c r="F60" s="39">
         <f>IF(C60="","",C60*D60)</f>
         <v/>
       </c>
-      <c r="G60" s="34">
+      <c r="G60" s="39">
         <f>IF(C60="","",E60*(C60/8)*2)</f>
         <v/>
       </c>
-      <c r="H60" s="33" t="n"/>
-      <c r="I60" s="34">
+      <c r="H60" s="38" t="n"/>
+      <c r="I60" s="39">
         <f>IF(C60="","",ROUND((F60+G60)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J60" s="33" t="n"/>
-      <c r="K60" s="34">
+      <c r="J60" s="38" t="n"/>
+      <c r="K60" s="39">
         <f>IF(C60="","",F60+G60+H60-I60-J60)</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="32" t="n">
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="36" t="n">
         <v>54</v>
       </c>
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="33" t="n"/>
-      <c r="D61" s="17" t="n"/>
-      <c r="E61" s="17" t="n"/>
-      <c r="F61" s="34">
+      <c r="B61" s="37" t="n"/>
+      <c r="C61" s="38" t="n"/>
+      <c r="D61" s="37" t="n"/>
+      <c r="E61" s="37" t="n"/>
+      <c r="F61" s="39">
         <f>IF(C61="","",C61*D61)</f>
         <v/>
       </c>
-      <c r="G61" s="34">
+      <c r="G61" s="39">
         <f>IF(C61="","",E61*(C61/8)*2)</f>
         <v/>
       </c>
-      <c r="H61" s="33" t="n"/>
-      <c r="I61" s="34">
+      <c r="H61" s="38" t="n"/>
+      <c r="I61" s="39">
         <f>IF(C61="","",ROUND((F61+G61)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J61" s="33" t="n"/>
-      <c r="K61" s="34">
+      <c r="J61" s="38" t="n"/>
+      <c r="K61" s="39">
         <f>IF(C61="","",F61+G61+H61-I61-J61)</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="32" t="n">
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="36" t="n">
         <v>55</v>
       </c>
-      <c r="B62" s="17" t="n"/>
-      <c r="C62" s="33" t="n"/>
-      <c r="D62" s="17" t="n"/>
-      <c r="E62" s="17" t="n"/>
-      <c r="F62" s="34">
+      <c r="B62" s="37" t="n"/>
+      <c r="C62" s="38" t="n"/>
+      <c r="D62" s="37" t="n"/>
+      <c r="E62" s="37" t="n"/>
+      <c r="F62" s="39">
         <f>IF(C62="","",C62*D62)</f>
         <v/>
       </c>
-      <c r="G62" s="34">
+      <c r="G62" s="39">
         <f>IF(C62="","",E62*(C62/8)*2)</f>
         <v/>
       </c>
-      <c r="H62" s="33" t="n"/>
-      <c r="I62" s="34">
+      <c r="H62" s="38" t="n"/>
+      <c r="I62" s="39">
         <f>IF(C62="","",ROUND((F62+G62)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J62" s="33" t="n"/>
-      <c r="K62" s="34">
+      <c r="J62" s="38" t="n"/>
+      <c r="K62" s="39">
         <f>IF(C62="","",F62+G62+H62-I62-J62)</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="32" t="n">
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="36" t="n">
         <v>56</v>
       </c>
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="33" t="n"/>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="17" t="n"/>
-      <c r="F63" s="34">
+      <c r="B63" s="37" t="n"/>
+      <c r="C63" s="38" t="n"/>
+      <c r="D63" s="37" t="n"/>
+      <c r="E63" s="37" t="n"/>
+      <c r="F63" s="39">
         <f>IF(C63="","",C63*D63)</f>
         <v/>
       </c>
-      <c r="G63" s="34">
+      <c r="G63" s="39">
         <f>IF(C63="","",E63*(C63/8)*2)</f>
         <v/>
       </c>
-      <c r="H63" s="33" t="n"/>
-      <c r="I63" s="34">
+      <c r="H63" s="38" t="n"/>
+      <c r="I63" s="39">
         <f>IF(C63="","",ROUND((F63+G63)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J63" s="33" t="n"/>
-      <c r="K63" s="34">
+      <c r="J63" s="38" t="n"/>
+      <c r="K63" s="39">
         <f>IF(C63="","",F63+G63+H63-I63-J63)</f>
         <v/>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="32" t="n">
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="36" t="n">
         <v>57</v>
       </c>
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="33" t="n"/>
-      <c r="D64" s="17" t="n"/>
-      <c r="E64" s="17" t="n"/>
-      <c r="F64" s="34">
+      <c r="B64" s="37" t="n"/>
+      <c r="C64" s="38" t="n"/>
+      <c r="D64" s="37" t="n"/>
+      <c r="E64" s="37" t="n"/>
+      <c r="F64" s="39">
         <f>IF(C64="","",C64*D64)</f>
         <v/>
       </c>
-      <c r="G64" s="34">
+      <c r="G64" s="39">
         <f>IF(C64="","",E64*(C64/8)*2)</f>
         <v/>
       </c>
-      <c r="H64" s="33" t="n"/>
-      <c r="I64" s="34">
+      <c r="H64" s="38" t="n"/>
+      <c r="I64" s="39">
         <f>IF(C64="","",ROUND((F64+G64)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J64" s="33" t="n"/>
-      <c r="K64" s="34">
+      <c r="J64" s="38" t="n"/>
+      <c r="K64" s="39">
         <f>IF(C64="","",F64+G64+H64-I64-J64)</f>
         <v/>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="32" t="n">
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="36" t="n">
         <v>58</v>
       </c>
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="33" t="n"/>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="17" t="n"/>
-      <c r="F65" s="34">
+      <c r="B65" s="37" t="n"/>
+      <c r="C65" s="38" t="n"/>
+      <c r="D65" s="37" t="n"/>
+      <c r="E65" s="37" t="n"/>
+      <c r="F65" s="39">
         <f>IF(C65="","",C65*D65)</f>
         <v/>
       </c>
-      <c r="G65" s="34">
+      <c r="G65" s="39">
         <f>IF(C65="","",E65*(C65/8)*2)</f>
         <v/>
       </c>
-      <c r="H65" s="33" t="n"/>
-      <c r="I65" s="34">
+      <c r="H65" s="38" t="n"/>
+      <c r="I65" s="39">
         <f>IF(C65="","",ROUND((F65+G65)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J65" s="33" t="n"/>
-      <c r="K65" s="34">
+      <c r="J65" s="38" t="n"/>
+      <c r="K65" s="39">
         <f>IF(C65="","",F65+G65+H65-I65-J65)</f>
         <v/>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="32" t="n">
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="36" t="n">
         <v>59</v>
       </c>
-      <c r="B66" s="17" t="n"/>
-      <c r="C66" s="33" t="n"/>
-      <c r="D66" s="17" t="n"/>
-      <c r="E66" s="17" t="n"/>
-      <c r="F66" s="34">
+      <c r="B66" s="37" t="n"/>
+      <c r="C66" s="38" t="n"/>
+      <c r="D66" s="37" t="n"/>
+      <c r="E66" s="37" t="n"/>
+      <c r="F66" s="39">
         <f>IF(C66="","",C66*D66)</f>
         <v/>
       </c>
-      <c r="G66" s="34">
+      <c r="G66" s="39">
         <f>IF(C66="","",E66*(C66/8)*2)</f>
         <v/>
       </c>
-      <c r="H66" s="33" t="n"/>
-      <c r="I66" s="34">
+      <c r="H66" s="38" t="n"/>
+      <c r="I66" s="39">
         <f>IF(C66="","",ROUND((F66+G66)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J66" s="33" t="n"/>
-      <c r="K66" s="34">
+      <c r="J66" s="38" t="n"/>
+      <c r="K66" s="39">
         <f>IF(C66="","",F66+G66+H66-I66-J66)</f>
         <v/>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="32" t="n">
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="36" t="n">
         <v>60</v>
       </c>
-      <c r="B67" s="17" t="n"/>
-      <c r="C67" s="33" t="n"/>
-      <c r="D67" s="17" t="n"/>
-      <c r="E67" s="17" t="n"/>
-      <c r="F67" s="34">
+      <c r="B67" s="37" t="n"/>
+      <c r="C67" s="38" t="n"/>
+      <c r="D67" s="37" t="n"/>
+      <c r="E67" s="37" t="n"/>
+      <c r="F67" s="39">
         <f>IF(C67="","",C67*D67)</f>
         <v/>
       </c>
-      <c r="G67" s="34">
+      <c r="G67" s="39">
         <f>IF(C67="","",E67*(C67/8)*2)</f>
         <v/>
       </c>
-      <c r="H67" s="33" t="n"/>
-      <c r="I67" s="34">
+      <c r="H67" s="38" t="n"/>
+      <c r="I67" s="39">
         <f>IF(C67="","",ROUND((F67+G67)*$G$5,2))</f>
         <v/>
       </c>
-      <c r="J67" s="33" t="n"/>
-      <c r="K67" s="34">
+      <c r="J67" s="38" t="n"/>
+      <c r="K67" s="39">
         <f>IF(C67="","",F67+G67+H67-I67-J67)</f>
         <v/>
       </c>
@@ -3316,32 +3536,32 @@
       <c r="B68" s="4" t="n"/>
       <c r="C68" s="4" t="n"/>
       <c r="D68" s="4" t="n"/>
-      <c r="E68" s="35" t="inlineStr">
+      <c r="E68" s="40" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="F68" s="36">
+      <c r="F68" s="41">
         <f>SUM(F8:F67)</f>
         <v/>
       </c>
-      <c r="G68" s="36">
+      <c r="G68" s="41">
         <f>SUM(G8:G67)</f>
         <v/>
       </c>
-      <c r="H68" s="36">
+      <c r="H68" s="41">
         <f>SUM(H8:H67)</f>
         <v/>
       </c>
-      <c r="I68" s="36">
+      <c r="I68" s="41">
         <f>SUM(I8:I67)</f>
         <v/>
       </c>
-      <c r="J68" s="36">
+      <c r="J68" s="41">
         <f>SUM(J8:J67)</f>
         <v/>
       </c>
-      <c r="K68" s="36">
+      <c r="K68" s="41">
         <f>SUM(K8:K67)</f>
         <v/>
       </c>
@@ -3373,34 +3593,34 @@
       <c r="K70" s="4" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="37" t="n"/>
-      <c r="B71" s="37" t="n"/>
+      <c r="A71" s="42" t="n"/>
+      <c r="B71" s="42" t="n"/>
       <c r="C71" s="4" t="n"/>
-      <c r="D71" s="37" t="n"/>
-      <c r="E71" s="37" t="n"/>
+      <c r="D71" s="42" t="n"/>
+      <c r="E71" s="42" t="n"/>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="37" t="n"/>
-      <c r="H71" s="37" t="n"/>
+      <c r="G71" s="42" t="n"/>
+      <c r="H71" s="42" t="n"/>
       <c r="I71" s="4" t="n"/>
       <c r="J71" s="4" t="n"/>
       <c r="K71" s="4" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="38" t="inlineStr">
+      <c r="A72" s="43" t="inlineStr">
         <is>
           <t>ELABORÓ</t>
         </is>
       </c>
       <c r="B72" s="4" t="n"/>
       <c r="C72" s="4" t="n"/>
-      <c r="D72" s="38" t="inlineStr">
+      <c r="D72" s="43" t="inlineStr">
         <is>
           <t>REVISÓ</t>
         </is>
       </c>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="38" t="inlineStr">
+      <c r="G72" s="43" t="inlineStr">
         <is>
           <t>AUTORIZÓ</t>
         </is>
@@ -3427,6 +3647,26 @@
     <mergeCell ref="D71:E71"/>
     <mergeCell ref="G72:H72"/>
   </mergeCells>
+  <conditionalFormatting sqref="K8:K67">
+    <cfRule type="dataBar" priority="1">
+      <dataBar showValue="1">
+        <cfvo type="num" val="0"/>
+        <cfvo type="max"/>
+        <color rgb="002A6FBA"/>
+      </dataBar>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="3">
+    <dataValidation sqref="C8:C67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="H8:H67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="J8:J67" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="IMPORTE NO VÁLIDO" error="Escribe un importe numérico positivo, sin símbolo $ ni letras." promptTitle="IMPORTE (MXN)" prompt="Solo números, sin $ ni comas." type="decimal" errorStyle="warning" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="1"/>
@@ -3464,7 +3704,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="22" t="inlineStr">
+      <c r="A1" s="26" t="inlineStr">
         <is>
           <t>RESUMEN DE NÓMINA</t>
         </is>
@@ -3475,30 +3715,30 @@
       <c r="E1" s="1" t="n"/>
       <c r="F1" s="1" t="n"/>
       <c r="G1" s="1" t="n"/>
-      <c r="H1" s="23" t="inlineStr">
+      <c r="H1" s="27" t="inlineStr">
         <is>
           <t>INSERTE SU LOGO
 (clic derecho &gt; Insertar imagen)</t>
         </is>
       </c>
-      <c r="I1" s="39" t="n"/>
-      <c r="J1" s="24" t="n"/>
+      <c r="I1" s="44" t="n"/>
+      <c r="J1" s="28" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="29" t="inlineStr">
         <is>
           <t>Percepciones, deducciones y neto del periodo</t>
         </is>
       </c>
-      <c r="B2" s="26" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="40" t="n"/>
-      <c r="J2" s="28" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
+      <c r="H2" s="31" t="n"/>
+      <c r="I2" s="45" t="n"/>
+      <c r="J2" s="32" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n"/>
@@ -3512,56 +3752,56 @@
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="41" t="inlineStr">
+      <c r="B4" s="46" t="inlineStr">
         <is>
           <t>PERCEPCIONES</t>
         </is>
       </c>
-      <c r="C4" s="42" t="n"/>
-      <c r="D4" s="41" t="inlineStr">
+      <c r="C4" s="47" t="n"/>
+      <c r="D4" s="46" t="inlineStr">
         <is>
           <t>DEDUCCIONES</t>
         </is>
       </c>
-      <c r="E4" s="42" t="n"/>
-      <c r="F4" s="41" t="inlineStr">
+      <c r="E4" s="47" t="n"/>
+      <c r="F4" s="46" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
       </c>
-      <c r="G4" s="42" t="n"/>
-      <c r="H4" s="41" t="inlineStr">
+      <c r="G4" s="47" t="n"/>
+      <c r="H4" s="46" t="inlineStr">
         <is>
           <t>EMPLEADOS</t>
         </is>
       </c>
-      <c r="I4" s="42" t="n"/>
+      <c r="I4" s="47" t="n"/>
       <c r="J4" s="4" t="n"/>
     </row>
-    <row r="5" ht="36" customHeight="1">
+    <row r="5" ht="46" customHeight="1">
       <c r="A5" s="4" t="n"/>
-      <c r="B5" s="43">
+      <c r="B5" s="48">
         <f>FORMATO!F68+FORMATO!G68+FORMATO!H68</f>
         <v/>
       </c>
-      <c r="C5" s="44" t="n"/>
-      <c r="D5" s="43">
+      <c r="C5" s="49" t="n"/>
+      <c r="D5" s="48">
         <f>FORMATO!I68+FORMATO!J68</f>
         <v/>
       </c>
-      <c r="E5" s="44" t="n"/>
-      <c r="F5" s="43">
+      <c r="E5" s="49" t="n"/>
+      <c r="F5" s="48">
         <f>FORMATO!K68</f>
         <v/>
       </c>
-      <c r="G5" s="44" t="n"/>
-      <c r="H5" s="45">
+      <c r="G5" s="49" t="n"/>
+      <c r="H5" s="50">
         <f>COUNT(FORMATO!C8:C67)</f>
         <v/>
       </c>
-      <c r="I5" s="44" t="n"/>
+      <c r="I5" s="49" t="n"/>
       <c r="J5" s="4" t="n"/>
     </row>
     <row r="6">
@@ -3576,9 +3816,12 @@
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
-      <c r="B7" s="4" t="n"/>
+      <c r="B7" s="51">
+        <f>IF(H5=0,"Captura empleados en la hoja FORMATO para ver el análisis automático.","Mayor neto: "&amp;INDEX(FORMATO!B8:B67,MATCH(MAX(FORMATO!K8:K67),FORMATO!K8:K67,0))&amp;" ($"&amp;TEXT(MAX(FORMATO!K8:K67),"#,##0")&amp;"). Neto promedio por empleado: $"&amp;TEXT(F5/H5,"#,##0")&amp;".")</f>
+        <v/>
+      </c>
       <c r="C7" s="4" t="n"/>
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
@@ -3794,12 +4037,12 @@
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="31" t="inlineStr">
+      <c r="B25" s="35" t="inlineStr">
         <is>
           <t>EMPLEADO</t>
         </is>
       </c>
-      <c r="C25" s="31" t="inlineStr">
+      <c r="C25" s="35" t="inlineStr">
         <is>
           <t>NETO A PAGAR</t>
         </is>
@@ -3814,11 +4057,11 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="46">
+      <c r="B26" s="52">
         <f>IF(FORMATO!B8="","",FORMATO!B8)</f>
         <v/>
       </c>
-      <c r="C26" s="34">
+      <c r="C26" s="53">
         <f>IF(FORMATO!K8="",0,FORMATO!K8)</f>
         <v/>
       </c>
@@ -3832,11 +4075,11 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="n"/>
-      <c r="B27" s="46">
+      <c r="B27" s="52">
         <f>IF(FORMATO!B9="","",FORMATO!B9)</f>
         <v/>
       </c>
-      <c r="C27" s="34">
+      <c r="C27" s="53">
         <f>IF(FORMATO!K9="",0,FORMATO!K9)</f>
         <v/>
       </c>
@@ -3850,11 +4093,11 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="n"/>
-      <c r="B28" s="46">
+      <c r="B28" s="52">
         <f>IF(FORMATO!B10="","",FORMATO!B10)</f>
         <v/>
       </c>
-      <c r="C28" s="34">
+      <c r="C28" s="53">
         <f>IF(FORMATO!K10="",0,FORMATO!K10)</f>
         <v/>
       </c>
@@ -3868,11 +4111,11 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="n"/>
-      <c r="B29" s="46">
+      <c r="B29" s="52">
         <f>IF(FORMATO!B11="","",FORMATO!B11)</f>
         <v/>
       </c>
-      <c r="C29" s="34">
+      <c r="C29" s="53">
         <f>IF(FORMATO!K11="",0,FORMATO!K11)</f>
         <v/>
       </c>
@@ -3886,11 +4129,11 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="n"/>
-      <c r="B30" s="46">
+      <c r="B30" s="52">
         <f>IF(FORMATO!B12="","",FORMATO!B12)</f>
         <v/>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="53">
         <f>IF(FORMATO!K12="",0,FORMATO!K12)</f>
         <v/>
       </c>
@@ -3904,11 +4147,11 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="n"/>
-      <c r="B31" s="46">
+      <c r="B31" s="52">
         <f>IF(FORMATO!B13="","",FORMATO!B13)</f>
         <v/>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="53">
         <f>IF(FORMATO!K13="",0,FORMATO!K13)</f>
         <v/>
       </c>
@@ -3922,11 +4165,11 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="n"/>
-      <c r="B32" s="46">
+      <c r="B32" s="52">
         <f>IF(FORMATO!B14="","",FORMATO!B14)</f>
         <v/>
       </c>
-      <c r="C32" s="34">
+      <c r="C32" s="53">
         <f>IF(FORMATO!K14="",0,FORMATO!K14)</f>
         <v/>
       </c>
@@ -3940,11 +4183,11 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="n"/>
-      <c r="B33" s="46">
+      <c r="B33" s="52">
         <f>IF(FORMATO!B15="","",FORMATO!B15)</f>
         <v/>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="53">
         <f>IF(FORMATO!K15="",0,FORMATO!K15)</f>
         <v/>
       </c>
@@ -3958,11 +4201,11 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="n"/>
-      <c r="B34" s="46">
+      <c r="B34" s="52">
         <f>IF(FORMATO!B16="","",FORMATO!B16)</f>
         <v/>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="53">
         <f>IF(FORMATO!K16="",0,FORMATO!K16)</f>
         <v/>
       </c>
@@ -3976,11 +4219,11 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="n"/>
-      <c r="B35" s="46">
+      <c r="B35" s="52">
         <f>IF(FORMATO!B17="","",FORMATO!B17)</f>
         <v/>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="53">
         <f>IF(FORMATO!K17="",0,FORMATO!K17)</f>
         <v/>
       </c>
@@ -3994,11 +4237,11 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="n"/>
-      <c r="B36" s="46">
+      <c r="B36" s="52">
         <f>IF(FORMATO!B18="","",FORMATO!B18)</f>
         <v/>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="53">
         <f>IF(FORMATO!K18="",0,FORMATO!K18)</f>
         <v/>
       </c>
@@ -4012,11 +4255,11 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="n"/>
-      <c r="B37" s="46">
+      <c r="B37" s="52">
         <f>IF(FORMATO!B19="","",FORMATO!B19)</f>
         <v/>
       </c>
-      <c r="C37" s="34">
+      <c r="C37" s="53">
         <f>IF(FORMATO!K19="",0,FORMATO!K19)</f>
         <v/>
       </c>
@@ -4030,11 +4273,11 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="n"/>
-      <c r="B38" s="46">
+      <c r="B38" s="52">
         <f>IF(FORMATO!B20="","",FORMATO!B20)</f>
         <v/>
       </c>
-      <c r="C38" s="34">
+      <c r="C38" s="53">
         <f>IF(FORMATO!K20="",0,FORMATO!K20)</f>
         <v/>
       </c>
@@ -4048,11 +4291,11 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="n"/>
-      <c r="B39" s="46">
+      <c r="B39" s="52">
         <f>IF(FORMATO!B21="","",FORMATO!B21)</f>
         <v/>
       </c>
-      <c r="C39" s="34">
+      <c r="C39" s="53">
         <f>IF(FORMATO!K21="",0,FORMATO!K21)</f>
         <v/>
       </c>
@@ -4066,11 +4309,11 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="n"/>
-      <c r="B40" s="46">
+      <c r="B40" s="52">
         <f>IF(FORMATO!B22="","",FORMATO!B22)</f>
         <v/>
       </c>
-      <c r="C40" s="34">
+      <c r="C40" s="53">
         <f>IF(FORMATO!K22="",0,FORMATO!K22)</f>
         <v/>
       </c>
@@ -4084,10 +4327,11 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H1:J2"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="B7:I7"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D5:E5"/>
@@ -4131,7 +4375,7 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="47" t="inlineStr">
+      <c r="B1" s="54" t="inlineStr">
         <is>
           <t>AYUDA Y PREGUNTAS FRECUENTES</t>
         </is>
@@ -4142,7 +4386,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
-      <c r="B2" s="48" t="inlineStr">
+      <c r="B2" s="55" t="inlineStr">
         <is>
           <t>NÓMINA SIMPLIFICADA</t>
         </is>
@@ -4179,12 +4423,12 @@
     <row r="6" ht="38" customHeight="1">
       <c r="A6" s="4" t="n"/>
       <c r="B6" s="4" t="n"/>
-      <c r="C6" s="49" t="inlineStr">
+      <c r="C6" s="56" t="inlineStr">
         <is>
           <t>¿El % de IMSS es exacto?</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>No. Es una referencia editable; la cuota real varía por ramo, salario base de cotización y prima de riesgo.</t>
         </is>
@@ -4194,12 +4438,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
-      <c r="C7" s="49" t="inlineStr">
+      <c r="C7" s="56" t="inlineStr">
         <is>
           <t>¿Sirve para timbrar recibos?</t>
         </is>
       </c>
-      <c r="D7" s="50" t="inlineStr">
+      <c r="D7" s="57" t="inlineStr">
         <is>
           <t>No. Para recibos CFDI de nómina usa tu sistema de timbrado.</t>
         </is>
@@ -4209,12 +4453,12 @@
     <row r="8" ht="53" customHeight="1">
       <c r="A8" s="4" t="n"/>
       <c r="B8" s="4" t="n"/>
-      <c r="C8" s="49" t="inlineStr">
+      <c r="C8" s="56" t="inlineStr">
         <is>
           <t>¿Por qué no puedo escribir en algunas celdas?</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>La hoja está protegida para que no se borren fórmulas por accidente. Solo se editan las celdas de captura (color crema). Si necesitas modificar algo más: pestaña Revisar &gt; Desproteger hoja (no tiene contraseña).</t>
         </is>
@@ -4224,12 +4468,12 @@
     <row r="9" ht="38" customHeight="1">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
-      <c r="C9" s="49" t="inlineStr">
+      <c r="C9" s="56" t="inlineStr">
         <is>
           <t>¿Cómo agrego mi logotipo?</t>
         </is>
       </c>
-      <c r="D9" s="50" t="inlineStr">
+      <c r="D9" s="57" t="inlineStr">
         <is>
           <t>Haz clic en el recuadro punteado de la esquina superior derecha del formato y usa Insertar &gt; Imágenes. Ajusta el tamaño sin salirte del recuadro.</t>
         </is>
@@ -4239,12 +4483,12 @@
     <row r="10" ht="38" customHeight="1">
       <c r="A10" s="4" t="n"/>
       <c r="B10" s="4" t="n"/>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="56" t="inlineStr">
         <is>
           <t>¿Cómo lo imprimo o lo convierto a PDF?</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>Archivo &gt; Imprimir (ya está ajustado a una hoja de ancho). Para PDF elige 'Microsoft Print to PDF' o Archivo &gt; Exportar &gt; PDF.</t>
         </is>
@@ -4254,12 +4498,12 @@
     <row r="11" ht="38" customHeight="1">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
-      <c r="C11" s="49" t="inlineStr">
+      <c r="C11" s="56" t="inlineStr">
         <is>
           <t>¿Con qué versiones de Excel funciona?</t>
         </is>
       </c>
-      <c r="D11" s="50" t="inlineStr">
+      <c r="D11" s="57" t="inlineStr">
         <is>
           <t>Excel 2016, 2019, 2021 y Microsoft 365 (Windows y Mac). Funciona en LibreOffice y Google Sheets, aunque algunas gráficas y formatos pueden verse distintos.</t>
         </is>
@@ -4269,14 +4513,14 @@
     <row r="12" ht="38" customHeight="1">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
-      <c r="C12" s="49" t="inlineStr">
-        <is>
-          <t>¿Por qué la letra se ve diferente?</t>
-        </is>
-      </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>El diseño usa la fuente Abadi, incluida en Microsoft 365. Si tu versión no la tiene, Excel la sustituye por otra; no afecta el funcionamiento.</t>
+      <c r="C12" s="56" t="inlineStr">
+        <is>
+          <t>¿Puedo cambiar la letra?</t>
+        </is>
+      </c>
+      <c r="D12" s="57" t="inlineStr">
+        <is>
+          <t>El diseño usa la fuente Arial, disponible en Windows, Mac y Google Sheets. Si necesitas otra, selecciona todo (Ctrl+E) y cambia la fuente; no afecta el funcionamiento.</t>
         </is>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -4284,12 +4528,12 @@
     <row r="13" ht="38" customHeight="1">
       <c r="A13" s="4" t="n"/>
       <c r="B13" s="4" t="n"/>
-      <c r="C13" s="49" t="inlineStr">
+      <c r="C13" s="56" t="inlineStr">
         <is>
           <t>¿Puedo usarlo en varias empresas o por varios años?</t>
         </is>
       </c>
-      <c r="D13" s="50" t="inlineStr">
+      <c r="D13" s="57" t="inlineStr">
         <is>
           <t>Sí. Guarda una copia del archivo por empresa o por periodo (Archivo &gt; Guardar como) y deja el original en blanco como plantilla maestra.</t>
         </is>
@@ -4317,12 +4561,12 @@
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
-      <c r="C16" s="51" t="inlineStr">
+      <c r="C16" s="58" t="inlineStr">
         <is>
           <t>SUELDO DIARIO</t>
         </is>
       </c>
-      <c r="D16" s="52" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>Pago por día laborado.</t>
         </is>
@@ -4332,12 +4576,12 @@
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
-      <c r="C17" s="51" t="inlineStr">
+      <c r="C17" s="58" t="inlineStr">
         <is>
           <t>SDI</t>
         </is>
       </c>
-      <c r="D17" s="52" t="inlineStr">
+      <c r="D17" s="59" t="inlineStr">
         <is>
           <t>Salario diario integrado, base de cotización al IMSS.</t>
         </is>
@@ -4347,12 +4591,12 @@
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="4" t="n"/>
       <c r="B18" s="4" t="n"/>
-      <c r="C18" s="51" t="inlineStr">
+      <c r="C18" s="58" t="inlineStr">
         <is>
           <t>PERCEPCIONES</t>
         </is>
       </c>
-      <c r="D18" s="52" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>Sueldos, horas extra, bonos y demás pagos.</t>
         </is>
@@ -4362,12 +4606,12 @@
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="4" t="n"/>
       <c r="B19" s="4" t="n"/>
-      <c r="C19" s="51" t="inlineStr">
+      <c r="C19" s="58" t="inlineStr">
         <is>
           <t>DEDUCCIONES</t>
         </is>
       </c>
-      <c r="D19" s="52" t="inlineStr">
+      <c r="D19" s="59" t="inlineStr">
         <is>
           <t>ISR, IMSS y otros descuentos.</t>
         </is>
@@ -4377,12 +4621,12 @@
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="4" t="n"/>
       <c r="B20" s="4" t="n"/>
-      <c r="C20" s="51" t="inlineStr">
+      <c r="C20" s="58" t="inlineStr">
         <is>
           <t>NETO</t>
         </is>
       </c>
-      <c r="D20" s="52" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>Percepciones - deducciones.</t>
         </is>
@@ -4409,12 +4653,12 @@
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="4" t="n"/>
-      <c r="B23" s="53" t="inlineStr">
+      <c r="B23" s="60" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C23" s="54" t="inlineStr">
+      <c r="C23" s="61" t="inlineStr">
         <is>
           <t>Asistencia del periodo validada</t>
         </is>
@@ -4424,12 +4668,12 @@
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="4" t="n"/>
-      <c r="B24" s="53" t="inlineStr">
+      <c r="B24" s="60" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C24" s="54" t="inlineStr">
+      <c r="C24" s="61" t="inlineStr">
         <is>
           <t>Horas extra autorizadas</t>
         </is>
@@ -4439,12 +4683,12 @@
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="4" t="n"/>
-      <c r="B25" s="53" t="inlineStr">
+      <c r="B25" s="60" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C25" s="54" t="inlineStr">
+      <c r="C25" s="61" t="inlineStr">
         <is>
           <t>ISR/IMSS calculados</t>
         </is>
@@ -4454,12 +4698,12 @@
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="4" t="n"/>
-      <c r="B26" s="53" t="inlineStr">
+      <c r="B26" s="60" t="inlineStr">
         <is>
           <t>☐</t>
         </is>
       </c>
-      <c r="C26" s="54" t="inlineStr">
+      <c r="C26" s="61" t="inlineStr">
         <is>
           <t>Dispersión y recibos entregados</t>
         </is>
